--- a/public/Quiz.xlsx
+++ b/public/Quiz.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Micael\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4FC84CF-519E-455D-8C58-0532AA83C81C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52B9BBA4-10E5-45B9-BCC4-C744704C6EC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{814585D2-DACD-4865-94B7-0CB5BA22B5AF}"/>
   </bookViews>
@@ -54,217 +54,217 @@
     <t>correct</t>
   </si>
   <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>C1</t>
-  </si>
-  <si>
-    <t>Estas a punto de entrar y vas tarde. Tenes 45 segundos. Cual preparacion minima te deja mejor parado para no improvisar adentro?</t>
-  </si>
-  <si>
-    <t>Entrar directo y preguntar “¿qué te anoto?” para ahorrar tiempo, sin preparar nada afuera.</t>
-  </si>
-  <si>
-    <t>Mirar solo promos generales y entrar a ofrecerlas, para no meter presión ni discutir.</t>
-  </si>
-  <si>
-    <t>Marcar GPS, mirar en Bot/App 2 datos (compra fija + última compra) y entrar con plan simple: base + 1 idea.</t>
-  </si>
-  <si>
-    <t>Pensar una estrategia sin mirar Bot/App: “adentro veo” y arrancar. Y seguís con el pedido en el sistema.</t>
-  </si>
-  <si>
-    <t>Llamar al cliente antes de entrar para preguntarle qué quiere y armar el pedido por teléfono.</t>
-  </si>
-  <si>
-    <t>C2</t>
-  </si>
-  <si>
-    <t>En el Bot ves que un cliente que siempre compraba un producto fuerte bajo mucho el volumen las ultimas 2 visitas. Que preparación es más inteligente antes de entrar?</t>
-  </si>
-  <si>
-    <t>Ignorarlo y sostener la visita igual, asumiendo que ya no le interesa ese producto.</t>
-  </si>
-  <si>
-    <t>Entrar ofreciendo solo productos nuevos para subir ticket, sin revisar qué pasó con el fuerte.</t>
-  </si>
-  <si>
-    <t>Preparar una pregunta corta para entender el motivo (rotación/precio/competencia) y ajustar reposición a su realidad.</t>
-  </si>
-  <si>
-    <t>Entrar a reclamarle por qué bajó y presionarlo para que vuelva a subir el volumen.</t>
-  </si>
-  <si>
-    <t>No visitarlo por ahora, asumir que no vale la pena y pasar al siguiente cliente hoy.</t>
-  </si>
-  <si>
-    <t>C3</t>
-  </si>
-  <si>
-    <t>Cual de estas cosas NO es parte del checklist de preparacion inmediata antes de entrar?</t>
-  </si>
-  <si>
-    <t>Marcar GPS al llegar. Para no meter presión ni discutir.</t>
-  </si>
-  <si>
-    <t>Revisar qué compra siempre, cantidades y frecuencia. Para que quede corto y claro.</t>
-  </si>
-  <si>
-    <t>Identificar si compra categorías del portfolio a otros proveedores.</t>
-  </si>
-  <si>
-    <t>Memorizar una lista completa de 10 promos para decirlas todas</t>
-  </si>
-  <si>
-    <t>Recordar su problema principal de la visita anterior.</t>
-  </si>
-  <si>
-    <t>C4</t>
-  </si>
-  <si>
-    <t>Cliente nuevo sin historial. Cual seria una preparacion minima aceptable antes de entrar?</t>
-  </si>
-  <si>
-    <t>Entrar sin preparar nada y empezar la conversación “a ver qué sale” en el momento.</t>
-  </si>
-  <si>
-    <t>Marcar GPS, revisar ofertas zonales y armar un pedido base típico más una pregunta de diagnóstico.</t>
-  </si>
-  <si>
-    <t>Marcar GPS y confiar en improvisar todo adentro, sin revisar información previa del recorrido.</t>
-  </si>
-  <si>
-    <t>Entrar con un discurso de promos generales y esperar que alguna alternativa le interese hoy.</t>
-  </si>
-  <si>
-    <t>Postergar la visita hasta tener compras registradas y recién ahí empezar a trabajarlo en serio.</t>
-  </si>
-  <si>
-    <t>C5</t>
-  </si>
-  <si>
-    <t>Tenes 6 promos activas. En el Bot ves que el cliente viene quejandose de margen. Que decision previa es mas solida?</t>
-  </si>
-  <si>
-    <t>Entrar y recitar las 6 promos seguidas, esperando que alguna le cierre en el momento.</t>
-  </si>
-  <si>
-    <t>Elegir la promo más fuerte del mes, aunque no conecte con el problema de margen del cliente.</t>
-  </si>
-  <si>
-    <t>Evitar promos por completo y limitarte a tomar el pedido habitual sin proponer alternativas.</t>
-  </si>
-  <si>
-    <t>Seleccionar 1–2 promos que mejoren margen y preparar una frase simple de beneficio para ese cliente.</t>
-  </si>
-  <si>
-    <t>Ofrecer solo lanzamientos nuevos y dejar afuera promos pensadas para margen y rotación del local.</t>
-  </si>
-  <si>
-    <t>C6</t>
-  </si>
-  <si>
-    <t>Antes de entrar, recordas que el cliente te dijo la visita pasada: 'no tengo mas lugar'. Que mini estrategia pre-armas?</t>
-  </si>
-  <si>
-    <t>Entrar con foco en subir volumen para aprovechar el viaje, aunque ya avisó que no tiene espacio.</t>
-  </si>
-  <si>
-    <t>Entrar con foco en liberar espacio: ver qué no rota y proponer alta rotación en pocas unidades y formato chico.</t>
-  </si>
-  <si>
-    <t>No ofrecer nada nuevo y pedir solo “lo de siempre”, aunque la traba de espacio siga igual.</t>
-  </si>
-  <si>
-    <t>Cambiar el tema hacia impuestos y desviar la conversación, sin resolver la traba principal del cliente.</t>
-  </si>
-  <si>
-    <t>Evitar mirar depósito/estantería para no incomodar y seguir la visita como si no hubiera problema.</t>
-  </si>
-  <si>
-    <t>C7</t>
-  </si>
-  <si>
-    <t>Te diste cuenta de que entraste sin marcar GPS. Que accion es mas profesional?</t>
-  </si>
-  <si>
-    <t>Marcar GPS apenas puedas (si hace falta, salir un segundo a la puerta) para que la visita quede registrada.</t>
-  </si>
-  <si>
-    <t>Seguir la visita normal sin marcar GPS y darlo por perdido en esta vuelta.</t>
-  </si>
-  <si>
-    <t>Marcar el GPS al final del día desde cualquier lugar, solo para que figure en el sistema.</t>
-  </si>
-  <si>
-    <t>Pedirle al cliente que confirme que estuviste y usar eso como reemplazo del GPS.</t>
-  </si>
-  <si>
-    <t>Marcar GPS en el negocio siguiente “para compensar” y cerrar el número de visitas.</t>
-  </si>
-  <si>
-    <t>C8</t>
-  </si>
-  <si>
-    <t>Ordena la secuencia mas logica antes de entrar (1 minuto de preparacion).</t>
-  </si>
-  <si>
-    <t>Marcar GPS -&gt; mirar Bot/App -&gt; pensar 1–2 ideas -&gt; entrar y saludar con foco.</t>
-  </si>
-  <si>
-    <t>Entrar y saludar -&gt; marcar GPS -&gt; mirar Bot/App -&gt; pensar estrategia ya adentro.</t>
-  </si>
-  <si>
-    <t>Mirar Bot/App -&gt; entrar y saludar -&gt; marcar GPS -&gt; pensar estrategia a mitad de visita.</t>
-  </si>
-  <si>
-    <t>Pensar estrategia -&gt; entrar y saludar -&gt; mirar Bot/App -&gt; marcar GPS al final.</t>
-  </si>
-  <si>
-    <t>Marcar GPS -&gt; entrar -&gt; pensar estrategia sin mirar Bot/App y salir improvisando.</t>
-  </si>
-  <si>
-    <t>C9</t>
-  </si>
-  <si>
-    <t>Cual de estas senales en el Bot/App deberia prenderte una luz para preparar la visita con mas cuidado?</t>
-  </si>
-  <si>
-    <t>Compra siempre lo mismo con la misma frecuencia, y todo viene estable, sin cambios grandes.</t>
-  </si>
-  <si>
-    <t>Tiene pedidos regulares y un comportamiento parejo, sin cambios relevantes. Para seguir con la visita con orden.</t>
-  </si>
-  <si>
-    <t>Tiene histórico corto pero constante, sin variaciones fuertes, y mantiene el mismo patrón.</t>
-  </si>
-  <si>
-    <t>No tiene promos activas hoy, pero su compra viene normal y no hay alertas de caída.</t>
-  </si>
-  <si>
-    <t>Bajó de golpe un producto que antes rotaba bien, y se repitió en las últimas dos visitas.</t>
-  </si>
-  <si>
-    <t>C10</t>
-  </si>
-  <si>
-    <t>Cual de estas notas de pre-visita es la mas util (1 renglon) para entrar con plan?</t>
-  </si>
-  <si>
-    <t>“Repasar qué rotó la última visita y entrar con 1 pregunta corta para entender qué cambió.”</t>
-  </si>
-  <si>
-    <t>“Priorizar 2 promos que encajen con su compra habitual y mencionarlas si aparece la oportunidad.”</t>
-  </si>
-  <si>
-    <t>“Repasar caballitos X e Y y chequear si hay quiebre/stock para ajustar reposición sin inflar.”</t>
-  </si>
-  <si>
-    <t>“Entrar a escuchar primero y, según lo que diga, armar una propuesta simple en el momento.”</t>
-  </si>
-  <si>
-    <t>“Repongo X e Y (caballitos) + propongo prueba acotada para margen o ahorro de viajes hoy.” Respuestas + explicacion (por que es correcta)</t>
+    <t>3</t>
+  </si>
+  <si>
+    <t>D1</t>
+  </si>
+  <si>
+    <t>Cliente conocido. Queres una apertura que mezcle cercania y foco. Cual opcion es la mejor?</t>
+  </si>
+  <si>
+    <t>¿Qué hacés? ¿Cómo venís hoy? Reponemos lo básico y después te dejo una idea corta.</t>
+  </si>
+  <si>
+    <t>Hola Juan, soy ___ de VA Food. ¿Cómo vienen las ventas? Repongo y te dejo una mejora breve.</t>
+  </si>
+  <si>
+    <t>Entrar, mirar el celular en silencio y esperar que el cliente arranque la charla.</t>
+  </si>
+  <si>
+    <t>Che, ¿viste el partido? y dejar que la charla marque el ritmo de la visita.</t>
+  </si>
+  <si>
+    <t>Vengo con seis promos para contarte; te las digo rápido y después armamos el pedido.</t>
+  </si>
+  <si>
+    <t>D2</t>
+  </si>
+  <si>
+    <t>Cliente frio y cortante: 'Decime rapido'. Cual apertura respeta el metodo y cuida el vinculo?</t>
+  </si>
+  <si>
+    <t>“Dale, ¿qué te anoto y me voy?”. Para dejar una salida concreta.</t>
+  </si>
+  <si>
+    <t>“Buen día, soy ___ de VA Food. Te hago una sola pregunta rápida: ¿hoy te complica más vender, margen o tiempo?”.</t>
+  </si>
+  <si>
+    <t>“Si me apurás no te puedo atender”. Para ordenar el foco y avanzar.</t>
+  </si>
+  <si>
+    <t>“Vengo a hablarte de una promo, escuchá”. Para que quede corto y claro.</t>
+  </si>
+  <si>
+    <t>“Te dejo el catálogo y paso otro día”. Para ordenar el foco y avanzar.</t>
+  </si>
+  <si>
+    <t>D3</t>
+  </si>
+  <si>
+    <t>Entras y el cliente esta atendiendo a una fila. Que accion en los primeros 30 segundos es mas profesional?</t>
+  </si>
+  <si>
+    <t>Saludas, pedís permiso y avisas que vas a pasar, aprovechas que esta con clientes y te da tiempo de revisar el stock y después volves y charlas</t>
+  </si>
+  <si>
+    <t>Interrumpir igual para decirle todas las promos de entrada, aunque esté con clientes y se corte la atención.</t>
+  </si>
+  <si>
+    <t>Empezar a revisar heladeras o góndola sin decir nada, como si no estuviera, y recién después saludar.</t>
+  </si>
+  <si>
+    <t>Irte y volver sin avisar, dejando la visita colgada. Para que quede corto y claro.</t>
+  </si>
+  <si>
+    <t>Hablarle fuerte desde la puerta para que te escuche, aunque quede incómodo delante de la fila.</t>
+  </si>
+  <si>
+    <t>D4</t>
+  </si>
+  <si>
+    <t>Entrás al local para iniciar la visita con un cliente nuevo. Querés primero generar confianza y miedo a no tener acceso a mejores ofertas de otros almacenes en el barrio, si te lo permite, recién ahí entender su foco (venta, margen o tiempo). ¿Cómo abrís la conversación?</t>
+  </si>
+  <si>
+    <t>Hola, ¿cómo va? Soy ___ de VA Food. Trabajo con varios almacenes del barrio; manejo marcas fuertes y ofertas que suelen volar. ¿Te muestro opciones?</t>
+  </si>
+  <si>
+    <t>Buen día, te saluda ___ de VA Food. Para ir directo al punto: ¿hoy priorizás vender más, cuidar margen o ahorrar tiempo? Así lo armamos rápido.</t>
+  </si>
+  <si>
+    <t>Hola, soy ___, de VA Food. Primero te cuento promos y condiciones que tengo hoy; después vemos si te sirven y recién ahí hablamos de tu foco.</t>
+  </si>
+  <si>
+    <t>Buen día, acá ___ de VA Food. Estoy pasando por la zona: hagamos un mínimo para dejarte activo, y en la próxima visita vemos opciones con calma.</t>
+  </si>
+  <si>
+    <t>Hola, soy ___ de VA Food. Vengo a reordenar tu mix: decime qué se traba o no rota y qué sacarías, así cambiamos todo hoy mismo.</t>
+  </si>
+  <si>
+    <t>D5</t>
+  </si>
+  <si>
+    <t>Cual de estas aperturas NO cumple con una buena apertura de 30 segundos?</t>
+  </si>
+  <si>
+    <t>Saludo + nombre + una pregunta breve de negocio para ordenar el foco en 30 segundos.</t>
+  </si>
+  <si>
+    <t>Pregunta corta sobre cómo viene la semana y revisar reposición base antes de proponer algo puntual.</t>
+  </si>
+  <si>
+    <t>Arrancar con quejas de logística/entregas sin que el cliente lo mencione</t>
+  </si>
+  <si>
+    <t>Presentarte con nombre y decir que venís con una o dos opciones concretas, sin abrumar de entrada.</t>
+  </si>
+  <si>
+    <t>Frase cálida y profesional sin ir directo a “¿qué te anoto?”, cuidando vínculo y foco comercial.</t>
+  </si>
+  <si>
+    <t>D6</t>
+  </si>
+  <si>
+    <t>El cliente te recibe seco y dice: “Está difícil”. Querés validar sin quedarte en la queja y ubicar rápido el foco (venta vs margen). ¿Qué respondés?</t>
+  </si>
+  <si>
+    <t>Te entiendo. ¿Querés que te muestre dos opciones rápidas? Para dejar una salida concreta.</t>
+  </si>
+  <si>
+    <t>Si hoy estás así, mejor no te ofrezco nada; vuelvo otro día con más tiempo y lo vemos con calma.</t>
+  </si>
+  <si>
+    <t>Sí, viene difícil. Decime rápido qué te está frenando más hoy para ordenar la visita.</t>
+  </si>
+  <si>
+    <t>Te entiendo, está difícil. Para ubicar el foco, ¿te preocupa más que no entre gente o la ganancia que te queda?</t>
+  </si>
+  <si>
+    <t>A veces se destraba ajustando precios o armando combos; podrías subir un poco y ver si mejora.</t>
+  </si>
+  <si>
+    <t>D7</t>
+  </si>
+  <si>
+    <t>Queres una pregunta inicial que abra negocio sin interrogar. Cual opcion es mejor?</t>
+  </si>
+  <si>
+    <t>¿Cuántos empleados tenés en este turno y cómo te organizás para atender y reponer hoy?</t>
+  </si>
+  <si>
+    <t>¿Cómo venís con impuestos y costos fijos este mes; te está pegando en la ganancia del local?</t>
+  </si>
+  <si>
+    <t>¿A qué hora estás cerrando y cómo resolvés la última reposición del día cuando hay movimiento?</t>
+  </si>
+  <si>
+    <t>Si tuvieras que elegir, ¿hoy te complica más vender, cuidar el margen o el tiempo que te lleva todo?</t>
+  </si>
+  <si>
+    <t>¿Cómo ves el clima del país para el consumo y qué expectativas tenés para las próximas semanas?</t>
+  </si>
+  <si>
+    <t>D8</t>
+  </si>
+  <si>
+    <t>Cual frase muestra mejor “vengo a ayudarte” y no “vengo a vender por vender”?</t>
+  </si>
+  <si>
+    <t>“Hoy traje promos que suelen salir; si querés te cuento dos opciones rápidas para sumar algo.”</t>
+  </si>
+  <si>
+    <t>“Si hoy no querés comprar, no hay problema: vuelvo otro día y lo vemos con más tiempo.”</t>
+  </si>
+  <si>
+    <t>“Vengo a asegurar lo que rota y buscar una mejora simple según tu objetivo de hoy.”</t>
+  </si>
+  <si>
+    <t>“¿Cómo anda la familia? Contame un poco y después vemos si necesitás algo del pedido.”</t>
+  </si>
+  <si>
+    <t>“Necesito que hoy metas más cantidad para que cierre el número; después vemos el resto.”.</t>
+  </si>
+  <si>
+    <t>D9</t>
+  </si>
+  <si>
+    <t>En que momento tiene mas sentido usar una frase tipo 'Te puedo hacer una pregunta rapida?'</t>
+  </si>
+  <si>
+    <t>Antes de saludar, la decís de entrada sin pedir permiso, para apurar la visita aunque recién llegás.</t>
+  </si>
+  <si>
+    <t>Después de discutir precio y ya con tensión, la usás como freno; suena tarde y poco natural.</t>
+  </si>
+  <si>
+    <t>Después de cerrar el pedido, cuando el diagnóstico ya pasó, la pregunta no impacta en la visita.</t>
+  </si>
+  <si>
+    <t>Solo con clientes muy amigos, como si con nuevos o fríos no correspondiera pedir permiso.</t>
+  </si>
+  <si>
+    <t>Después del saludo y de reponer, para pedir permiso y diagnosticar sin meter presión.</t>
+  </si>
+  <si>
+    <t>D10</t>
+  </si>
+  <si>
+    <t>Que combinacion describe mejor una apertura completa (en orden)?</t>
+  </si>
+  <si>
+    <t>Saludo + nombre → mostrar opciones/promos disponibles → recién después hacer una pregunta de negocio.</t>
+  </si>
+  <si>
+    <t>Saludo + nombre → abrir con tema de entregas/servicio → luego hacer una pregunta de negocio.</t>
+  </si>
+  <si>
+    <t>Saludo rápido → mencionar promos puntuales → cerrar la visita sin diagnóstico ni reposición base.</t>
+  </si>
+  <si>
+    <t>Saludo + nombre → esperar que el cliente lidere la conversación → preguntar cuando haya espacio.</t>
+  </si>
+  <si>
+    <t>Saludo + nombre → pregunta corta de negocio → propósito de ayuda y reposición base antes de proponer. Respuestas + explicacion (por que es correcta)</t>
   </si>
 </sst>
 </file>
@@ -674,7 +674,7 @@
         <v>16</v>
       </c>
       <c r="I2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
@@ -703,7 +703,7 @@
         <v>23</v>
       </c>
       <c r="I3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
@@ -732,7 +732,7 @@
         <v>30</v>
       </c>
       <c r="I4" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
@@ -761,7 +761,7 @@
         <v>37</v>
       </c>
       <c r="I5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
@@ -790,7 +790,7 @@
         <v>44</v>
       </c>
       <c r="I6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
@@ -819,7 +819,7 @@
         <v>51</v>
       </c>
       <c r="I7" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
@@ -848,7 +848,7 @@
         <v>58</v>
       </c>
       <c r="I8" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
@@ -877,7 +877,7 @@
         <v>65</v>
       </c>
       <c r="I9" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">

--- a/public/Quiz.xlsx
+++ b/public/Quiz.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Micael\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52B9BBA4-10E5-45B9-BCC4-C744704C6EC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A939C47A-95CC-43AF-8A9E-D91EE4921CF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{814585D2-DACD-4865-94B7-0CB5BA22B5AF}"/>
   </bookViews>
@@ -54,217 +54,217 @@
     <t>correct</t>
   </si>
   <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>D1</t>
-  </si>
-  <si>
-    <t>Cliente conocido. Queres una apertura que mezcle cercania y foco. Cual opcion es la mejor?</t>
-  </si>
-  <si>
-    <t>¿Qué hacés? ¿Cómo venís hoy? Reponemos lo básico y después te dejo una idea corta.</t>
-  </si>
-  <si>
-    <t>Hola Juan, soy ___ de VA Food. ¿Cómo vienen las ventas? Repongo y te dejo una mejora breve.</t>
-  </si>
-  <si>
-    <t>Entrar, mirar el celular en silencio y esperar que el cliente arranque la charla.</t>
-  </si>
-  <si>
-    <t>Che, ¿viste el partido? y dejar que la charla marque el ritmo de la visita.</t>
-  </si>
-  <si>
-    <t>Vengo con seis promos para contarte; te las digo rápido y después armamos el pedido.</t>
-  </si>
-  <si>
-    <t>D2</t>
-  </si>
-  <si>
-    <t>Cliente frio y cortante: 'Decime rapido'. Cual apertura respeta el metodo y cuida el vinculo?</t>
-  </si>
-  <si>
-    <t>“Dale, ¿qué te anoto y me voy?”. Para dejar una salida concreta.</t>
-  </si>
-  <si>
-    <t>“Buen día, soy ___ de VA Food. Te hago una sola pregunta rápida: ¿hoy te complica más vender, margen o tiempo?”.</t>
-  </si>
-  <si>
-    <t>“Si me apurás no te puedo atender”. Para ordenar el foco y avanzar.</t>
-  </si>
-  <si>
-    <t>“Vengo a hablarte de una promo, escuchá”. Para que quede corto y claro.</t>
-  </si>
-  <si>
-    <t>“Te dejo el catálogo y paso otro día”. Para ordenar el foco y avanzar.</t>
-  </si>
-  <si>
-    <t>D3</t>
-  </si>
-  <si>
-    <t>Entras y el cliente esta atendiendo a una fila. Que accion en los primeros 30 segundos es mas profesional?</t>
-  </si>
-  <si>
-    <t>Saludas, pedís permiso y avisas que vas a pasar, aprovechas que esta con clientes y te da tiempo de revisar el stock y después volves y charlas</t>
-  </si>
-  <si>
-    <t>Interrumpir igual para decirle todas las promos de entrada, aunque esté con clientes y se corte la atención.</t>
-  </si>
-  <si>
-    <t>Empezar a revisar heladeras o góndola sin decir nada, como si no estuviera, y recién después saludar.</t>
-  </si>
-  <si>
-    <t>Irte y volver sin avisar, dejando la visita colgada. Para que quede corto y claro.</t>
-  </si>
-  <si>
-    <t>Hablarle fuerte desde la puerta para que te escuche, aunque quede incómodo delante de la fila.</t>
-  </si>
-  <si>
-    <t>D4</t>
-  </si>
-  <si>
-    <t>Entrás al local para iniciar la visita con un cliente nuevo. Querés primero generar confianza y miedo a no tener acceso a mejores ofertas de otros almacenes en el barrio, si te lo permite, recién ahí entender su foco (venta, margen o tiempo). ¿Cómo abrís la conversación?</t>
-  </si>
-  <si>
-    <t>Hola, ¿cómo va? Soy ___ de VA Food. Trabajo con varios almacenes del barrio; manejo marcas fuertes y ofertas que suelen volar. ¿Te muestro opciones?</t>
-  </si>
-  <si>
-    <t>Buen día, te saluda ___ de VA Food. Para ir directo al punto: ¿hoy priorizás vender más, cuidar margen o ahorrar tiempo? Así lo armamos rápido.</t>
-  </si>
-  <si>
-    <t>Hola, soy ___, de VA Food. Primero te cuento promos y condiciones que tengo hoy; después vemos si te sirven y recién ahí hablamos de tu foco.</t>
-  </si>
-  <si>
-    <t>Buen día, acá ___ de VA Food. Estoy pasando por la zona: hagamos un mínimo para dejarte activo, y en la próxima visita vemos opciones con calma.</t>
-  </si>
-  <si>
-    <t>Hola, soy ___ de VA Food. Vengo a reordenar tu mix: decime qué se traba o no rota y qué sacarías, así cambiamos todo hoy mismo.</t>
-  </si>
-  <si>
-    <t>D5</t>
-  </si>
-  <si>
-    <t>Cual de estas aperturas NO cumple con una buena apertura de 30 segundos?</t>
-  </si>
-  <si>
-    <t>Saludo + nombre + una pregunta breve de negocio para ordenar el foco en 30 segundos.</t>
-  </si>
-  <si>
-    <t>Pregunta corta sobre cómo viene la semana y revisar reposición base antes de proponer algo puntual.</t>
-  </si>
-  <si>
-    <t>Arrancar con quejas de logística/entregas sin que el cliente lo mencione</t>
-  </si>
-  <si>
-    <t>Presentarte con nombre y decir que venís con una o dos opciones concretas, sin abrumar de entrada.</t>
-  </si>
-  <si>
-    <t>Frase cálida y profesional sin ir directo a “¿qué te anoto?”, cuidando vínculo y foco comercial.</t>
-  </si>
-  <si>
-    <t>D6</t>
-  </si>
-  <si>
-    <t>El cliente te recibe seco y dice: “Está difícil”. Querés validar sin quedarte en la queja y ubicar rápido el foco (venta vs margen). ¿Qué respondés?</t>
-  </si>
-  <si>
-    <t>Te entiendo. ¿Querés que te muestre dos opciones rápidas? Para dejar una salida concreta.</t>
-  </si>
-  <si>
-    <t>Si hoy estás así, mejor no te ofrezco nada; vuelvo otro día con más tiempo y lo vemos con calma.</t>
-  </si>
-  <si>
-    <t>Sí, viene difícil. Decime rápido qué te está frenando más hoy para ordenar la visita.</t>
-  </si>
-  <si>
-    <t>Te entiendo, está difícil. Para ubicar el foco, ¿te preocupa más que no entre gente o la ganancia que te queda?</t>
-  </si>
-  <si>
-    <t>A veces se destraba ajustando precios o armando combos; podrías subir un poco y ver si mejora.</t>
-  </si>
-  <si>
-    <t>D7</t>
-  </si>
-  <si>
-    <t>Queres una pregunta inicial que abra negocio sin interrogar. Cual opcion es mejor?</t>
-  </si>
-  <si>
-    <t>¿Cuántos empleados tenés en este turno y cómo te organizás para atender y reponer hoy?</t>
-  </si>
-  <si>
-    <t>¿Cómo venís con impuestos y costos fijos este mes; te está pegando en la ganancia del local?</t>
-  </si>
-  <si>
-    <t>¿A qué hora estás cerrando y cómo resolvés la última reposición del día cuando hay movimiento?</t>
-  </si>
-  <si>
-    <t>Si tuvieras que elegir, ¿hoy te complica más vender, cuidar el margen o el tiempo que te lleva todo?</t>
-  </si>
-  <si>
-    <t>¿Cómo ves el clima del país para el consumo y qué expectativas tenés para las próximas semanas?</t>
-  </si>
-  <si>
-    <t>D8</t>
-  </si>
-  <si>
-    <t>Cual frase muestra mejor “vengo a ayudarte” y no “vengo a vender por vender”?</t>
-  </si>
-  <si>
-    <t>“Hoy traje promos que suelen salir; si querés te cuento dos opciones rápidas para sumar algo.”</t>
-  </si>
-  <si>
-    <t>“Si hoy no querés comprar, no hay problema: vuelvo otro día y lo vemos con más tiempo.”</t>
-  </si>
-  <si>
-    <t>“Vengo a asegurar lo que rota y buscar una mejora simple según tu objetivo de hoy.”</t>
-  </si>
-  <si>
-    <t>“¿Cómo anda la familia? Contame un poco y después vemos si necesitás algo del pedido.”</t>
-  </si>
-  <si>
-    <t>“Necesito que hoy metas más cantidad para que cierre el número; después vemos el resto.”.</t>
-  </si>
-  <si>
-    <t>D9</t>
-  </si>
-  <si>
-    <t>En que momento tiene mas sentido usar una frase tipo 'Te puedo hacer una pregunta rapida?'</t>
-  </si>
-  <si>
-    <t>Antes de saludar, la decís de entrada sin pedir permiso, para apurar la visita aunque recién llegás.</t>
-  </si>
-  <si>
-    <t>Después de discutir precio y ya con tensión, la usás como freno; suena tarde y poco natural.</t>
-  </si>
-  <si>
-    <t>Después de cerrar el pedido, cuando el diagnóstico ya pasó, la pregunta no impacta en la visita.</t>
-  </si>
-  <si>
-    <t>Solo con clientes muy amigos, como si con nuevos o fríos no correspondiera pedir permiso.</t>
-  </si>
-  <si>
-    <t>Después del saludo y de reponer, para pedir permiso y diagnosticar sin meter presión.</t>
-  </si>
-  <si>
-    <t>D10</t>
-  </si>
-  <si>
-    <t>Que combinacion describe mejor una apertura completa (en orden)?</t>
-  </si>
-  <si>
-    <t>Saludo + nombre → mostrar opciones/promos disponibles → recién después hacer una pregunta de negocio.</t>
-  </si>
-  <si>
-    <t>Saludo + nombre → abrir con tema de entregas/servicio → luego hacer una pregunta de negocio.</t>
-  </si>
-  <si>
-    <t>Saludo rápido → mencionar promos puntuales → cerrar la visita sin diagnóstico ni reposición base.</t>
-  </si>
-  <si>
-    <t>Saludo + nombre → esperar que el cliente lidere la conversación → preguntar cuando haya espacio.</t>
-  </si>
-  <si>
-    <t>Saludo + nombre → pregunta corta de negocio → propósito de ayuda y reposición base antes de proponer. Respuestas + explicacion (por que es correcta)</t>
+    <t>4</t>
+  </si>
+  <si>
+    <t>E1</t>
+  </si>
+  <si>
+    <t>En góndola ves un hueco de tu producto más rotador (A) y, en su lugar, un producto de otro proveedor (C). El cliente está ocupado. ¿Cuál es tu primera acción más inteligente?</t>
+  </si>
+  <si>
+    <t>Preguntar por qué está comprando C a otro proveedor antes de resolver reposición y quiebres de tus productos.</t>
+  </si>
+  <si>
+    <t>Asegurar reposición de A para no perder ventas y, con eso cubierto, abrir la conversación sobre el frente de C.</t>
+  </si>
+  <si>
+    <t>Pedirle que saque C de la góndola y te dé ese frente, sin revisar rotación ni motivo de la elección.</t>
+  </si>
+  <si>
+    <t>Dejar el quiebre de A para después y arrancar mostrando promos generales para sumar volumen hoy.</t>
+  </si>
+  <si>
+    <t>Abrir la charla por logística/entregas antes de resolver el faltante visible en góndola y su impacto.</t>
+  </si>
+  <si>
+    <t>E2</t>
+  </si>
+  <si>
+    <t>Ves un producto tuyo bien ubicado pero sin precio visible. Cual accion se alinea mejor al rol?</t>
+  </si>
+  <si>
+    <t>No decir nada: asumir que el cliente ya sabe el precio y que eso no afecta la decisión de compra.</t>
+  </si>
+  <si>
+    <t>Sugerir poner precio visible y, si corresponde, un cartel simple para facilitar la venta y la rotación.</t>
+  </si>
+  <si>
+    <t>Cambiar vos mismo el precio con una etiqueta nueva, aunque no corresponda. Para dejar una salida concreta.</t>
+  </si>
+  <si>
+    <t>Sacar el producto del frente para que no se note, y después ver si lo reubicás en otro lado.</t>
+  </si>
+  <si>
+    <t>Usar ese detalle para presionarlo a comprar más. Para ordenar el foco y avanzar.</t>
+  </si>
+  <si>
+    <t>E3</t>
+  </si>
+  <si>
+    <t>El cliente te dice: “La entrega anterior llegó tarde”. Cual respuesta te mantiene profesional y te devuelve rapido al foco comercial?</t>
+  </si>
+  <si>
+    <t>Entiendo, gracias por avisarme. Lo registro para que se corrija. Para no perder ventas hoy: ¿cómo venís de stock y reposición?</t>
+  </si>
+  <si>
+    <t>Sí, tenés razón, no vuelve a pasar; te explico rápido qué pasó y cómo se corrige.</t>
+  </si>
+  <si>
+    <t>No fue culpa mía; si tu encargado pidió tarde o el depósito se demoró, no es tema mío.</t>
+  </si>
+  <si>
+    <t>Contame bien: qué hora, quién recibió, qué remito y qué faltó, y lo vemos ahora.</t>
+  </si>
+  <si>
+    <t>Eso no lo manejo yo, yo solo vendo. Para que quede corto y claro.</t>
+  </si>
+  <si>
+    <t>E4</t>
+  </si>
+  <si>
+    <t>El Bot muestra que normalmente compra 5 cajas por semana de un producto. En heladera quedan 2 unidades. Cual propuesta de reposicion es mas ordenada?</t>
+  </si>
+  <si>
+    <t>“Veo que venís en 5 cajas por semana y hoy te quedan 2 unidades; ¿reponemos 5 para cubrir esta semana?”</t>
+  </si>
+  <si>
+    <t>“Decime qué te gustaría llevar hoy y lo armamos sobre la marcha con lo que te parezca.”</t>
+  </si>
+  <si>
+    <t>“Aprovechemos y llevemos 15 cajas así te olvidás por un tiempo y no te preocupás después.”</t>
+  </si>
+  <si>
+    <t>“Si te quedó poco, mejor no repongas por ahora y lo revisamos más adelante en otra visita.”</t>
+  </si>
+  <si>
+    <t>“Te dejo el catálogo para que lo mires y después lo vemos con más tiempo cuando estés más tranquilo.”</t>
+  </si>
+  <si>
+    <t>E5</t>
+  </si>
+  <si>
+    <t>Detectas un producto tuyo clavado (mismo nivel de stock hace semanas). Que enfoque de reposicion es mas inteligente?</t>
+  </si>
+  <si>
+    <t>“Sumemos un poco más del mismo para darle más presencia y ver si se mueve por volumen.”</t>
+  </si>
+  <si>
+    <t>“Dejémoslo como está y sigamos con el pedido habitual, sin meternos en ese producto hoy.”</t>
+  </si>
+  <si>
+    <t>“Antes de reponer, ubiquemos qué lo frena: salida, precio o ubicación, y definimos un ajuste puntual.”</t>
+  </si>
+  <si>
+    <t>“Esto lo compraste mal; así no se trabaja. La próxima pedime solo lo que rota bien.”</t>
+  </si>
+  <si>
+    <t>“Después lo vemos; por ahora sigamos con otra cosa y cerramos el pedido como siempre hoy.”</t>
+  </si>
+  <si>
+    <t>E6</t>
+  </si>
+  <si>
+    <t>Despues de asegurar reposicion, queres entender por que el cliente compra una categoria a otro proveedor. Que pregunta cuida mejor el vinculo?</t>
+  </si>
+  <si>
+    <t>¿Por qué le comprás a otro si yo también te lo puedo vender hoy mismo acá?</t>
+  </si>
+  <si>
+    <t>¿Ese proveedor te da mejor precio? Si no, te conviene comprarme a mí esta vez hoy.</t>
+  </si>
+  <si>
+    <t>¿Qué te gusta más de ese proveedor: precio, entrega o surtido, para entender tu elección mejor?</t>
+  </si>
+  <si>
+    <t>¿Qué te viene resolviendo ese proveedor en esa categoría, para ver cómo me ajusto yo también?</t>
+  </si>
+  <si>
+    <t>Si preferís, no lo hablamos ahora; seguimos con lo de siempre y cerramos tranquilo hoy acá.</t>
+  </si>
+  <si>
+    <t>E7</t>
+  </si>
+  <si>
+    <t>Ves que el precio en gondola de tu producto esta muy por encima de lo habitual del barrio. Que accion es mas alineada al foco en venta?</t>
+  </si>
+  <si>
+    <t>“Lo dejo como está; el precio lo maneja el local y no me meto con eso hoy.”</t>
+  </si>
+  <si>
+    <t>“Lo bajo yo ahora mismo para que se venda, y después vemos el resto cuando haya tiempo.”</t>
+  </si>
+  <si>
+    <t>“Ese precio está mal; así no vas a vender” y lo marco como error sin preguntar contexto.</t>
+  </si>
+  <si>
+    <t>“Llevemos más cantidad igual para compensar” y después vemos si se mueve con volumen ahí.</t>
+  </si>
+  <si>
+    <t>“¿A cuánto lo estás vendiendo hoy?” para entender el punto de partida antes de proponer ajuste.</t>
+  </si>
+  <si>
+    <t>E8</t>
+  </si>
+  <si>
+    <t>Que tema NO deberias abrir vos durante la recorrida si el cliente no lo menciona?</t>
+  </si>
+  <si>
+    <t>Faltantes de stock o quiebres en góndola que puedan estar frenando ventas hoy.</t>
+  </si>
+  <si>
+    <t>Productos que no rotan o están clavados y ocupan espacio sin aportar margen.</t>
+  </si>
+  <si>
+    <t>Precio visible en góndola si está fuera de rango para el barrio o la rotación.</t>
+  </si>
+  <si>
+    <t>Problemas de logística o entregas como tema principal, sin señal previa del cliente.</t>
+  </si>
+  <si>
+    <t>Productos de otros proveedores en la categoría y cómo conviven con tus frentes actuales.</t>
+  </si>
+  <si>
+    <t>E9</t>
+  </si>
+  <si>
+    <t>Tenes 3 minutos para recorrer. Que chequeo te da mas informacion para armar un pedido base con sentido?</t>
+  </si>
+  <si>
+    <t>Chequear faltantes y quiebres de lo que más rota para armar la reposición base del local hoy.</t>
+  </si>
+  <si>
+    <t>Detectar qué productos están clavados y qué conviene pausar, sin mirar el resto del recorrido.</t>
+  </si>
+  <si>
+    <t>Revisar precios visibles en góndola para ver desvíos, sin mirar rotación ni faltantes del local.</t>
+  </si>
+  <si>
+    <t>Abrir por entregas y servicio para ver reclamos, antes de revisar stock en punto de venta.</t>
+  </si>
+  <si>
+    <t>Mirar el triángulo: vendido, no vendido y competencia, para armar base y una oportunidad real.</t>
+  </si>
+  <si>
+    <t>E10</t>
+  </si>
+  <si>
+    <t>Cual frase propone reposicion base sin marear al cliente?</t>
+  </si>
+  <si>
+    <t>Si querés, decime qué te falta hoy y lo armamos rápido con eso.</t>
+  </si>
+  <si>
+    <t>Te muestro algunas opciones y vos vas eligiendo de a poco lo que prefieras.</t>
+  </si>
+  <si>
+    <t>Veo que de X estás corto; para cubrir la semana te propongo reponer 5 cajas hoy.</t>
+  </si>
+  <si>
+    <t>Hoy te recomiendo sumar algunos lanzamientos que están saliendo y probarlos esta semana.</t>
+  </si>
+  <si>
+    <t>Necesito que hoy el pedido sea más grande para que me cierre bien la visita. Respuestas + explicacion (por que es correcta)</t>
   </si>
 </sst>
 </file>
@@ -848,7 +848,7 @@
         <v>58</v>
       </c>
       <c r="I8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
@@ -877,7 +877,7 @@
         <v>65</v>
       </c>
       <c r="I9" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
@@ -935,7 +935,7 @@
         <v>79</v>
       </c>
       <c r="I11" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/public/Quiz.xlsx
+++ b/public/Quiz.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Micael\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A939C47A-95CC-43AF-8A9E-D91EE4921CF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95BA0806-DE1A-4FFB-AE87-22F8680EC88C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{814585D2-DACD-4865-94B7-0CB5BA22B5AF}"/>
   </bookViews>
@@ -54,217 +54,217 @@
     <t>correct</t>
   </si>
   <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>E1</t>
-  </si>
-  <si>
-    <t>En góndola ves un hueco de tu producto más rotador (A) y, en su lugar, un producto de otro proveedor (C). El cliente está ocupado. ¿Cuál es tu primera acción más inteligente?</t>
-  </si>
-  <si>
-    <t>Preguntar por qué está comprando C a otro proveedor antes de resolver reposición y quiebres de tus productos.</t>
-  </si>
-  <si>
-    <t>Asegurar reposición de A para no perder ventas y, con eso cubierto, abrir la conversación sobre el frente de C.</t>
-  </si>
-  <si>
-    <t>Pedirle que saque C de la góndola y te dé ese frente, sin revisar rotación ni motivo de la elección.</t>
-  </si>
-  <si>
-    <t>Dejar el quiebre de A para después y arrancar mostrando promos generales para sumar volumen hoy.</t>
-  </si>
-  <si>
-    <t>Abrir la charla por logística/entregas antes de resolver el faltante visible en góndola y su impacto.</t>
-  </si>
-  <si>
-    <t>E2</t>
-  </si>
-  <si>
-    <t>Ves un producto tuyo bien ubicado pero sin precio visible. Cual accion se alinea mejor al rol?</t>
-  </si>
-  <si>
-    <t>No decir nada: asumir que el cliente ya sabe el precio y que eso no afecta la decisión de compra.</t>
-  </si>
-  <si>
-    <t>Sugerir poner precio visible y, si corresponde, un cartel simple para facilitar la venta y la rotación.</t>
-  </si>
-  <si>
-    <t>Cambiar vos mismo el precio con una etiqueta nueva, aunque no corresponda. Para dejar una salida concreta.</t>
-  </si>
-  <si>
-    <t>Sacar el producto del frente para que no se note, y después ver si lo reubicás en otro lado.</t>
-  </si>
-  <si>
-    <t>Usar ese detalle para presionarlo a comprar más. Para ordenar el foco y avanzar.</t>
-  </si>
-  <si>
-    <t>E3</t>
-  </si>
-  <si>
-    <t>El cliente te dice: “La entrega anterior llegó tarde”. Cual respuesta te mantiene profesional y te devuelve rapido al foco comercial?</t>
-  </si>
-  <si>
-    <t>Entiendo, gracias por avisarme. Lo registro para que se corrija. Para no perder ventas hoy: ¿cómo venís de stock y reposición?</t>
-  </si>
-  <si>
-    <t>Sí, tenés razón, no vuelve a pasar; te explico rápido qué pasó y cómo se corrige.</t>
-  </si>
-  <si>
-    <t>No fue culpa mía; si tu encargado pidió tarde o el depósito se demoró, no es tema mío.</t>
-  </si>
-  <si>
-    <t>Contame bien: qué hora, quién recibió, qué remito y qué faltó, y lo vemos ahora.</t>
-  </si>
-  <si>
-    <t>Eso no lo manejo yo, yo solo vendo. Para que quede corto y claro.</t>
-  </si>
-  <si>
-    <t>E4</t>
-  </si>
-  <si>
-    <t>El Bot muestra que normalmente compra 5 cajas por semana de un producto. En heladera quedan 2 unidades. Cual propuesta de reposicion es mas ordenada?</t>
-  </si>
-  <si>
-    <t>“Veo que venís en 5 cajas por semana y hoy te quedan 2 unidades; ¿reponemos 5 para cubrir esta semana?”</t>
-  </si>
-  <si>
-    <t>“Decime qué te gustaría llevar hoy y lo armamos sobre la marcha con lo que te parezca.”</t>
-  </si>
-  <si>
-    <t>“Aprovechemos y llevemos 15 cajas así te olvidás por un tiempo y no te preocupás después.”</t>
-  </si>
-  <si>
-    <t>“Si te quedó poco, mejor no repongas por ahora y lo revisamos más adelante en otra visita.”</t>
-  </si>
-  <si>
-    <t>“Te dejo el catálogo para que lo mires y después lo vemos con más tiempo cuando estés más tranquilo.”</t>
-  </si>
-  <si>
-    <t>E5</t>
-  </si>
-  <si>
-    <t>Detectas un producto tuyo clavado (mismo nivel de stock hace semanas). Que enfoque de reposicion es mas inteligente?</t>
-  </si>
-  <si>
-    <t>“Sumemos un poco más del mismo para darle más presencia y ver si se mueve por volumen.”</t>
-  </si>
-  <si>
-    <t>“Dejémoslo como está y sigamos con el pedido habitual, sin meternos en ese producto hoy.”</t>
-  </si>
-  <si>
-    <t>“Antes de reponer, ubiquemos qué lo frena: salida, precio o ubicación, y definimos un ajuste puntual.”</t>
-  </si>
-  <si>
-    <t>“Esto lo compraste mal; así no se trabaja. La próxima pedime solo lo que rota bien.”</t>
-  </si>
-  <si>
-    <t>“Después lo vemos; por ahora sigamos con otra cosa y cerramos el pedido como siempre hoy.”</t>
-  </si>
-  <si>
-    <t>E6</t>
-  </si>
-  <si>
-    <t>Despues de asegurar reposicion, queres entender por que el cliente compra una categoria a otro proveedor. Que pregunta cuida mejor el vinculo?</t>
-  </si>
-  <si>
-    <t>¿Por qué le comprás a otro si yo también te lo puedo vender hoy mismo acá?</t>
-  </si>
-  <si>
-    <t>¿Ese proveedor te da mejor precio? Si no, te conviene comprarme a mí esta vez hoy.</t>
-  </si>
-  <si>
-    <t>¿Qué te gusta más de ese proveedor: precio, entrega o surtido, para entender tu elección mejor?</t>
-  </si>
-  <si>
-    <t>¿Qué te viene resolviendo ese proveedor en esa categoría, para ver cómo me ajusto yo también?</t>
-  </si>
-  <si>
-    <t>Si preferís, no lo hablamos ahora; seguimos con lo de siempre y cerramos tranquilo hoy acá.</t>
-  </si>
-  <si>
-    <t>E7</t>
-  </si>
-  <si>
-    <t>Ves que el precio en gondola de tu producto esta muy por encima de lo habitual del barrio. Que accion es mas alineada al foco en venta?</t>
-  </si>
-  <si>
-    <t>“Lo dejo como está; el precio lo maneja el local y no me meto con eso hoy.”</t>
-  </si>
-  <si>
-    <t>“Lo bajo yo ahora mismo para que se venda, y después vemos el resto cuando haya tiempo.”</t>
-  </si>
-  <si>
-    <t>“Ese precio está mal; así no vas a vender” y lo marco como error sin preguntar contexto.</t>
-  </si>
-  <si>
-    <t>“Llevemos más cantidad igual para compensar” y después vemos si se mueve con volumen ahí.</t>
-  </si>
-  <si>
-    <t>“¿A cuánto lo estás vendiendo hoy?” para entender el punto de partida antes de proponer ajuste.</t>
-  </si>
-  <si>
-    <t>E8</t>
-  </si>
-  <si>
-    <t>Que tema NO deberias abrir vos durante la recorrida si el cliente no lo menciona?</t>
-  </si>
-  <si>
-    <t>Faltantes de stock o quiebres en góndola que puedan estar frenando ventas hoy.</t>
-  </si>
-  <si>
-    <t>Productos que no rotan o están clavados y ocupan espacio sin aportar margen.</t>
-  </si>
-  <si>
-    <t>Precio visible en góndola si está fuera de rango para el barrio o la rotación.</t>
-  </si>
-  <si>
-    <t>Problemas de logística o entregas como tema principal, sin señal previa del cliente.</t>
-  </si>
-  <si>
-    <t>Productos de otros proveedores en la categoría y cómo conviven con tus frentes actuales.</t>
-  </si>
-  <si>
-    <t>E9</t>
-  </si>
-  <si>
-    <t>Tenes 3 minutos para recorrer. Que chequeo te da mas informacion para armar un pedido base con sentido?</t>
-  </si>
-  <si>
-    <t>Chequear faltantes y quiebres de lo que más rota para armar la reposición base del local hoy.</t>
-  </si>
-  <si>
-    <t>Detectar qué productos están clavados y qué conviene pausar, sin mirar el resto del recorrido.</t>
-  </si>
-  <si>
-    <t>Revisar precios visibles en góndola para ver desvíos, sin mirar rotación ni faltantes del local.</t>
-  </si>
-  <si>
-    <t>Abrir por entregas y servicio para ver reclamos, antes de revisar stock en punto de venta.</t>
-  </si>
-  <si>
-    <t>Mirar el triángulo: vendido, no vendido y competencia, para armar base y una oportunidad real.</t>
-  </si>
-  <si>
-    <t>E10</t>
-  </si>
-  <si>
-    <t>Cual frase propone reposicion base sin marear al cliente?</t>
-  </si>
-  <si>
-    <t>Si querés, decime qué te falta hoy y lo armamos rápido con eso.</t>
-  </si>
-  <si>
-    <t>Te muestro algunas opciones y vos vas eligiendo de a poco lo que prefieras.</t>
-  </si>
-  <si>
-    <t>Veo que de X estás corto; para cubrir la semana te propongo reponer 5 cajas hoy.</t>
-  </si>
-  <si>
-    <t>Hoy te recomiendo sumar algunos lanzamientos que están saliendo y probarlos esta semana.</t>
-  </si>
-  <si>
-    <t>Necesito que hoy el pedido sea más grande para que me cierre bien la visita. Respuestas + explicacion (por que es correcta)</t>
+    <t>1</t>
+  </si>
+  <si>
+    <t>B1</t>
+  </si>
+  <si>
+    <t>El cliente te dice apenas entras: 'Hoy estoy a mil. Anotame lo de siempre y listo'. Tenes 2 minutos reales. Que harías para sostener el vinculo y actuar como asesor sin alargar?</t>
+  </si>
+  <si>
+    <t>“Dale, te anoto lo de siempre y no te robo tiempo”; cargás el habitual tal cual, sin relevar góndola/heladera ni validar faltantes para no incomodarlo.</t>
+  </si>
+  <si>
+    <t>“Para no errarle, necesito 3–4 preguntas”; abrís diagnóstico completo, aunque esté apurado, y seguís con el diagnóstico igual. Para no meter presión ni discutir.</t>
+  </si>
+  <si>
+    <t>“Ya que estás a mil, te confirmo rápido entregas y servicio”; metés logística para mostrar cuidado, y te enfocás en entregas y servicio.</t>
+  </si>
+  <si>
+    <t>“Perfecto, voy con la reposición base y te hago una sola rápida”; sumás 1 pregunta de negocio o una mini prueba (1 SKU) y cerrás sin estirar.</t>
+  </si>
+  <si>
+    <t>“Entiendo, pero así no puedo asesorarte”; marcás límite, sugerís reprogramar y cortás la visita, y proponés volver en otro horario.</t>
+  </si>
+  <si>
+    <t>B2</t>
+  </si>
+  <si>
+    <t>Tenes que entrenar a un preventista nuevo. Cual frase describe mejor el objetivo del rol en ruta?</t>
+  </si>
+  <si>
+    <t>Mi trabajo es pasar, preguntar qué necesita y cargar exactamente lo que el cliente me pida.</t>
+  </si>
+  <si>
+    <t>Mi trabajo es hablar de ofertas todo el tiempo, y que el cliente termine comprando.</t>
+  </si>
+  <si>
+    <t>Mi trabajo es evitar faltantes que le hagan perder ventas y ayudarlo a vender más o ganar más según su problema.</t>
+  </si>
+  <si>
+    <t>Mi trabajo es discutir precio en cada visita para ganar la negociación.</t>
+  </si>
+  <si>
+    <t>Mi trabajo es visitar la mayor cantidad posible, incluso sin pedido.</t>
+  </si>
+  <si>
+    <t>B3</t>
+  </si>
+  <si>
+    <t>Salis de una visita sin pedido porque el cliente estaba indeciso. Cual resultado minimo te conviene buscar antes de irte para que la visita no quede 'en el aire'?</t>
+  </si>
+  <si>
+    <t>cerrás con un “la próxima lo vemos” y te vas. Para no meter presión ni discutir.</t>
+  </si>
+  <si>
+    <t>Un avance concreto: prueba chica, cambio de exhibición o compromiso específico para la próxima (qué, cuánto y cuándo).</t>
+  </si>
+  <si>
+    <t>Una discusión de precio para que entienda tu punto y se vaya pensando que, al final, no estabas tan caro.</t>
+  </si>
+  <si>
+    <t>Que te firme un papel donde diga que no va a comprarle a la competencia, así te quedás “cubierto” en la zona.</t>
+  </si>
+  <si>
+    <t>Irte rápido para no incomodar, cortar la charla y volver otro día cuando esté de mejor humor.</t>
+  </si>
+  <si>
+    <t>B4</t>
+  </si>
+  <si>
+    <t>El cliente te dice: 'No tengo tiempo para charlar'. Cual respuesta muestra mejor tu rol y cuida el vinculo?</t>
+  </si>
+  <si>
+    <t>Entonces decime rápido qué querés y listo, así no te demoro más.</t>
+  </si>
+  <si>
+    <t>Te entiendo: vamos hacerlo rápido, te hago una pregunta para ayudarte mejor. Hoy te complica más vender, ganar margen o el tiempo?</t>
+  </si>
+  <si>
+    <t>Ok, te dejo el catálogo y vuelvo otro día, cuando estés más tranquilo.</t>
+  </si>
+  <si>
+    <t>Si no charlamos, no te puedo vender nada, y así no pierdo el tiempo.</t>
+  </si>
+  <si>
+    <t>antes contame lo de la entrega anterior, así entiendo qué pasó y después vemos el pedido.</t>
+  </si>
+  <si>
+    <t>B5</t>
+  </si>
+  <si>
+    <t>Cual acción al salir del local te acerca más a ser consistente visita a visita?</t>
+  </si>
+  <si>
+    <t>Anotar el monto final del pedido y cerrar la visita, sin agregar comentarios.</t>
+  </si>
+  <si>
+    <t>No anotar nada, confiar en la memoria y repasarlo luego antes de volver.</t>
+  </si>
+  <si>
+    <t>Registrar breve reposición, trabas y objetivo del cliente, y definir un próximo paso simple.</t>
+  </si>
+  <si>
+    <t>Mandar un audio al grupo con lo observado y el cierre de la visita.</t>
+  </si>
+  <si>
+    <t>Guardar una foto del frente del local, sin registrar qué se conversó adentro hoy.</t>
+  </si>
+  <si>
+    <t>B6</t>
+  </si>
+  <si>
+    <t>El cliente suele ir al mayorista y se queja de cansancio. Como preventista asesor, cual enfoque tiene más sentido?</t>
+  </si>
+  <si>
+    <t>Sugerirle que cambie de rubro si el trabajo lo está cansando demasiado.</t>
+  </si>
+  <si>
+    <t>Ofrecerle una promo puntual para ver si así se anima a comprar algo hoy.</t>
+  </si>
+  <si>
+    <t>Pedirle que compre el doble para que no tenga que volver al mayorista por un tiempo.</t>
+  </si>
+  <si>
+    <t>Proponer un mix para cubrir días fuertes y reducir viajes, con cantidades cuidadas para evitar sobrestock.</t>
+  </si>
+  <si>
+    <t>Cerrar la visita por hoy y dejar agendado un regreso con foco en revisar reposición y necesidades</t>
+  </si>
+  <si>
+    <t>B7</t>
+  </si>
+  <si>
+    <t>Un preventista dice: 'Mi trabajo termina cuando cargo el pedido'. Cual respuesta corrige mejor esa idea?</t>
+  </si>
+  <si>
+    <t>No: también incluye preparar la visita, recorrer, proponer y registrar lo que pasó para mejorar la próxima.</t>
+  </si>
+  <si>
+    <t>Sí, lo importante es cargar rápido y salir. Para ordenar el foco y avanzar.</t>
+  </si>
+  <si>
+    <t>No, termina cuando retirás el pago del cliente y te asegurás que quede todo cobrado, sin excepciones.</t>
+  </si>
+  <si>
+    <t>No, termina cuando revisás todas las entregas del mes y controlás cada detalle de logística y reparto.</t>
+  </si>
+  <si>
+    <t>No, termina cuando el cliente te recomienda en redes y te etiqueta. Para dejar una salida concreta.</t>
+  </si>
+  <si>
+    <t>B8</t>
+  </si>
+  <si>
+    <t>Cliente con poco espacio: 'No me entra nada mas'. Que respuesta muestra rol asesor y criterio comercial?</t>
+  </si>
+  <si>
+    <t>Revisar qué no rota y ocupa lugar; proponer sacar eso y probar productos chicos, de alta rotación, en cantidades cuidadas.</t>
+  </si>
+  <si>
+    <t>Pedirle que lleve tres cajas más igual, confiando en que “después se acomoda” el espacio.</t>
+  </si>
+  <si>
+    <t>Aceptar el “no entra” y no ofrecer nada más hoy, cerrando la visita sin explorar alternativas.</t>
+  </si>
+  <si>
+    <t>Pedirle un rincón y cargarle el depósito para aprovechar la visita, sin validar capacidad real de espacio.</t>
+  </si>
+  <si>
+    <t>Dejar el tema como problema del cliente y seguir vendiendo sin aportar una alternativa concreta.</t>
+  </si>
+  <si>
+    <t>B9</t>
+  </si>
+  <si>
+    <t>Ves que el cliente compra una categoría de tu portfolio a otro proveedor. Que secuencia es mas profesional?</t>
+  </si>
+  <si>
+    <t>Confrontar de entrada: “¿por qué me comprás a mí y a otro?”, y esperar respuesta.</t>
+  </si>
+  <si>
+    <t>Ignorarlo: si compra a otro no hay nada que hacer, y seguís como siempre.</t>
+  </si>
+  <si>
+    <t>Criticar al otro proveedor para que cambie. Para ordenar el foco y avanzar.</t>
+  </si>
+  <si>
+    <t>Ofrecer un descuento grande para “ganar” la compra. Para dejar una salida concreta.</t>
+  </si>
+  <si>
+    <t>Asegurar reposición de lo que rota y después preguntar con curiosidad qué valora ahí (precio, presentación o entrega).</t>
+  </si>
+  <si>
+    <t>B10</t>
+  </si>
+  <si>
+    <t>Elegis el flujo de visita mas completo y ordenado para un preventista de VA Food.</t>
+  </si>
+  <si>
+    <t>Saludo, pedir el pedido y cerrar la visita, pasando rápido al siguiente cliente hoy.</t>
+  </si>
+  <si>
+    <t>Ir directo a reposición, saludar después y cerrar con preguntas de negocio.</t>
+  </si>
+  <si>
+    <t>Arrancar con promos generales, luego reposición, después saludar y cierre con monto final</t>
+  </si>
+  <si>
+    <t>Hacer charla personal extensa, tomar pedido y cerrar la visita con monto final.</t>
+  </si>
+  <si>
+    <t>Preparación, saludo con pregunta de negocio, reposición base, propuesta alineada y cierre con monto final. Respuestas + explicacion (por que es correcta)</t>
   </si>
 </sst>
 </file>
@@ -674,7 +674,7 @@
         <v>16</v>
       </c>
       <c r="I2" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
@@ -703,7 +703,7 @@
         <v>23</v>
       </c>
       <c r="I3" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
@@ -732,7 +732,7 @@
         <v>30</v>
       </c>
       <c r="I4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
@@ -761,7 +761,7 @@
         <v>37</v>
       </c>
       <c r="I5" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
@@ -848,7 +848,7 @@
         <v>58</v>
       </c>
       <c r="I8" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
@@ -877,7 +877,7 @@
         <v>65</v>
       </c>
       <c r="I9" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
@@ -935,7 +935,7 @@
         <v>79</v>
       </c>
       <c r="I11" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/public/Quiz.xlsx
+++ b/public/Quiz.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Micael\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95BA0806-DE1A-4FFB-AE87-22F8680EC88C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24F4D271-5812-424E-B3FD-B65FC6E2B224}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{814585D2-DACD-4865-94B7-0CB5BA22B5AF}"/>
   </bookViews>
@@ -54,217 +54,217 @@
     <t>correct</t>
   </si>
   <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>B1</t>
-  </si>
-  <si>
-    <t>El cliente te dice apenas entras: 'Hoy estoy a mil. Anotame lo de siempre y listo'. Tenes 2 minutos reales. Que harías para sostener el vinculo y actuar como asesor sin alargar?</t>
-  </si>
-  <si>
-    <t>“Dale, te anoto lo de siempre y no te robo tiempo”; cargás el habitual tal cual, sin relevar góndola/heladera ni validar faltantes para no incomodarlo.</t>
-  </si>
-  <si>
-    <t>“Para no errarle, necesito 3–4 preguntas”; abrís diagnóstico completo, aunque esté apurado, y seguís con el diagnóstico igual. Para no meter presión ni discutir.</t>
-  </si>
-  <si>
-    <t>“Ya que estás a mil, te confirmo rápido entregas y servicio”; metés logística para mostrar cuidado, y te enfocás en entregas y servicio.</t>
-  </si>
-  <si>
-    <t>“Perfecto, voy con la reposición base y te hago una sola rápida”; sumás 1 pregunta de negocio o una mini prueba (1 SKU) y cerrás sin estirar.</t>
-  </si>
-  <si>
-    <t>“Entiendo, pero así no puedo asesorarte”; marcás límite, sugerís reprogramar y cortás la visita, y proponés volver en otro horario.</t>
-  </si>
-  <si>
-    <t>B2</t>
-  </si>
-  <si>
-    <t>Tenes que entrenar a un preventista nuevo. Cual frase describe mejor el objetivo del rol en ruta?</t>
-  </si>
-  <si>
-    <t>Mi trabajo es pasar, preguntar qué necesita y cargar exactamente lo que el cliente me pida.</t>
-  </si>
-  <si>
-    <t>Mi trabajo es hablar de ofertas todo el tiempo, y que el cliente termine comprando.</t>
-  </si>
-  <si>
-    <t>Mi trabajo es evitar faltantes que le hagan perder ventas y ayudarlo a vender más o ganar más según su problema.</t>
-  </si>
-  <si>
-    <t>Mi trabajo es discutir precio en cada visita para ganar la negociación.</t>
-  </si>
-  <si>
-    <t>Mi trabajo es visitar la mayor cantidad posible, incluso sin pedido.</t>
-  </si>
-  <si>
-    <t>B3</t>
-  </si>
-  <si>
-    <t>Salis de una visita sin pedido porque el cliente estaba indeciso. Cual resultado minimo te conviene buscar antes de irte para que la visita no quede 'en el aire'?</t>
-  </si>
-  <si>
-    <t>cerrás con un “la próxima lo vemos” y te vas. Para no meter presión ni discutir.</t>
-  </si>
-  <si>
-    <t>Un avance concreto: prueba chica, cambio de exhibición o compromiso específico para la próxima (qué, cuánto y cuándo).</t>
-  </si>
-  <si>
-    <t>Una discusión de precio para que entienda tu punto y se vaya pensando que, al final, no estabas tan caro.</t>
-  </si>
-  <si>
-    <t>Que te firme un papel donde diga que no va a comprarle a la competencia, así te quedás “cubierto” en la zona.</t>
-  </si>
-  <si>
-    <t>Irte rápido para no incomodar, cortar la charla y volver otro día cuando esté de mejor humor.</t>
-  </si>
-  <si>
-    <t>B4</t>
-  </si>
-  <si>
-    <t>El cliente te dice: 'No tengo tiempo para charlar'. Cual respuesta muestra mejor tu rol y cuida el vinculo?</t>
-  </si>
-  <si>
-    <t>Entonces decime rápido qué querés y listo, así no te demoro más.</t>
-  </si>
-  <si>
-    <t>Te entiendo: vamos hacerlo rápido, te hago una pregunta para ayudarte mejor. Hoy te complica más vender, ganar margen o el tiempo?</t>
-  </si>
-  <si>
-    <t>Ok, te dejo el catálogo y vuelvo otro día, cuando estés más tranquilo.</t>
-  </si>
-  <si>
-    <t>Si no charlamos, no te puedo vender nada, y así no pierdo el tiempo.</t>
-  </si>
-  <si>
-    <t>antes contame lo de la entrega anterior, así entiendo qué pasó y después vemos el pedido.</t>
-  </si>
-  <si>
-    <t>B5</t>
-  </si>
-  <si>
-    <t>Cual acción al salir del local te acerca más a ser consistente visita a visita?</t>
-  </si>
-  <si>
-    <t>Anotar el monto final del pedido y cerrar la visita, sin agregar comentarios.</t>
-  </si>
-  <si>
-    <t>No anotar nada, confiar en la memoria y repasarlo luego antes de volver.</t>
-  </si>
-  <si>
-    <t>Registrar breve reposición, trabas y objetivo del cliente, y definir un próximo paso simple.</t>
-  </si>
-  <si>
-    <t>Mandar un audio al grupo con lo observado y el cierre de la visita.</t>
-  </si>
-  <si>
-    <t>Guardar una foto del frente del local, sin registrar qué se conversó adentro hoy.</t>
-  </si>
-  <si>
-    <t>B6</t>
-  </si>
-  <si>
-    <t>El cliente suele ir al mayorista y se queja de cansancio. Como preventista asesor, cual enfoque tiene más sentido?</t>
-  </si>
-  <si>
-    <t>Sugerirle que cambie de rubro si el trabajo lo está cansando demasiado.</t>
-  </si>
-  <si>
-    <t>Ofrecerle una promo puntual para ver si así se anima a comprar algo hoy.</t>
-  </si>
-  <si>
-    <t>Pedirle que compre el doble para que no tenga que volver al mayorista por un tiempo.</t>
-  </si>
-  <si>
-    <t>Proponer un mix para cubrir días fuertes y reducir viajes, con cantidades cuidadas para evitar sobrestock.</t>
-  </si>
-  <si>
-    <t>Cerrar la visita por hoy y dejar agendado un regreso con foco en revisar reposición y necesidades</t>
-  </si>
-  <si>
-    <t>B7</t>
-  </si>
-  <si>
-    <t>Un preventista dice: 'Mi trabajo termina cuando cargo el pedido'. Cual respuesta corrige mejor esa idea?</t>
-  </si>
-  <si>
-    <t>No: también incluye preparar la visita, recorrer, proponer y registrar lo que pasó para mejorar la próxima.</t>
-  </si>
-  <si>
-    <t>Sí, lo importante es cargar rápido y salir. Para ordenar el foco y avanzar.</t>
-  </si>
-  <si>
-    <t>No, termina cuando retirás el pago del cliente y te asegurás que quede todo cobrado, sin excepciones.</t>
-  </si>
-  <si>
-    <t>No, termina cuando revisás todas las entregas del mes y controlás cada detalle de logística y reparto.</t>
-  </si>
-  <si>
-    <t>No, termina cuando el cliente te recomienda en redes y te etiqueta. Para dejar una salida concreta.</t>
-  </si>
-  <si>
-    <t>B8</t>
-  </si>
-  <si>
-    <t>Cliente con poco espacio: 'No me entra nada mas'. Que respuesta muestra rol asesor y criterio comercial?</t>
-  </si>
-  <si>
-    <t>Revisar qué no rota y ocupa lugar; proponer sacar eso y probar productos chicos, de alta rotación, en cantidades cuidadas.</t>
-  </si>
-  <si>
-    <t>Pedirle que lleve tres cajas más igual, confiando en que “después se acomoda” el espacio.</t>
-  </si>
-  <si>
-    <t>Aceptar el “no entra” y no ofrecer nada más hoy, cerrando la visita sin explorar alternativas.</t>
-  </si>
-  <si>
-    <t>Pedirle un rincón y cargarle el depósito para aprovechar la visita, sin validar capacidad real de espacio.</t>
-  </si>
-  <si>
-    <t>Dejar el tema como problema del cliente y seguir vendiendo sin aportar una alternativa concreta.</t>
-  </si>
-  <si>
-    <t>B9</t>
-  </si>
-  <si>
-    <t>Ves que el cliente compra una categoría de tu portfolio a otro proveedor. Que secuencia es mas profesional?</t>
-  </si>
-  <si>
-    <t>Confrontar de entrada: “¿por qué me comprás a mí y a otro?”, y esperar respuesta.</t>
-  </si>
-  <si>
-    <t>Ignorarlo: si compra a otro no hay nada que hacer, y seguís como siempre.</t>
-  </si>
-  <si>
-    <t>Criticar al otro proveedor para que cambie. Para ordenar el foco y avanzar.</t>
-  </si>
-  <si>
-    <t>Ofrecer un descuento grande para “ganar” la compra. Para dejar una salida concreta.</t>
-  </si>
-  <si>
-    <t>Asegurar reposición de lo que rota y después preguntar con curiosidad qué valora ahí (precio, presentación o entrega).</t>
-  </si>
-  <si>
-    <t>B10</t>
-  </si>
-  <si>
-    <t>Elegis el flujo de visita mas completo y ordenado para un preventista de VA Food.</t>
-  </si>
-  <si>
-    <t>Saludo, pedir el pedido y cerrar la visita, pasando rápido al siguiente cliente hoy.</t>
-  </si>
-  <si>
-    <t>Ir directo a reposición, saludar después y cerrar con preguntas de negocio.</t>
-  </si>
-  <si>
-    <t>Arrancar con promos generales, luego reposición, después saludar y cierre con monto final</t>
-  </si>
-  <si>
-    <t>Hacer charla personal extensa, tomar pedido y cerrar la visita con monto final.</t>
-  </si>
-  <si>
-    <t>Preparación, saludo con pregunta de negocio, reposición base, propuesta alineada y cierre con monto final. Respuestas + explicacion (por que es correcta)</t>
+    <t>3</t>
+  </si>
+  <si>
+    <t>D1</t>
+  </si>
+  <si>
+    <t>Cliente conocido. Queres una apertura que mezcle cercania y foco. Cual opcion es la mejor?</t>
+  </si>
+  <si>
+    <t>¿Qué hacés? ¿Cómo venís hoy? Reponemos lo básico y después te dejo una idea corta.</t>
+  </si>
+  <si>
+    <t>Hola Juan, soy ___ de VA Food. ¿Cómo vienen las ventas? Repongo y te dejo una mejora breve.</t>
+  </si>
+  <si>
+    <t>Entrar, mirar el celular en silencio y esperar que el cliente arranque la charla.</t>
+  </si>
+  <si>
+    <t>Che, ¿viste el partido? y dejar que la charla marque el ritmo de la visita.</t>
+  </si>
+  <si>
+    <t>Vengo con seis promos para contarte; te las digo rápido y después armamos el pedido.</t>
+  </si>
+  <si>
+    <t>D2</t>
+  </si>
+  <si>
+    <t>Cliente frio y cortante: 'Decime rapido'. Cual apertura respeta el metodo y cuida el vinculo?</t>
+  </si>
+  <si>
+    <t>“Dale, ¿qué te anoto y me voy?”. Para dejar una salida concreta.</t>
+  </si>
+  <si>
+    <t>“Buen día, soy ___ de VA Food. Te hago una sola pregunta rápida: ¿hoy te complica más vender, margen o tiempo?”.</t>
+  </si>
+  <si>
+    <t>“Si me apurás no te puedo atender”. Para ordenar el foco y avanzar.</t>
+  </si>
+  <si>
+    <t>“Vengo a hablarte de una promo, escuchá”. Para que quede corto y claro.</t>
+  </si>
+  <si>
+    <t>“Te dejo el catálogo y paso otro día”. Para ordenar el foco y avanzar.</t>
+  </si>
+  <si>
+    <t>D3</t>
+  </si>
+  <si>
+    <t>Entras y el cliente esta atendiendo a una fila. Que accion en los primeros 30 segundos es mas profesional?</t>
+  </si>
+  <si>
+    <t>Saludas, pedís permiso y avisas que vas a pasar, aprovechas que esta con clientes y te da tiempo de revisar el stock y después volves y charlas</t>
+  </si>
+  <si>
+    <t>Interrumpir igual para decirle todas las promos de entrada, aunque esté con clientes y se corte la atención.</t>
+  </si>
+  <si>
+    <t>Empezar a revisar heladeras o góndola sin decir nada, como si no estuviera, y recién después saludar.</t>
+  </si>
+  <si>
+    <t>Irte y volver sin avisar, dejando la visita colgada. Para que quede corto y claro.</t>
+  </si>
+  <si>
+    <t>Hablarle fuerte desde la puerta para que te escuche, aunque quede incómodo delante de la fila.</t>
+  </si>
+  <si>
+    <t>D4</t>
+  </si>
+  <si>
+    <t>Entrás al local para iniciar la visita con un cliente nuevo. Querés primero generar confianza y miedo a no tener acceso a mejores ofertas de otros almacenes en el barrio, si te lo permite, recién ahí entender su foco (venta, margen o tiempo). ¿Cómo abrís la conversación?</t>
+  </si>
+  <si>
+    <t>Hola, ¿cómo va? Soy ___ de VA Food. Trabajo con varios almacenes del barrio; manejo marcas fuertes y ofertas que suelen volar. ¿Te muestro opciones?</t>
+  </si>
+  <si>
+    <t>Buen día, te saluda ___ de VA Food. Para ir directo al punto: ¿hoy priorizás vender más, cuidar margen o ahorrar tiempo? Así lo armamos rápido.</t>
+  </si>
+  <si>
+    <t>Hola, soy ___, de VA Food. Primero te cuento promos y condiciones que tengo hoy; después vemos si te sirven y recién ahí hablamos de tu foco.</t>
+  </si>
+  <si>
+    <t>Buen día, acá ___ de VA Food. Estoy pasando por la zona: hagamos un mínimo para dejarte activo, y en la próxima visita vemos opciones con calma.</t>
+  </si>
+  <si>
+    <t>Hola, soy ___ de VA Food. Vengo a reordenar tu mix: decime qué se traba o no rota y qué sacarías, así cambiamos todo hoy mismo.</t>
+  </si>
+  <si>
+    <t>D5</t>
+  </si>
+  <si>
+    <t>Cual de estas aperturas NO cumple con una buena apertura de 30 segundos?</t>
+  </si>
+  <si>
+    <t>Saludo + nombre + una pregunta breve de negocio para ordenar el foco en 30 segundos.</t>
+  </si>
+  <si>
+    <t>Pregunta corta sobre cómo viene la semana y revisar reposición base antes de proponer algo puntual.</t>
+  </si>
+  <si>
+    <t>Arrancar con quejas de logística/entregas sin que el cliente lo mencione</t>
+  </si>
+  <si>
+    <t>Presentarte con nombre y decir que venís con una o dos opciones concretas, sin abrumar de entrada.</t>
+  </si>
+  <si>
+    <t>Frase cálida y profesional sin ir directo a “¿qué te anoto?”, cuidando vínculo y foco comercial.</t>
+  </si>
+  <si>
+    <t>D6</t>
+  </si>
+  <si>
+    <t>El cliente te recibe seco y dice: “Está difícil”. Querés validar sin quedarte en la queja y ubicar rápido el foco (venta vs margen). ¿Qué respondés?</t>
+  </si>
+  <si>
+    <t>Te entiendo. ¿Querés que te muestre dos opciones rápidas? Para dejar una salida concreta.</t>
+  </si>
+  <si>
+    <t>Si hoy estás así, mejor no te ofrezco nada; vuelvo otro día con más tiempo y lo vemos con calma.</t>
+  </si>
+  <si>
+    <t>Sí, viene difícil. Decime rápido qué te está frenando más hoy para ordenar la visita.</t>
+  </si>
+  <si>
+    <t>Te entiendo, está difícil. Para ubicar el foco, ¿te preocupa más que no entre gente o la ganancia que te queda?</t>
+  </si>
+  <si>
+    <t>A veces se destraba ajustando precios o armando combos; podrías subir un poco y ver si mejora.</t>
+  </si>
+  <si>
+    <t>D7</t>
+  </si>
+  <si>
+    <t>Queres una pregunta inicial que abra negocio sin interrogar. Cual opcion es mejor?</t>
+  </si>
+  <si>
+    <t>¿Cuántos empleados tenés en este turno y cómo te organizás para atender y reponer hoy?</t>
+  </si>
+  <si>
+    <t>¿Cómo venís con impuestos y costos fijos este mes; te está pegando en la ganancia del local?</t>
+  </si>
+  <si>
+    <t>¿A qué hora estás cerrando y cómo resolvés la última reposición del día cuando hay movimiento?</t>
+  </si>
+  <si>
+    <t>Si tuvieras que elegir, ¿hoy te complica más vender, cuidar el margen o el tiempo que te lleva todo?</t>
+  </si>
+  <si>
+    <t>¿Cómo ves el clima del país para el consumo y qué expectativas tenés para las próximas semanas?</t>
+  </si>
+  <si>
+    <t>D8</t>
+  </si>
+  <si>
+    <t>Cual frase muestra mejor “vengo a ayudarte” y no “vengo a vender por vender”?</t>
+  </si>
+  <si>
+    <t>“Hoy traje promos que suelen salir; si querés te cuento dos opciones rápidas para sumar algo.”</t>
+  </si>
+  <si>
+    <t>“Si hoy no querés comprar, no hay problema: vuelvo otro día y lo vemos con más tiempo.”</t>
+  </si>
+  <si>
+    <t>“Vengo a asegurar lo que rota y buscar una mejora simple según tu objetivo de hoy.”</t>
+  </si>
+  <si>
+    <t>“¿Cómo anda la familia? Contame un poco y después vemos si necesitás algo del pedido.”</t>
+  </si>
+  <si>
+    <t>“Necesito que hoy metas más cantidad para que cierre el número; después vemos el resto.”.</t>
+  </si>
+  <si>
+    <t>D9</t>
+  </si>
+  <si>
+    <t>En que momento tiene mas sentido usar una frase tipo 'Te puedo hacer una pregunta rapida?'</t>
+  </si>
+  <si>
+    <t>Antes de saludar, la decís de entrada sin pedir permiso, para apurar la visita aunque recién llegás.</t>
+  </si>
+  <si>
+    <t>Después de discutir precio y ya con tensión, la usás como freno; suena tarde y poco natural.</t>
+  </si>
+  <si>
+    <t>Después de cerrar el pedido, cuando el diagnóstico ya pasó, la pregunta no impacta en la visita.</t>
+  </si>
+  <si>
+    <t>Solo con clientes muy amigos, como si con nuevos o fríos no correspondiera pedir permiso.</t>
+  </si>
+  <si>
+    <t>Después del saludo y de reponer, para pedir permiso y diagnosticar sin meter presión.</t>
+  </si>
+  <si>
+    <t>D10</t>
+  </si>
+  <si>
+    <t>Que combinacion describe mejor una apertura completa (en orden)?</t>
+  </si>
+  <si>
+    <t>Saludo + nombre → mostrar opciones/promos disponibles → recién después hacer una pregunta de negocio.</t>
+  </si>
+  <si>
+    <t>Saludo + nombre → abrir con tema de entregas/servicio → luego hacer una pregunta de negocio.</t>
+  </si>
+  <si>
+    <t>Saludo rápido → mencionar promos puntuales → cerrar la visita sin diagnóstico ni reposición base.</t>
+  </si>
+  <si>
+    <t>Saludo + nombre → esperar que el cliente lidere la conversación → preguntar cuando haya espacio.</t>
+  </si>
+  <si>
+    <t>Saludo + nombre → pregunta corta de negocio → propósito de ayuda y reposición base antes de proponer. Respuestas + explicacion (por que es correcta)</t>
   </si>
 </sst>
 </file>
@@ -674,7 +674,7 @@
         <v>16</v>
       </c>
       <c r="I2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
@@ -703,7 +703,7 @@
         <v>23</v>
       </c>
       <c r="I3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
@@ -732,7 +732,7 @@
         <v>30</v>
       </c>
       <c r="I4" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
@@ -761,7 +761,7 @@
         <v>37</v>
       </c>
       <c r="I5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
@@ -848,7 +848,7 @@
         <v>58</v>
       </c>
       <c r="I8" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
@@ -877,7 +877,7 @@
         <v>65</v>
       </c>
       <c r="I9" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">

--- a/public/Quiz.xlsx
+++ b/public/Quiz.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Micael\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24F4D271-5812-424E-B3FD-B65FC6E2B224}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ABEC81E-5795-40DE-ABF5-4469D2D3CF44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{814585D2-DACD-4865-94B7-0CB5BA22B5AF}"/>
   </bookViews>
@@ -54,217 +54,217 @@
     <t>correct</t>
   </si>
   <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>D1</t>
-  </si>
-  <si>
-    <t>Cliente conocido. Queres una apertura que mezcle cercania y foco. Cual opcion es la mejor?</t>
-  </si>
-  <si>
-    <t>¿Qué hacés? ¿Cómo venís hoy? Reponemos lo básico y después te dejo una idea corta.</t>
-  </si>
-  <si>
-    <t>Hola Juan, soy ___ de VA Food. ¿Cómo vienen las ventas? Repongo y te dejo una mejora breve.</t>
-  </si>
-  <si>
-    <t>Entrar, mirar el celular en silencio y esperar que el cliente arranque la charla.</t>
-  </si>
-  <si>
-    <t>Che, ¿viste el partido? y dejar que la charla marque el ritmo de la visita.</t>
-  </si>
-  <si>
-    <t>Vengo con seis promos para contarte; te las digo rápido y después armamos el pedido.</t>
-  </si>
-  <si>
-    <t>D2</t>
-  </si>
-  <si>
-    <t>Cliente frio y cortante: 'Decime rapido'. Cual apertura respeta el metodo y cuida el vinculo?</t>
-  </si>
-  <si>
-    <t>“Dale, ¿qué te anoto y me voy?”. Para dejar una salida concreta.</t>
-  </si>
-  <si>
-    <t>“Buen día, soy ___ de VA Food. Te hago una sola pregunta rápida: ¿hoy te complica más vender, margen o tiempo?”.</t>
-  </si>
-  <si>
-    <t>“Si me apurás no te puedo atender”. Para ordenar el foco y avanzar.</t>
-  </si>
-  <si>
-    <t>“Vengo a hablarte de una promo, escuchá”. Para que quede corto y claro.</t>
-  </si>
-  <si>
-    <t>“Te dejo el catálogo y paso otro día”. Para ordenar el foco y avanzar.</t>
-  </si>
-  <si>
-    <t>D3</t>
-  </si>
-  <si>
-    <t>Entras y el cliente esta atendiendo a una fila. Que accion en los primeros 30 segundos es mas profesional?</t>
-  </si>
-  <si>
-    <t>Saludas, pedís permiso y avisas que vas a pasar, aprovechas que esta con clientes y te da tiempo de revisar el stock y después volves y charlas</t>
-  </si>
-  <si>
-    <t>Interrumpir igual para decirle todas las promos de entrada, aunque esté con clientes y se corte la atención.</t>
-  </si>
-  <si>
-    <t>Empezar a revisar heladeras o góndola sin decir nada, como si no estuviera, y recién después saludar.</t>
-  </si>
-  <si>
-    <t>Irte y volver sin avisar, dejando la visita colgada. Para que quede corto y claro.</t>
-  </si>
-  <si>
-    <t>Hablarle fuerte desde la puerta para que te escuche, aunque quede incómodo delante de la fila.</t>
-  </si>
-  <si>
-    <t>D4</t>
-  </si>
-  <si>
-    <t>Entrás al local para iniciar la visita con un cliente nuevo. Querés primero generar confianza y miedo a no tener acceso a mejores ofertas de otros almacenes en el barrio, si te lo permite, recién ahí entender su foco (venta, margen o tiempo). ¿Cómo abrís la conversación?</t>
-  </si>
-  <si>
-    <t>Hola, ¿cómo va? Soy ___ de VA Food. Trabajo con varios almacenes del barrio; manejo marcas fuertes y ofertas que suelen volar. ¿Te muestro opciones?</t>
-  </si>
-  <si>
-    <t>Buen día, te saluda ___ de VA Food. Para ir directo al punto: ¿hoy priorizás vender más, cuidar margen o ahorrar tiempo? Así lo armamos rápido.</t>
-  </si>
-  <si>
-    <t>Hola, soy ___, de VA Food. Primero te cuento promos y condiciones que tengo hoy; después vemos si te sirven y recién ahí hablamos de tu foco.</t>
-  </si>
-  <si>
-    <t>Buen día, acá ___ de VA Food. Estoy pasando por la zona: hagamos un mínimo para dejarte activo, y en la próxima visita vemos opciones con calma.</t>
-  </si>
-  <si>
-    <t>Hola, soy ___ de VA Food. Vengo a reordenar tu mix: decime qué se traba o no rota y qué sacarías, así cambiamos todo hoy mismo.</t>
-  </si>
-  <si>
-    <t>D5</t>
-  </si>
-  <si>
-    <t>Cual de estas aperturas NO cumple con una buena apertura de 30 segundos?</t>
-  </si>
-  <si>
-    <t>Saludo + nombre + una pregunta breve de negocio para ordenar el foco en 30 segundos.</t>
-  </si>
-  <si>
-    <t>Pregunta corta sobre cómo viene la semana y revisar reposición base antes de proponer algo puntual.</t>
-  </si>
-  <si>
-    <t>Arrancar con quejas de logística/entregas sin que el cliente lo mencione</t>
-  </si>
-  <si>
-    <t>Presentarte con nombre y decir que venís con una o dos opciones concretas, sin abrumar de entrada.</t>
-  </si>
-  <si>
-    <t>Frase cálida y profesional sin ir directo a “¿qué te anoto?”, cuidando vínculo y foco comercial.</t>
-  </si>
-  <si>
-    <t>D6</t>
-  </si>
-  <si>
-    <t>El cliente te recibe seco y dice: “Está difícil”. Querés validar sin quedarte en la queja y ubicar rápido el foco (venta vs margen). ¿Qué respondés?</t>
-  </si>
-  <si>
-    <t>Te entiendo. ¿Querés que te muestre dos opciones rápidas? Para dejar una salida concreta.</t>
-  </si>
-  <si>
-    <t>Si hoy estás así, mejor no te ofrezco nada; vuelvo otro día con más tiempo y lo vemos con calma.</t>
-  </si>
-  <si>
-    <t>Sí, viene difícil. Decime rápido qué te está frenando más hoy para ordenar la visita.</t>
-  </si>
-  <si>
-    <t>Te entiendo, está difícil. Para ubicar el foco, ¿te preocupa más que no entre gente o la ganancia que te queda?</t>
-  </si>
-  <si>
-    <t>A veces se destraba ajustando precios o armando combos; podrías subir un poco y ver si mejora.</t>
-  </si>
-  <si>
-    <t>D7</t>
-  </si>
-  <si>
-    <t>Queres una pregunta inicial que abra negocio sin interrogar. Cual opcion es mejor?</t>
-  </si>
-  <si>
-    <t>¿Cuántos empleados tenés en este turno y cómo te organizás para atender y reponer hoy?</t>
-  </si>
-  <si>
-    <t>¿Cómo venís con impuestos y costos fijos este mes; te está pegando en la ganancia del local?</t>
-  </si>
-  <si>
-    <t>¿A qué hora estás cerrando y cómo resolvés la última reposición del día cuando hay movimiento?</t>
-  </si>
-  <si>
-    <t>Si tuvieras que elegir, ¿hoy te complica más vender, cuidar el margen o el tiempo que te lleva todo?</t>
-  </si>
-  <si>
-    <t>¿Cómo ves el clima del país para el consumo y qué expectativas tenés para las próximas semanas?</t>
-  </si>
-  <si>
-    <t>D8</t>
-  </si>
-  <si>
-    <t>Cual frase muestra mejor “vengo a ayudarte” y no “vengo a vender por vender”?</t>
-  </si>
-  <si>
-    <t>“Hoy traje promos que suelen salir; si querés te cuento dos opciones rápidas para sumar algo.”</t>
-  </si>
-  <si>
-    <t>“Si hoy no querés comprar, no hay problema: vuelvo otro día y lo vemos con más tiempo.”</t>
-  </si>
-  <si>
-    <t>“Vengo a asegurar lo que rota y buscar una mejora simple según tu objetivo de hoy.”</t>
-  </si>
-  <si>
-    <t>“¿Cómo anda la familia? Contame un poco y después vemos si necesitás algo del pedido.”</t>
-  </si>
-  <si>
-    <t>“Necesito que hoy metas más cantidad para que cierre el número; después vemos el resto.”.</t>
-  </si>
-  <si>
-    <t>D9</t>
-  </si>
-  <si>
-    <t>En que momento tiene mas sentido usar una frase tipo 'Te puedo hacer una pregunta rapida?'</t>
-  </si>
-  <si>
-    <t>Antes de saludar, la decís de entrada sin pedir permiso, para apurar la visita aunque recién llegás.</t>
-  </si>
-  <si>
-    <t>Después de discutir precio y ya con tensión, la usás como freno; suena tarde y poco natural.</t>
-  </si>
-  <si>
-    <t>Después de cerrar el pedido, cuando el diagnóstico ya pasó, la pregunta no impacta en la visita.</t>
-  </si>
-  <si>
-    <t>Solo con clientes muy amigos, como si con nuevos o fríos no correspondiera pedir permiso.</t>
-  </si>
-  <si>
-    <t>Después del saludo y de reponer, para pedir permiso y diagnosticar sin meter presión.</t>
-  </si>
-  <si>
-    <t>D10</t>
-  </si>
-  <si>
-    <t>Que combinacion describe mejor una apertura completa (en orden)?</t>
-  </si>
-  <si>
-    <t>Saludo + nombre → mostrar opciones/promos disponibles → recién después hacer una pregunta de negocio.</t>
-  </si>
-  <si>
-    <t>Saludo + nombre → abrir con tema de entregas/servicio → luego hacer una pregunta de negocio.</t>
-  </si>
-  <si>
-    <t>Saludo rápido → mencionar promos puntuales → cerrar la visita sin diagnóstico ni reposición base.</t>
-  </si>
-  <si>
-    <t>Saludo + nombre → esperar que el cliente lidere la conversación → preguntar cuando haya espacio.</t>
-  </si>
-  <si>
-    <t>Saludo + nombre → pregunta corta de negocio → propósito de ayuda y reposición base antes de proponer. Respuestas + explicacion (por que es correcta)</t>
+    <t>4</t>
+  </si>
+  <si>
+    <t>E1</t>
+  </si>
+  <si>
+    <t>En góndola ves un hueco de tu producto más rotador (A) y, en su lugar, un producto de otro proveedor (C). El cliente está ocupado. ¿Cuál es tu primera acción más inteligente?</t>
+  </si>
+  <si>
+    <t>Preguntar por qué está comprando C a otro proveedor antes de resolver reposición y quiebres de tus productos.</t>
+  </si>
+  <si>
+    <t>Asegurar reposición de A para no perder ventas y, con eso cubierto, abrir la conversación sobre el frente de C.</t>
+  </si>
+  <si>
+    <t>Pedirle que saque C de la góndola y te dé ese frente, sin revisar rotación ni motivo de la elección.</t>
+  </si>
+  <si>
+    <t>Dejar el quiebre de A para después y arrancar mostrando promos generales para sumar volumen hoy.</t>
+  </si>
+  <si>
+    <t>Abrir la charla por logística/entregas antes de resolver el faltante visible en góndola y su impacto.</t>
+  </si>
+  <si>
+    <t>E2</t>
+  </si>
+  <si>
+    <t>Ves un producto tuyo bien ubicado pero sin precio visible. Cual accion se alinea mejor al rol?</t>
+  </si>
+  <si>
+    <t>No decir nada: asumir que el cliente ya sabe el precio y que eso no afecta la decisión de compra.</t>
+  </si>
+  <si>
+    <t>Sugerir poner precio visible y, si corresponde, un cartel simple para facilitar la venta y la rotación.</t>
+  </si>
+  <si>
+    <t>Cambiar vos mismo el precio con una etiqueta nueva, aunque no corresponda. Para dejar una salida concreta.</t>
+  </si>
+  <si>
+    <t>Sacar el producto del frente para que no se note, y después ver si lo reubicás en otro lado.</t>
+  </si>
+  <si>
+    <t>Usar ese detalle para presionarlo a comprar más. Para ordenar el foco y avanzar.</t>
+  </si>
+  <si>
+    <t>E3</t>
+  </si>
+  <si>
+    <t>El cliente te dice: “La entrega anterior llegó tarde”. Cual respuesta te mantiene profesional y te devuelve rapido al foco comercial?</t>
+  </si>
+  <si>
+    <t>Entiendo, gracias por avisarme. Lo registro para que se corrija. Para no perder ventas hoy: ¿cómo venís de stock y reposición?</t>
+  </si>
+  <si>
+    <t>Sí, tenés razón, no vuelve a pasar; te explico rápido qué pasó y cómo se corrige.</t>
+  </si>
+  <si>
+    <t>No fue culpa mía; si tu encargado pidió tarde o el depósito se demoró, no es tema mío.</t>
+  </si>
+  <si>
+    <t>Contame bien: qué hora, quién recibió, qué remito y qué faltó, y lo vemos ahora.</t>
+  </si>
+  <si>
+    <t>Eso no lo manejo yo, yo solo vendo. Para que quede corto y claro.</t>
+  </si>
+  <si>
+    <t>E4</t>
+  </si>
+  <si>
+    <t>El Bot muestra que normalmente compra 5 cajas por semana de un producto. En heladera quedan 2 unidades. Cual propuesta de reposicion es mas ordenada?</t>
+  </si>
+  <si>
+    <t>“Veo que venís en 5 cajas por semana y hoy te quedan 2 unidades; ¿reponemos 5 para cubrir esta semana?”</t>
+  </si>
+  <si>
+    <t>“Decime qué te gustaría llevar hoy y lo armamos sobre la marcha con lo que te parezca.”</t>
+  </si>
+  <si>
+    <t>“Aprovechemos y llevemos 15 cajas así te olvidás por un tiempo y no te preocupás después.”</t>
+  </si>
+  <si>
+    <t>“Si te quedó poco, mejor no repongas por ahora y lo revisamos más adelante en otra visita.”</t>
+  </si>
+  <si>
+    <t>“Te dejo el catálogo para que lo mires y después lo vemos con más tiempo cuando estés más tranquilo.”</t>
+  </si>
+  <si>
+    <t>E5</t>
+  </si>
+  <si>
+    <t>Detectas un producto tuyo clavado (mismo nivel de stock hace semanas). Que enfoque de reposicion es mas inteligente?</t>
+  </si>
+  <si>
+    <t>“Sumemos un poco más del mismo para darle más presencia y ver si se mueve por volumen.”</t>
+  </si>
+  <si>
+    <t>“Dejémoslo como está y sigamos con el pedido habitual, sin meternos en ese producto hoy.”</t>
+  </si>
+  <si>
+    <t>“Antes de reponer, ubiquemos qué lo frena: salida, precio o ubicación, y definimos un ajuste puntual.”</t>
+  </si>
+  <si>
+    <t>“Esto lo compraste mal; así no se trabaja. La próxima pedime solo lo que rota bien.”</t>
+  </si>
+  <si>
+    <t>“Después lo vemos; por ahora sigamos con otra cosa y cerramos el pedido como siempre hoy.”</t>
+  </si>
+  <si>
+    <t>E6</t>
+  </si>
+  <si>
+    <t>Despues de asegurar reposicion, queres entender por que el cliente compra una categoria a otro proveedor. Que pregunta cuida mejor el vinculo?</t>
+  </si>
+  <si>
+    <t>¿Por qué le comprás a otro si yo también te lo puedo vender hoy mismo acá?</t>
+  </si>
+  <si>
+    <t>¿Ese proveedor te da mejor precio? Si no, te conviene comprarme a mí esta vez hoy.</t>
+  </si>
+  <si>
+    <t>¿Qué te gusta más de ese proveedor: precio, entrega o surtido, para entender tu elección mejor?</t>
+  </si>
+  <si>
+    <t>¿Qué te viene resolviendo ese proveedor en esa categoría, para ver cómo me ajusto yo también?</t>
+  </si>
+  <si>
+    <t>Si preferís, no lo hablamos ahora; seguimos con lo de siempre y cerramos tranquilo hoy acá.</t>
+  </si>
+  <si>
+    <t>E7</t>
+  </si>
+  <si>
+    <t>Ves que el precio en gondola de tu producto esta muy por encima de lo habitual del barrio. Que accion es mas alineada al foco en venta?</t>
+  </si>
+  <si>
+    <t>“Lo dejo como está; el precio lo maneja el local y no me meto con eso hoy.”</t>
+  </si>
+  <si>
+    <t>“Lo bajo yo ahora mismo para que se venda, y después vemos el resto cuando haya tiempo.”</t>
+  </si>
+  <si>
+    <t>“Ese precio está mal; así no vas a vender” y lo marco como error sin preguntar contexto.</t>
+  </si>
+  <si>
+    <t>“Llevemos más cantidad igual para compensar” y después vemos si se mueve con volumen ahí.</t>
+  </si>
+  <si>
+    <t>“¿A cuánto lo estás vendiendo hoy?” para entender el punto de partida antes de proponer ajuste.</t>
+  </si>
+  <si>
+    <t>E8</t>
+  </si>
+  <si>
+    <t>Que tema NO deberias abrir vos durante la recorrida si el cliente no lo menciona?</t>
+  </si>
+  <si>
+    <t>Faltantes de stock o quiebres en góndola que puedan estar frenando ventas hoy.</t>
+  </si>
+  <si>
+    <t>Productos que no rotan o están clavados y ocupan espacio sin aportar margen.</t>
+  </si>
+  <si>
+    <t>Precio visible en góndola si está fuera de rango para el barrio o la rotación.</t>
+  </si>
+  <si>
+    <t>Problemas de logística o entregas como tema principal, sin señal previa del cliente.</t>
+  </si>
+  <si>
+    <t>Productos de otros proveedores en la categoría y cómo conviven con tus frentes actuales.</t>
+  </si>
+  <si>
+    <t>E9</t>
+  </si>
+  <si>
+    <t>Tenes 3 minutos para recorrer. Que chequeo te da mas informacion para armar un pedido base con sentido?</t>
+  </si>
+  <si>
+    <t>Chequear faltantes y quiebres de lo que más rota para armar la reposición base del local hoy.</t>
+  </si>
+  <si>
+    <t>Detectar qué productos están clavados y qué conviene pausar, sin mirar el resto del recorrido.</t>
+  </si>
+  <si>
+    <t>Revisar precios visibles en góndola para ver desvíos, sin mirar rotación ni faltantes del local.</t>
+  </si>
+  <si>
+    <t>Abrir por entregas y servicio para ver reclamos, antes de revisar stock en punto de venta.</t>
+  </si>
+  <si>
+    <t>Mirar el triángulo: vendido, no vendido y competencia, para armar base y una oportunidad real.</t>
+  </si>
+  <si>
+    <t>E10</t>
+  </si>
+  <si>
+    <t>Cual frase propone reposicion base sin marear al cliente?</t>
+  </si>
+  <si>
+    <t>Si querés, decime qué te falta hoy y lo armamos rápido con eso.</t>
+  </si>
+  <si>
+    <t>Te muestro algunas opciones y vos vas eligiendo de a poco lo que prefieras.</t>
+  </si>
+  <si>
+    <t>Veo que de X estás corto; para cubrir la semana te propongo reponer 5 cajas hoy.</t>
+  </si>
+  <si>
+    <t>Hoy te recomiendo sumar algunos lanzamientos que están saliendo y probarlos esta semana.</t>
+  </si>
+  <si>
+    <t>Necesito que hoy el pedido sea más grande para que me cierre bien la visita. Respuestas + explicacion (por que es correcta)</t>
   </si>
 </sst>
 </file>
@@ -848,7 +848,7 @@
         <v>58</v>
       </c>
       <c r="I8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
@@ -877,7 +877,7 @@
         <v>65</v>
       </c>
       <c r="I9" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
@@ -935,7 +935,7 @@
         <v>79</v>
       </c>
       <c r="I11" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/public/Quiz.xlsx
+++ b/public/Quiz.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Micael\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ABEC81E-5795-40DE-ABF5-4469D2D3CF44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75C27BCB-B185-4261-935A-381E51165394}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{814585D2-DACD-4865-94B7-0CB5BA22B5AF}"/>
   </bookViews>
@@ -54,217 +54,217 @@
     <t>correct</t>
   </si>
   <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>E1</t>
-  </si>
-  <si>
-    <t>En góndola ves un hueco de tu producto más rotador (A) y, en su lugar, un producto de otro proveedor (C). El cliente está ocupado. ¿Cuál es tu primera acción más inteligente?</t>
-  </si>
-  <si>
-    <t>Preguntar por qué está comprando C a otro proveedor antes de resolver reposición y quiebres de tus productos.</t>
-  </si>
-  <si>
-    <t>Asegurar reposición de A para no perder ventas y, con eso cubierto, abrir la conversación sobre el frente de C.</t>
-  </si>
-  <si>
-    <t>Pedirle que saque C de la góndola y te dé ese frente, sin revisar rotación ni motivo de la elección.</t>
-  </si>
-  <si>
-    <t>Dejar el quiebre de A para después y arrancar mostrando promos generales para sumar volumen hoy.</t>
-  </si>
-  <si>
-    <t>Abrir la charla por logística/entregas antes de resolver el faltante visible en góndola y su impacto.</t>
-  </si>
-  <si>
-    <t>E2</t>
-  </si>
-  <si>
-    <t>Ves un producto tuyo bien ubicado pero sin precio visible. Cual accion se alinea mejor al rol?</t>
-  </si>
-  <si>
-    <t>No decir nada: asumir que el cliente ya sabe el precio y que eso no afecta la decisión de compra.</t>
-  </si>
-  <si>
-    <t>Sugerir poner precio visible y, si corresponde, un cartel simple para facilitar la venta y la rotación.</t>
-  </si>
-  <si>
-    <t>Cambiar vos mismo el precio con una etiqueta nueva, aunque no corresponda. Para dejar una salida concreta.</t>
-  </si>
-  <si>
-    <t>Sacar el producto del frente para que no se note, y después ver si lo reubicás en otro lado.</t>
-  </si>
-  <si>
-    <t>Usar ese detalle para presionarlo a comprar más. Para ordenar el foco y avanzar.</t>
-  </si>
-  <si>
-    <t>E3</t>
-  </si>
-  <si>
-    <t>El cliente te dice: “La entrega anterior llegó tarde”. Cual respuesta te mantiene profesional y te devuelve rapido al foco comercial?</t>
-  </si>
-  <si>
-    <t>Entiendo, gracias por avisarme. Lo registro para que se corrija. Para no perder ventas hoy: ¿cómo venís de stock y reposición?</t>
-  </si>
-  <si>
-    <t>Sí, tenés razón, no vuelve a pasar; te explico rápido qué pasó y cómo se corrige.</t>
-  </si>
-  <si>
-    <t>No fue culpa mía; si tu encargado pidió tarde o el depósito se demoró, no es tema mío.</t>
-  </si>
-  <si>
-    <t>Contame bien: qué hora, quién recibió, qué remito y qué faltó, y lo vemos ahora.</t>
-  </si>
-  <si>
-    <t>Eso no lo manejo yo, yo solo vendo. Para que quede corto y claro.</t>
-  </si>
-  <si>
-    <t>E4</t>
-  </si>
-  <si>
-    <t>El Bot muestra que normalmente compra 5 cajas por semana de un producto. En heladera quedan 2 unidades. Cual propuesta de reposicion es mas ordenada?</t>
-  </si>
-  <si>
-    <t>“Veo que venís en 5 cajas por semana y hoy te quedan 2 unidades; ¿reponemos 5 para cubrir esta semana?”</t>
-  </si>
-  <si>
-    <t>“Decime qué te gustaría llevar hoy y lo armamos sobre la marcha con lo que te parezca.”</t>
-  </si>
-  <si>
-    <t>“Aprovechemos y llevemos 15 cajas así te olvidás por un tiempo y no te preocupás después.”</t>
-  </si>
-  <si>
-    <t>“Si te quedó poco, mejor no repongas por ahora y lo revisamos más adelante en otra visita.”</t>
-  </si>
-  <si>
-    <t>“Te dejo el catálogo para que lo mires y después lo vemos con más tiempo cuando estés más tranquilo.”</t>
-  </si>
-  <si>
-    <t>E5</t>
-  </si>
-  <si>
-    <t>Detectas un producto tuyo clavado (mismo nivel de stock hace semanas). Que enfoque de reposicion es mas inteligente?</t>
-  </si>
-  <si>
-    <t>“Sumemos un poco más del mismo para darle más presencia y ver si se mueve por volumen.”</t>
-  </si>
-  <si>
-    <t>“Dejémoslo como está y sigamos con el pedido habitual, sin meternos en ese producto hoy.”</t>
-  </si>
-  <si>
-    <t>“Antes de reponer, ubiquemos qué lo frena: salida, precio o ubicación, y definimos un ajuste puntual.”</t>
-  </si>
-  <si>
-    <t>“Esto lo compraste mal; así no se trabaja. La próxima pedime solo lo que rota bien.”</t>
-  </si>
-  <si>
-    <t>“Después lo vemos; por ahora sigamos con otra cosa y cerramos el pedido como siempre hoy.”</t>
-  </si>
-  <si>
-    <t>E6</t>
-  </si>
-  <si>
-    <t>Despues de asegurar reposicion, queres entender por que el cliente compra una categoria a otro proveedor. Que pregunta cuida mejor el vinculo?</t>
-  </si>
-  <si>
-    <t>¿Por qué le comprás a otro si yo también te lo puedo vender hoy mismo acá?</t>
-  </si>
-  <si>
-    <t>¿Ese proveedor te da mejor precio? Si no, te conviene comprarme a mí esta vez hoy.</t>
-  </si>
-  <si>
-    <t>¿Qué te gusta más de ese proveedor: precio, entrega o surtido, para entender tu elección mejor?</t>
-  </si>
-  <si>
-    <t>¿Qué te viene resolviendo ese proveedor en esa categoría, para ver cómo me ajusto yo también?</t>
-  </si>
-  <si>
-    <t>Si preferís, no lo hablamos ahora; seguimos con lo de siempre y cerramos tranquilo hoy acá.</t>
-  </si>
-  <si>
-    <t>E7</t>
-  </si>
-  <si>
-    <t>Ves que el precio en gondola de tu producto esta muy por encima de lo habitual del barrio. Que accion es mas alineada al foco en venta?</t>
-  </si>
-  <si>
-    <t>“Lo dejo como está; el precio lo maneja el local y no me meto con eso hoy.”</t>
-  </si>
-  <si>
-    <t>“Lo bajo yo ahora mismo para que se venda, y después vemos el resto cuando haya tiempo.”</t>
-  </si>
-  <si>
-    <t>“Ese precio está mal; así no vas a vender” y lo marco como error sin preguntar contexto.</t>
-  </si>
-  <si>
-    <t>“Llevemos más cantidad igual para compensar” y después vemos si se mueve con volumen ahí.</t>
-  </si>
-  <si>
-    <t>“¿A cuánto lo estás vendiendo hoy?” para entender el punto de partida antes de proponer ajuste.</t>
-  </si>
-  <si>
-    <t>E8</t>
-  </si>
-  <si>
-    <t>Que tema NO deberias abrir vos durante la recorrida si el cliente no lo menciona?</t>
-  </si>
-  <si>
-    <t>Faltantes de stock o quiebres en góndola que puedan estar frenando ventas hoy.</t>
-  </si>
-  <si>
-    <t>Productos que no rotan o están clavados y ocupan espacio sin aportar margen.</t>
-  </si>
-  <si>
-    <t>Precio visible en góndola si está fuera de rango para el barrio o la rotación.</t>
-  </si>
-  <si>
-    <t>Problemas de logística o entregas como tema principal, sin señal previa del cliente.</t>
-  </si>
-  <si>
-    <t>Productos de otros proveedores en la categoría y cómo conviven con tus frentes actuales.</t>
-  </si>
-  <si>
-    <t>E9</t>
-  </si>
-  <si>
-    <t>Tenes 3 minutos para recorrer. Que chequeo te da mas informacion para armar un pedido base con sentido?</t>
-  </si>
-  <si>
-    <t>Chequear faltantes y quiebres de lo que más rota para armar la reposición base del local hoy.</t>
-  </si>
-  <si>
-    <t>Detectar qué productos están clavados y qué conviene pausar, sin mirar el resto del recorrido.</t>
-  </si>
-  <si>
-    <t>Revisar precios visibles en góndola para ver desvíos, sin mirar rotación ni faltantes del local.</t>
-  </si>
-  <si>
-    <t>Abrir por entregas y servicio para ver reclamos, antes de revisar stock en punto de venta.</t>
-  </si>
-  <si>
-    <t>Mirar el triángulo: vendido, no vendido y competencia, para armar base y una oportunidad real.</t>
-  </si>
-  <si>
-    <t>E10</t>
-  </si>
-  <si>
-    <t>Cual frase propone reposicion base sin marear al cliente?</t>
-  </si>
-  <si>
-    <t>Si querés, decime qué te falta hoy y lo armamos rápido con eso.</t>
-  </si>
-  <si>
-    <t>Te muestro algunas opciones y vos vas eligiendo de a poco lo que prefieras.</t>
-  </si>
-  <si>
-    <t>Veo que de X estás corto; para cubrir la semana te propongo reponer 5 cajas hoy.</t>
-  </si>
-  <si>
-    <t>Hoy te recomiendo sumar algunos lanzamientos que están saliendo y probarlos esta semana.</t>
-  </si>
-  <si>
-    <t>Necesito que hoy el pedido sea más grande para que me cierre bien la visita. Respuestas + explicacion (por que es correcta)</t>
+    <t>5</t>
+  </si>
+  <si>
+    <t>F1</t>
+  </si>
+  <si>
+    <t>Cual de estas preguntas es un ejemplo claro de implicacion (I) y no de situacion (S)?</t>
+  </si>
+  <si>
+    <t>¿Cuántas unidades estás vendiendo por semana de esta categoría?</t>
+  </si>
+  <si>
+    <t>¿A qué precio lo estás vendiendo hoy en góndola?</t>
+  </si>
+  <si>
+    <t>Si esto sigue igual un mes más, ¿en qué te termina pegando: caja, espacio o viajes al mayorista?</t>
+  </si>
+  <si>
+    <t>¿Desde cuándo notás que bajó la rotación de este producto?</t>
+  </si>
+  <si>
+    <t>¿Qué te gustaría mejorar primero: ventas, margen o tiempo?</t>
+  </si>
+  <si>
+    <t>F2</t>
+  </si>
+  <si>
+    <t>Cliente: “Esta flojo”. Queres aplicar SPIN rapido. Cual secuencia es la mas ordenada?</t>
+  </si>
+  <si>
+    <t>Proponer una promo para “levantar” -&gt; preguntar qué pasa -&gt; cerrar.</t>
+  </si>
+  <si>
+    <t>Situación -&gt; problema -&gt; implicación -&gt; necesidad/pago -&gt; recién ahí oferta.</t>
+  </si>
+  <si>
+    <t>Presentar novedades -&gt; sugerir algo “para mover” -&gt; recién después preguntar cómo viene.</t>
+  </si>
+  <si>
+    <t>Hacer 1–2 preguntas de situación -&gt; listar varias promos como respuesta.</t>
+  </si>
+  <si>
+    <t>Comparar con otros (“a otros les va bien”) -&gt; presionar para que compre -&gt; luego justificar.</t>
+  </si>
+  <si>
+    <t>F3</t>
+  </si>
+  <si>
+    <t>Tenes una promo que queres empujar, pero el cliente no dijo nada aun. Que haces para no caer en venta 'al azar'?</t>
+  </si>
+  <si>
+    <t>Abrís con la promo porque está activa y “suele funcionar”, y recién después ves si aplica a su local.</t>
+  </si>
+  <si>
+    <t>Hacés 1–2 preguntas de situación/problema (venta/margen/tiempo o rotación) y mostrás la promo solo si calza.</t>
+  </si>
+  <si>
+    <t>Esperás a que el cliente la pida solo, aunque no la haya visto ni sepa que existe hoy.</t>
+  </si>
+  <si>
+    <t>Arrancás por precio y descuento, buscando que cierre rápido, sin diagnosticar qué le pesa al negocio.</t>
+  </si>
+  <si>
+    <t>Cambiás de tema para no presionar y dejás la promo para otra visita, sin plantear un próximo paso</t>
+  </si>
+  <si>
+    <t>F4</t>
+  </si>
+  <si>
+    <t>En una visita corta, cuantas preguntas de situacion suelen ser suficientes para ubicar el terreno sin interrogar?</t>
+  </si>
+  <si>
+    <t>Entre 1 y 3, cortas y al punto. Para ordenar el foco y avanzar.</t>
+  </si>
+  <si>
+    <t>Cero preguntas: mejor no preguntar nada y ofrecer directo, aunque después aparezcan objeciones por falta de contexto.</t>
+  </si>
+  <si>
+    <t>Entre 6 y 8 preguntas. Para seguir con la visita con orden.</t>
+  </si>
+  <si>
+    <t>Depende: cuanto más preguntes mejor, aunque te comas el tiempo de reposición y de propuesta con sentido.</t>
+  </si>
+  <si>
+    <t>Diez preguntas mínimo, así se nota “profesional”, aunque el cliente se canse y te corte la charla.</t>
+  </si>
+  <si>
+    <t>F5</t>
+  </si>
+  <si>
+    <t>Cual opcion diferencia mejor 'problema' de 'necesidad' en SPIN?</t>
+  </si>
+  <si>
+    <t>Problema es lo que vos querés vender hoy; necesidad es lo que el cliente te pide en el momento.</t>
+  </si>
+  <si>
+    <t>Problema es el precio alto en góndola; necesidad es bajar precio para vender más rápido hoy.</t>
+  </si>
+  <si>
+    <t>Problema es falta de stock; necesidad es meter promos, asumiendo oferta sin mirar el diagnóstico.</t>
+  </si>
+  <si>
+    <t>Problema es lo que le duele (ej. baja rentabilidad); necesidad es lo que quiere mejorar (ej. ganar más).</t>
+  </si>
+  <si>
+    <t>Problema y necesidad son lo mismo, así que no hace falta diferenciarlos en la visita.</t>
+  </si>
+  <si>
+    <t>F6</t>
+  </si>
+  <si>
+    <t>Queres abrir diagnostico sin invadir. Cual frase es la mas adecuada?</t>
+  </si>
+  <si>
+    <t>“Para ubicarme rápido, te hago dos preguntas cortas y después avanzamos con el pedido.”</t>
+  </si>
+  <si>
+    <t>“¿Me compartís tus números y tu margen de esta semana para entender cómo venís?”</t>
+  </si>
+  <si>
+    <t>“Si querés, te muestro opciones y mientras me contás qué te está pasando en el negocio.”</t>
+  </si>
+  <si>
+    <t>“Antes de ofrecerte algo, ¿te puedo hacer una pregunta corta para orientarme y ayudarte mejor?”</t>
+  </si>
+  <si>
+    <t>“Decime si te molesta que te venda y me adapto según cómo te caiga hoy.”</t>
+  </si>
+  <si>
+    <t>F7</t>
+  </si>
+  <si>
+    <t>Cliente: “No paro nunca, no tengo tiempo”. Elegí el par más coherente (Situación y Problema) para arrancar.</t>
+  </si>
+  <si>
+    <t>Situación: ¿Cuántas horas estás al frente por día y quién te cubre cuando salís? / Problema: ¿Qué parte te come más tiempo: atender, reponer o salir a comprar?</t>
+  </si>
+  <si>
+    <t>Situación: ¿Hace cuánto tenés el local y cuántos años llevás en el rubro? / Problema: ¿Te está pegando más el cansancio o la falta de ventas?</t>
+  </si>
+  <si>
+    <t>Situación: ¿Hoy te abastecés con mayorista, con reparto o combinás las dos cosas? / Problema: ¿En qué momento se te desordena más el día: compras, reposición o entregas?</t>
+  </si>
+  <si>
+    <t>Situación: ¿Cómo venís de ventas esta semana y qué productos se movieron más? / Problema: ¿Sentís que el margen te está quedando corto últimamente?</t>
+  </si>
+  <si>
+    <t>Situación: Para ubicar el foco, ¿hoy te pesa más el tiempo, las ventas o el margen? / Problema: Cuando decís “sin tiempo”, ¿qué es lo que más se te traba en el día?</t>
+  </si>
+  <si>
+    <t>F8</t>
+  </si>
+  <si>
+    <t>Cual accion rompe la logica SPIN y suele disparar objeciones innecesarias?</t>
+  </si>
+  <si>
+    <t>Escuchar y resumir lo que el cliente dijo.</t>
+  </si>
+  <si>
+    <t>Hacer una pregunta de implicación antes de ofrecer.</t>
+  </si>
+  <si>
+    <t>Ofrecer productos o promo antes de entender el problema, y después bancarte objeciones.</t>
+  </si>
+  <si>
+    <t>Preguntar qué le gustaría mejorar. Para que quede corto y claro.</t>
+  </si>
+  <si>
+    <t>Usar lo que respondió para ajustar la oferta, cambiando cantidad o enfoque según su realidad y su meta.</t>
+  </si>
+  <si>
+    <t>F9</t>
+  </si>
+  <si>
+    <t>En una conversación ya hiciste preguntas de situación y preguntas de problema, y el cliente confirmó el problema. Saltaste directo a ofrecer. ¿Qué paso clave omitiste para que el cliente lo sienta más real?</t>
+  </si>
+  <si>
+    <t>Profundizar el impacto: qué te está costando hoy ese problema en plata, tiempo o pérdida de ventas.</t>
+  </si>
+  <si>
+    <t>Reforzar el encuadre inicial: presentarte bien y marcar el propósito antes de avanzar con propuestas.</t>
+  </si>
+  <si>
+    <t>Asegurar primero la reposición base “de lo que rota” y recién después volver al problema que mencionó.</t>
+  </si>
+  <si>
+    <t>Cerrar el registro de visita (GPS/nota) y retomar la charla cuando el sistema quede completo.</t>
+  </si>
+  <si>
+    <t>Ir directo al cierre: confirmar monto y condiciones, aunque todavía no se habló del beneficio concreto.</t>
+  </si>
+  <si>
+    <t>F10</t>
+  </si>
+  <si>
+    <t>Cual cierre de diagnóstico (necesidad) arma mejor el puente hacia la oferta?</t>
+  </si>
+  <si>
+    <t>“Perfecto, entonces te muestro algunas alternativas y elegimos; arranco por las promos activas de hoy.”</t>
+  </si>
+  <si>
+    <t>“Entiendo; mejor no te ofrezco nada ahora y lo retomamos otro día con más tiempo y tranquilidad.”</t>
+  </si>
+  <si>
+    <t>“Bueno, aflojemos un poco: ¿querés un café y charlamos? Después vemos si necesitás algo del pedido.”</t>
+  </si>
+  <si>
+    <t>“Listo, seguimos con lo de siempre: cargamos lo habitual y no cambiamos nada en esta visita.”</t>
+  </si>
+  <si>
+    <t>“Entonces, si lo principal es mejorar margen sin tocar precios, probemos este mix en cantidad cuidada.” Respuestas + explicacion (por que es correcta)</t>
   </si>
 </sst>
 </file>
@@ -674,7 +674,7 @@
         <v>16</v>
       </c>
       <c r="I2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
@@ -732,7 +732,7 @@
         <v>30</v>
       </c>
       <c r="I4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
@@ -790,7 +790,7 @@
         <v>44</v>
       </c>
       <c r="I6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
@@ -877,7 +877,7 @@
         <v>65</v>
       </c>
       <c r="I9" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
@@ -906,7 +906,7 @@
         <v>72</v>
       </c>
       <c r="I10" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
@@ -935,7 +935,7 @@
         <v>79</v>
       </c>
       <c r="I11" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/public/Quiz.xlsx
+++ b/public/Quiz.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Micael\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75C27BCB-B185-4261-935A-381E51165394}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DD8D3E2-AD9F-4D1E-B45E-E615FB8B3328}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{814585D2-DACD-4865-94B7-0CB5BA22B5AF}"/>
   </bookViews>
@@ -54,217 +54,217 @@
     <t>correct</t>
   </si>
   <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>F1</t>
-  </si>
-  <si>
-    <t>Cual de estas preguntas es un ejemplo claro de implicacion (I) y no de situacion (S)?</t>
-  </si>
-  <si>
-    <t>¿Cuántas unidades estás vendiendo por semana de esta categoría?</t>
-  </si>
-  <si>
-    <t>¿A qué precio lo estás vendiendo hoy en góndola?</t>
-  </si>
-  <si>
-    <t>Si esto sigue igual un mes más, ¿en qué te termina pegando: caja, espacio o viajes al mayorista?</t>
-  </si>
-  <si>
-    <t>¿Desde cuándo notás que bajó la rotación de este producto?</t>
-  </si>
-  <si>
-    <t>¿Qué te gustaría mejorar primero: ventas, margen o tiempo?</t>
-  </si>
-  <si>
-    <t>F2</t>
-  </si>
-  <si>
-    <t>Cliente: “Esta flojo”. Queres aplicar SPIN rapido. Cual secuencia es la mas ordenada?</t>
-  </si>
-  <si>
-    <t>Proponer una promo para “levantar” -&gt; preguntar qué pasa -&gt; cerrar.</t>
-  </si>
-  <si>
-    <t>Situación -&gt; problema -&gt; implicación -&gt; necesidad/pago -&gt; recién ahí oferta.</t>
-  </si>
-  <si>
-    <t>Presentar novedades -&gt; sugerir algo “para mover” -&gt; recién después preguntar cómo viene.</t>
-  </si>
-  <si>
-    <t>Hacer 1–2 preguntas de situación -&gt; listar varias promos como respuesta.</t>
-  </si>
-  <si>
-    <t>Comparar con otros (“a otros les va bien”) -&gt; presionar para que compre -&gt; luego justificar.</t>
-  </si>
-  <si>
-    <t>F3</t>
-  </si>
-  <si>
-    <t>Tenes una promo que queres empujar, pero el cliente no dijo nada aun. Que haces para no caer en venta 'al azar'?</t>
-  </si>
-  <si>
-    <t>Abrís con la promo porque está activa y “suele funcionar”, y recién después ves si aplica a su local.</t>
-  </si>
-  <si>
-    <t>Hacés 1–2 preguntas de situación/problema (venta/margen/tiempo o rotación) y mostrás la promo solo si calza.</t>
-  </si>
-  <si>
-    <t>Esperás a que el cliente la pida solo, aunque no la haya visto ni sepa que existe hoy.</t>
-  </si>
-  <si>
-    <t>Arrancás por precio y descuento, buscando que cierre rápido, sin diagnosticar qué le pesa al negocio.</t>
-  </si>
-  <si>
-    <t>Cambiás de tema para no presionar y dejás la promo para otra visita, sin plantear un próximo paso</t>
-  </si>
-  <si>
-    <t>F4</t>
-  </si>
-  <si>
-    <t>En una visita corta, cuantas preguntas de situacion suelen ser suficientes para ubicar el terreno sin interrogar?</t>
-  </si>
-  <si>
-    <t>Entre 1 y 3, cortas y al punto. Para ordenar el foco y avanzar.</t>
-  </si>
-  <si>
-    <t>Cero preguntas: mejor no preguntar nada y ofrecer directo, aunque después aparezcan objeciones por falta de contexto.</t>
-  </si>
-  <si>
-    <t>Entre 6 y 8 preguntas. Para seguir con la visita con orden.</t>
-  </si>
-  <si>
-    <t>Depende: cuanto más preguntes mejor, aunque te comas el tiempo de reposición y de propuesta con sentido.</t>
-  </si>
-  <si>
-    <t>Diez preguntas mínimo, así se nota “profesional”, aunque el cliente se canse y te corte la charla.</t>
-  </si>
-  <si>
-    <t>F5</t>
-  </si>
-  <si>
-    <t>Cual opcion diferencia mejor 'problema' de 'necesidad' en SPIN?</t>
-  </si>
-  <si>
-    <t>Problema es lo que vos querés vender hoy; necesidad es lo que el cliente te pide en el momento.</t>
-  </si>
-  <si>
-    <t>Problema es el precio alto en góndola; necesidad es bajar precio para vender más rápido hoy.</t>
-  </si>
-  <si>
-    <t>Problema es falta de stock; necesidad es meter promos, asumiendo oferta sin mirar el diagnóstico.</t>
-  </si>
-  <si>
-    <t>Problema es lo que le duele (ej. baja rentabilidad); necesidad es lo que quiere mejorar (ej. ganar más).</t>
-  </si>
-  <si>
-    <t>Problema y necesidad son lo mismo, así que no hace falta diferenciarlos en la visita.</t>
-  </si>
-  <si>
-    <t>F6</t>
-  </si>
-  <si>
-    <t>Queres abrir diagnostico sin invadir. Cual frase es la mas adecuada?</t>
-  </si>
-  <si>
-    <t>“Para ubicarme rápido, te hago dos preguntas cortas y después avanzamos con el pedido.”</t>
-  </si>
-  <si>
-    <t>“¿Me compartís tus números y tu margen de esta semana para entender cómo venís?”</t>
-  </si>
-  <si>
-    <t>“Si querés, te muestro opciones y mientras me contás qué te está pasando en el negocio.”</t>
-  </si>
-  <si>
-    <t>“Antes de ofrecerte algo, ¿te puedo hacer una pregunta corta para orientarme y ayudarte mejor?”</t>
-  </si>
-  <si>
-    <t>“Decime si te molesta que te venda y me adapto según cómo te caiga hoy.”</t>
-  </si>
-  <si>
-    <t>F7</t>
-  </si>
-  <si>
-    <t>Cliente: “No paro nunca, no tengo tiempo”. Elegí el par más coherente (Situación y Problema) para arrancar.</t>
-  </si>
-  <si>
-    <t>Situación: ¿Cuántas horas estás al frente por día y quién te cubre cuando salís? / Problema: ¿Qué parte te come más tiempo: atender, reponer o salir a comprar?</t>
-  </si>
-  <si>
-    <t>Situación: ¿Hace cuánto tenés el local y cuántos años llevás en el rubro? / Problema: ¿Te está pegando más el cansancio o la falta de ventas?</t>
-  </si>
-  <si>
-    <t>Situación: ¿Hoy te abastecés con mayorista, con reparto o combinás las dos cosas? / Problema: ¿En qué momento se te desordena más el día: compras, reposición o entregas?</t>
-  </si>
-  <si>
-    <t>Situación: ¿Cómo venís de ventas esta semana y qué productos se movieron más? / Problema: ¿Sentís que el margen te está quedando corto últimamente?</t>
-  </si>
-  <si>
-    <t>Situación: Para ubicar el foco, ¿hoy te pesa más el tiempo, las ventas o el margen? / Problema: Cuando decís “sin tiempo”, ¿qué es lo que más se te traba en el día?</t>
-  </si>
-  <si>
-    <t>F8</t>
-  </si>
-  <si>
-    <t>Cual accion rompe la logica SPIN y suele disparar objeciones innecesarias?</t>
-  </si>
-  <si>
-    <t>Escuchar y resumir lo que el cliente dijo.</t>
-  </si>
-  <si>
-    <t>Hacer una pregunta de implicación antes de ofrecer.</t>
-  </si>
-  <si>
-    <t>Ofrecer productos o promo antes de entender el problema, y después bancarte objeciones.</t>
-  </si>
-  <si>
-    <t>Preguntar qué le gustaría mejorar. Para que quede corto y claro.</t>
-  </si>
-  <si>
-    <t>Usar lo que respondió para ajustar la oferta, cambiando cantidad o enfoque según su realidad y su meta.</t>
-  </si>
-  <si>
-    <t>F9</t>
-  </si>
-  <si>
-    <t>En una conversación ya hiciste preguntas de situación y preguntas de problema, y el cliente confirmó el problema. Saltaste directo a ofrecer. ¿Qué paso clave omitiste para que el cliente lo sienta más real?</t>
-  </si>
-  <si>
-    <t>Profundizar el impacto: qué te está costando hoy ese problema en plata, tiempo o pérdida de ventas.</t>
-  </si>
-  <si>
-    <t>Reforzar el encuadre inicial: presentarte bien y marcar el propósito antes de avanzar con propuestas.</t>
-  </si>
-  <si>
-    <t>Asegurar primero la reposición base “de lo que rota” y recién después volver al problema que mencionó.</t>
-  </si>
-  <si>
-    <t>Cerrar el registro de visita (GPS/nota) y retomar la charla cuando el sistema quede completo.</t>
-  </si>
-  <si>
-    <t>Ir directo al cierre: confirmar monto y condiciones, aunque todavía no se habló del beneficio concreto.</t>
-  </si>
-  <si>
-    <t>F10</t>
-  </si>
-  <si>
-    <t>Cual cierre de diagnóstico (necesidad) arma mejor el puente hacia la oferta?</t>
-  </si>
-  <si>
-    <t>“Perfecto, entonces te muestro algunas alternativas y elegimos; arranco por las promos activas de hoy.”</t>
-  </si>
-  <si>
-    <t>“Entiendo; mejor no te ofrezco nada ahora y lo retomamos otro día con más tiempo y tranquilidad.”</t>
-  </si>
-  <si>
-    <t>“Bueno, aflojemos un poco: ¿querés un café y charlamos? Después vemos si necesitás algo del pedido.”</t>
-  </si>
-  <si>
-    <t>“Listo, seguimos con lo de siempre: cargamos lo habitual y no cambiamos nada en esta visita.”</t>
-  </si>
-  <si>
-    <t>“Entonces, si lo principal es mejorar margen sin tocar precios, probemos este mix en cantidad cuidada.” Respuestas + explicacion (por que es correcta)</t>
+    <t>6</t>
+  </si>
+  <si>
+    <t>G1</t>
+  </si>
+  <si>
+    <t>Cliente: “Vendo, pero no me queda nada”. En que tipo de dolor cae principalmente?</t>
+  </si>
+  <si>
+    <t>Dolor de ventas: vende “algo”, pero siente que no alcanza volumen, como si el movimiento no compensara el esfuerzo del día.</t>
+  </si>
+  <si>
+    <t>Dolor de rentabilidad/margen: hay venta, pero la ganancia por operación es baja y “no queda nada” al final, aunque entre plata.</t>
+  </si>
+  <si>
+    <t>Dolor de tiempo/cansancio: vende y trabaja. Para dejar una salida concreta. Para no entrar en detalles de más.</t>
+  </si>
+  <si>
+    <t>Dolor de espacio/stock: vende, pero se le desordena el local, se acumula mercadería o no puede exhibir bien, y eso le come resultado.</t>
+  </si>
+  <si>
+    <t>Comentario general: expresa frustración, pero no permite ubicar si es margen, ventas, tiempo o stock sin una pregunta más.</t>
+  </si>
+  <si>
+    <t>G2</t>
+  </si>
+  <si>
+    <t>Cliente: “No paro nunca, siempre tengo que ir yo al mayorista”. Que pregunta convierte mejor ese comentario en necesidad explicita?</t>
+  </si>
+  <si>
+    <t>“¿Te pasa que preferís hacerlo vos o es que no tenés a quién delegarlo en el local?”</t>
+  </si>
+  <si>
+    <t>“Si pudieras ahorrarte uno o dos viajes al mayorista por mes, ¿eso te resolvería parte del día?”</t>
+  </si>
+  <si>
+    <t>“¿Cuánto te cuesta por semana entre nafta, peajes y el tiempo que perdés en esos viajes?”</t>
+  </si>
+  <si>
+    <t>“¿Qué es lo que te obliga a ir vos: precio, falta de entrega o no tener una reposición armada?”</t>
+  </si>
+  <si>
+    <t>“Entiendo; hoy sigamos con lo de siempre y la próxima lo miramos con más calma.”</t>
+  </si>
+  <si>
+    <t>G3</t>
+  </si>
+  <si>
+    <t>Elegi la mejor pregunta de implicacion para un cliente con stock clavado.</t>
+  </si>
+  <si>
+    <t>“Si ese stock sigue parado 2–3 meses más, ¿qué te termina costando: plata inmovilizada, espacio o perder otras ventas?”.</t>
+  </si>
+  <si>
+    <t>“¿Cuánto espacio de góndola/heladera tenés disponible hoy?”. Para que quede corto y claro.</t>
+  </si>
+  <si>
+    <t>“¿Te convence esta marca o preferís otra?”. Para seguir con la visita con orden.</t>
+  </si>
+  <si>
+    <t>“Cuando vas al mayorista, ¿cada cuánto terminás yendo por semana?”.</t>
+  </si>
+  <si>
+    <t>“¿Hace cuánto lo trabajás y desde cuándo notaste que se clavó?”.</t>
+  </si>
+  <si>
+    <t>G4</t>
+  </si>
+  <si>
+    <t>Cliente: “Tengo el deposito explotado”. Cual frase de empatia es mas alineada?</t>
+  </si>
+  <si>
+    <t>“Te entiendo; a veces pasa cuando se compra sin mirar rotación y después queda todo apretado.”</t>
+  </si>
+  <si>
+    <t>“Te entiendo; es bastante común en estos días, vamos viendo cómo lo acomodamos con calma.”</t>
+  </si>
+  <si>
+    <t>“Te entiendo; con el depósito así se traba todo: no entra reposición, se desordena y se pierden ventas por falta de espacio.”</t>
+  </si>
+  <si>
+    <t>“Te entiendo; no es tan grave, suele acomodarse solo con un poco de orden y tiempo.”</t>
+  </si>
+  <si>
+    <t>“Te entiendo; metamos igual y después lo acomodás, así aprovechamos la visita y no perdés la vuelta.”</t>
+  </si>
+  <si>
+    <t>G5</t>
+  </si>
+  <si>
+    <t>El cliente dice dos cosas: “No se vende” y “no tengo lugar”. Que haria mejor un preventista para definir el foco?</t>
+  </si>
+  <si>
+    <t>“Para ordenar la charla, si tuvieras que elegir una sola: ¿hoy te frena más la venta o el espacio?”</t>
+  </si>
+  <si>
+    <t>“Arranco con una promo puntual para destrabar algo rápido y después vemos lo del lugar.”</t>
+  </si>
+  <si>
+    <t>“Dale, pasame lo de siempre y lo cargo, así no perdemos tiempo en esta visita.”</t>
+  </si>
+  <si>
+    <t>“Antes de eso, contame cómo venís con costos fijos e impuestos este mes, así entiendo el contexto.”</t>
+  </si>
+  <si>
+    <t>“En otros locales se está vendiendo; contame qué estás haciendo distinto acá con la categoría.”</t>
+  </si>
+  <si>
+    <t>G6</t>
+  </si>
+  <si>
+    <t>Mientras el cliente te cuenta su problema, cual conducta va en contra de una buena profundizacion del dolor?</t>
+  </si>
+  <si>
+    <t>Dejarlo terminar y hacer una pregunta corta para ordenar lo que escuchaste.</t>
+  </si>
+  <si>
+    <t>Hacer una pregunta sobre consecuencias para dimensionar el impacto del problema en su negocio.</t>
+  </si>
+  <si>
+    <t>Usar una frase breve de empatía y seguir con una pregunta para entender mejor el punto.</t>
+  </si>
+  <si>
+    <t>Interrumpir para mostrar catálogos y precios y pasar directo a oferta “para ahorrar tiempo”.</t>
+  </si>
+  <si>
+    <t>Repetir con tus palabras lo entendido y confirmar si lo interpretaste bien.</t>
+  </si>
+  <si>
+    <t>G7</t>
+  </si>
+  <si>
+    <t>Cliente: “Vendo, pero no me queda plata. Encima los impuestos me matan”. Elegi la mejor combinacion (pregunta de implicación + frase de empatía) para seguir.</t>
+  </si>
+  <si>
+    <t>Pregunta: ¿Más o menos cuánto se te va en impuestos por mes? + Empatía: Te entiendo, es un golpe cuando el margen ya viene justo.</t>
+  </si>
+  <si>
+    <t>Pregunta: ¿Y qué estás haciendo distinto que antes? + Empatía: A muchos les pasa, hay que aguantar. Para que quede corto y claro.</t>
+  </si>
+  <si>
+    <t>Pregunta: ¿Si subís un poco los precios lo compensás? + Empatía: Tranquilo, se acomoda. Para no entrar en detalles de más.</t>
+  </si>
+  <si>
+    <t>Pregunta: Si seguís con este margen 6 meses más, ¿qué te pasa en el negocio (pagos, reinversión, compras)? + Empatía: Te entiendo, es frustrante trabajar y que no quede.</t>
+  </si>
+  <si>
+    <t>Pregunta: ¿Qué sentís que te pega más: impuestos, costos o precio de compra? + Empatía: Qué bronca, la verdad.</t>
+  </si>
+  <si>
+    <t>G8</t>
+  </si>
+  <si>
+    <t>Despues de una pregunta de implicacion, cual es el paso mas conveniente antes de ofrecer producto?</t>
+  </si>
+  <si>
+    <t>Pasar directo a “te muestro cinco opciones que suelen funcionar”, sin chequear si encaja con lo que reconoció.</t>
+  </si>
+  <si>
+    <t>Hacer un comentario neutro y cambiar de tema, dejando la consecuencia planteada sin siguiente paso.</t>
+  </si>
+  <si>
+    <t>Empezar a hablar de entregas y condiciones, aunque no responda al foco del problema que salió.</t>
+  </si>
+  <si>
+    <t>Ir a “cerrémoslo así” y pedir confirmación del pedido, sin acordar antes qué sería útil.</t>
+  </si>
+  <si>
+    <t>Resumir en una frase, chequear acuerdo y recién ahí proponer una opción alineada al foco.</t>
+  </si>
+  <si>
+    <t>G9</t>
+  </si>
+  <si>
+    <t>Cual de estas frases es un ejemplo de necesidad explicita (no solo queja)?</t>
+  </si>
+  <si>
+    <t>“Estoy cansado” y me está costando sostener el ritmo del local esta semana.</t>
+  </si>
+  <si>
+    <t>“No se vende nada” y siento que la mercadería no se está moviendo como antes.</t>
+  </si>
+  <si>
+    <t>“Necesito un proveedor que me entregue y me ahorre ir al mayorista cada semana.”</t>
+  </si>
+  <si>
+    <t>“Los precios están altos” y así se me complica vender sin perder margen del local.</t>
+  </si>
+  <si>
+    <t>“El barrio está difícil” y cada vez entra menos gente a comprar en estos días.</t>
+  </si>
+  <si>
+    <t>G10</t>
+  </si>
+  <si>
+    <t>El cliente dice rápido: “No paro nunca, tengo que ir yo al mayorista.” Tenés 1 minuto para profundizar sin invadir. ¿Qué micro-pregunta es la más efectiva?</t>
+  </si>
+  <si>
+    <t>“¿Cada cuánto estás yendo al mayorista y en qué momento del día se te complica más hacerlo?”</t>
+  </si>
+  <si>
+    <t>“¿Qué es lo que te obliga a ir vos: precio, falta de entrega o que se te corta la mercadería?”</t>
+  </si>
+  <si>
+    <t>“Cuando vas al mayorista, ¿qué terminás buscando sí o sí para no quedarte corto en la semana?”</t>
+  </si>
+  <si>
+    <t>“¿Te pasa por falta de tiempo o porque no confiás en que te entreguen como corresponde siempre?”</t>
+  </si>
+  <si>
+    <t>“Si pudieras ahorrarte uno o dos viajes al mayorista por mes, ¿eso te resolvería parte del día?” Respuestas + explicacion (por que es correcta)</t>
   </si>
 </sst>
 </file>
@@ -674,7 +674,7 @@
         <v>16</v>
       </c>
       <c r="I2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
@@ -732,7 +732,7 @@
         <v>30</v>
       </c>
       <c r="I4" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
@@ -761,7 +761,7 @@
         <v>37</v>
       </c>
       <c r="I5" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
@@ -790,7 +790,7 @@
         <v>44</v>
       </c>
       <c r="I6" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
@@ -848,7 +848,7 @@
         <v>58</v>
       </c>
       <c r="I8" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
@@ -877,7 +877,7 @@
         <v>65</v>
       </c>
       <c r="I9" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
@@ -906,7 +906,7 @@
         <v>72</v>
       </c>
       <c r="I10" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">

--- a/public/Quiz.xlsx
+++ b/public/Quiz.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Micael\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DD8D3E2-AD9F-4D1E-B45E-E615FB8B3328}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFDA609B-A5B1-4297-BC11-B923CA896C97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{814585D2-DACD-4865-94B7-0CB5BA22B5AF}"/>
   </bookViews>
@@ -54,217 +54,217 @@
     <t>correct</t>
   </si>
   <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>G1</t>
-  </si>
-  <si>
-    <t>Cliente: “Vendo, pero no me queda nada”. En que tipo de dolor cae principalmente?</t>
-  </si>
-  <si>
-    <t>Dolor de ventas: vende “algo”, pero siente que no alcanza volumen, como si el movimiento no compensara el esfuerzo del día.</t>
-  </si>
-  <si>
-    <t>Dolor de rentabilidad/margen: hay venta, pero la ganancia por operación es baja y “no queda nada” al final, aunque entre plata.</t>
-  </si>
-  <si>
-    <t>Dolor de tiempo/cansancio: vende y trabaja. Para dejar una salida concreta. Para no entrar en detalles de más.</t>
-  </si>
-  <si>
-    <t>Dolor de espacio/stock: vende, pero se le desordena el local, se acumula mercadería o no puede exhibir bien, y eso le come resultado.</t>
-  </si>
-  <si>
-    <t>Comentario general: expresa frustración, pero no permite ubicar si es margen, ventas, tiempo o stock sin una pregunta más.</t>
-  </si>
-  <si>
-    <t>G2</t>
-  </si>
-  <si>
-    <t>Cliente: “No paro nunca, siempre tengo que ir yo al mayorista”. Que pregunta convierte mejor ese comentario en necesidad explicita?</t>
-  </si>
-  <si>
-    <t>“¿Te pasa que preferís hacerlo vos o es que no tenés a quién delegarlo en el local?”</t>
-  </si>
-  <si>
-    <t>“Si pudieras ahorrarte uno o dos viajes al mayorista por mes, ¿eso te resolvería parte del día?”</t>
-  </si>
-  <si>
-    <t>“¿Cuánto te cuesta por semana entre nafta, peajes y el tiempo que perdés en esos viajes?”</t>
-  </si>
-  <si>
-    <t>“¿Qué es lo que te obliga a ir vos: precio, falta de entrega o no tener una reposición armada?”</t>
-  </si>
-  <si>
-    <t>“Entiendo; hoy sigamos con lo de siempre y la próxima lo miramos con más calma.”</t>
-  </si>
-  <si>
-    <t>G3</t>
-  </si>
-  <si>
-    <t>Elegi la mejor pregunta de implicacion para un cliente con stock clavado.</t>
-  </si>
-  <si>
-    <t>“Si ese stock sigue parado 2–3 meses más, ¿qué te termina costando: plata inmovilizada, espacio o perder otras ventas?”.</t>
-  </si>
-  <si>
-    <t>“¿Cuánto espacio de góndola/heladera tenés disponible hoy?”. Para que quede corto y claro.</t>
-  </si>
-  <si>
-    <t>“¿Te convence esta marca o preferís otra?”. Para seguir con la visita con orden.</t>
-  </si>
-  <si>
-    <t>“Cuando vas al mayorista, ¿cada cuánto terminás yendo por semana?”.</t>
-  </si>
-  <si>
-    <t>“¿Hace cuánto lo trabajás y desde cuándo notaste que se clavó?”.</t>
-  </si>
-  <si>
-    <t>G4</t>
-  </si>
-  <si>
-    <t>Cliente: “Tengo el deposito explotado”. Cual frase de empatia es mas alineada?</t>
-  </si>
-  <si>
-    <t>“Te entiendo; a veces pasa cuando se compra sin mirar rotación y después queda todo apretado.”</t>
-  </si>
-  <si>
-    <t>“Te entiendo; es bastante común en estos días, vamos viendo cómo lo acomodamos con calma.”</t>
-  </si>
-  <si>
-    <t>“Te entiendo; con el depósito así se traba todo: no entra reposición, se desordena y se pierden ventas por falta de espacio.”</t>
-  </si>
-  <si>
-    <t>“Te entiendo; no es tan grave, suele acomodarse solo con un poco de orden y tiempo.”</t>
-  </si>
-  <si>
-    <t>“Te entiendo; metamos igual y después lo acomodás, así aprovechamos la visita y no perdés la vuelta.”</t>
-  </si>
-  <si>
-    <t>G5</t>
-  </si>
-  <si>
-    <t>El cliente dice dos cosas: “No se vende” y “no tengo lugar”. Que haria mejor un preventista para definir el foco?</t>
-  </si>
-  <si>
-    <t>“Para ordenar la charla, si tuvieras que elegir una sola: ¿hoy te frena más la venta o el espacio?”</t>
-  </si>
-  <si>
-    <t>“Arranco con una promo puntual para destrabar algo rápido y después vemos lo del lugar.”</t>
-  </si>
-  <si>
-    <t>“Dale, pasame lo de siempre y lo cargo, así no perdemos tiempo en esta visita.”</t>
-  </si>
-  <si>
-    <t>“Antes de eso, contame cómo venís con costos fijos e impuestos este mes, así entiendo el contexto.”</t>
-  </si>
-  <si>
-    <t>“En otros locales se está vendiendo; contame qué estás haciendo distinto acá con la categoría.”</t>
-  </si>
-  <si>
-    <t>G6</t>
-  </si>
-  <si>
-    <t>Mientras el cliente te cuenta su problema, cual conducta va en contra de una buena profundizacion del dolor?</t>
-  </si>
-  <si>
-    <t>Dejarlo terminar y hacer una pregunta corta para ordenar lo que escuchaste.</t>
-  </si>
-  <si>
-    <t>Hacer una pregunta sobre consecuencias para dimensionar el impacto del problema en su negocio.</t>
-  </si>
-  <si>
-    <t>Usar una frase breve de empatía y seguir con una pregunta para entender mejor el punto.</t>
-  </si>
-  <si>
-    <t>Interrumpir para mostrar catálogos y precios y pasar directo a oferta “para ahorrar tiempo”.</t>
-  </si>
-  <si>
-    <t>Repetir con tus palabras lo entendido y confirmar si lo interpretaste bien.</t>
-  </si>
-  <si>
-    <t>G7</t>
-  </si>
-  <si>
-    <t>Cliente: “Vendo, pero no me queda plata. Encima los impuestos me matan”. Elegi la mejor combinacion (pregunta de implicación + frase de empatía) para seguir.</t>
-  </si>
-  <si>
-    <t>Pregunta: ¿Más o menos cuánto se te va en impuestos por mes? + Empatía: Te entiendo, es un golpe cuando el margen ya viene justo.</t>
-  </si>
-  <si>
-    <t>Pregunta: ¿Y qué estás haciendo distinto que antes? + Empatía: A muchos les pasa, hay que aguantar. Para que quede corto y claro.</t>
-  </si>
-  <si>
-    <t>Pregunta: ¿Si subís un poco los precios lo compensás? + Empatía: Tranquilo, se acomoda. Para no entrar en detalles de más.</t>
-  </si>
-  <si>
-    <t>Pregunta: Si seguís con este margen 6 meses más, ¿qué te pasa en el negocio (pagos, reinversión, compras)? + Empatía: Te entiendo, es frustrante trabajar y que no quede.</t>
-  </si>
-  <si>
-    <t>Pregunta: ¿Qué sentís que te pega más: impuestos, costos o precio de compra? + Empatía: Qué bronca, la verdad.</t>
-  </si>
-  <si>
-    <t>G8</t>
-  </si>
-  <si>
-    <t>Despues de una pregunta de implicacion, cual es el paso mas conveniente antes de ofrecer producto?</t>
-  </si>
-  <si>
-    <t>Pasar directo a “te muestro cinco opciones que suelen funcionar”, sin chequear si encaja con lo que reconoció.</t>
-  </si>
-  <si>
-    <t>Hacer un comentario neutro y cambiar de tema, dejando la consecuencia planteada sin siguiente paso.</t>
-  </si>
-  <si>
-    <t>Empezar a hablar de entregas y condiciones, aunque no responda al foco del problema que salió.</t>
-  </si>
-  <si>
-    <t>Ir a “cerrémoslo así” y pedir confirmación del pedido, sin acordar antes qué sería útil.</t>
-  </si>
-  <si>
-    <t>Resumir en una frase, chequear acuerdo y recién ahí proponer una opción alineada al foco.</t>
-  </si>
-  <si>
-    <t>G9</t>
-  </si>
-  <si>
-    <t>Cual de estas frases es un ejemplo de necesidad explicita (no solo queja)?</t>
-  </si>
-  <si>
-    <t>“Estoy cansado” y me está costando sostener el ritmo del local esta semana.</t>
-  </si>
-  <si>
-    <t>“No se vende nada” y siento que la mercadería no se está moviendo como antes.</t>
-  </si>
-  <si>
-    <t>“Necesito un proveedor que me entregue y me ahorre ir al mayorista cada semana.”</t>
-  </si>
-  <si>
-    <t>“Los precios están altos” y así se me complica vender sin perder margen del local.</t>
-  </si>
-  <si>
-    <t>“El barrio está difícil” y cada vez entra menos gente a comprar en estos días.</t>
-  </si>
-  <si>
-    <t>G10</t>
-  </si>
-  <si>
-    <t>El cliente dice rápido: “No paro nunca, tengo que ir yo al mayorista.” Tenés 1 minuto para profundizar sin invadir. ¿Qué micro-pregunta es la más efectiva?</t>
-  </si>
-  <si>
-    <t>“¿Cada cuánto estás yendo al mayorista y en qué momento del día se te complica más hacerlo?”</t>
-  </si>
-  <si>
-    <t>“¿Qué es lo que te obliga a ir vos: precio, falta de entrega o que se te corta la mercadería?”</t>
-  </si>
-  <si>
-    <t>“Cuando vas al mayorista, ¿qué terminás buscando sí o sí para no quedarte corto en la semana?”</t>
-  </si>
-  <si>
-    <t>“¿Te pasa por falta de tiempo o porque no confiás en que te entreguen como corresponde siempre?”</t>
-  </si>
-  <si>
-    <t>“Si pudieras ahorrarte uno o dos viajes al mayorista por mes, ¿eso te resolvería parte del día?” Respuestas + explicacion (por que es correcta)</t>
+    <t>8</t>
+  </si>
+  <si>
+    <t>I1</t>
+  </si>
+  <si>
+    <t>Cual orden representa mejor el modelo para cualquier objecion?</t>
+  </si>
+  <si>
+    <t>Empatía -&gt; 2–3 beneficios -&gt; credibilidad -&gt; propuesta chica.</t>
+  </si>
+  <si>
+    <t>Empatía -&gt; credibilidad -&gt; propuesta chica -&gt; beneficios.</t>
+  </si>
+  <si>
+    <t>Empatía -&gt; credibilidad (casos similares) -&gt; 2–3 beneficios concretos -&gt; propuesta chica y medible.</t>
+  </si>
+  <si>
+    <t>Empatía -&gt; beneficios -&gt; descuento “para destrabar” -&gt; cierre.</t>
+  </si>
+  <si>
+    <t>Empatía -&gt; preguntar/confirmar la traba -&gt; beneficios -&gt; cierre directo.</t>
+  </si>
+  <si>
+    <t>I2</t>
+  </si>
+  <si>
+    <t>Cliente: 'Estas caro'. Elegi la respuesta mas completa</t>
+  </si>
+  <si>
+    <t>Te entiendo. ¿Qué estás comparando: precio por unidad o el costo total de tenerlo en el local?</t>
+  </si>
+  <si>
+    <t>Te entiendo. En locales parecidos les pasaba; al mirar el costo completo les cerró recibir en el local. Probemos chico y medimos.</t>
+  </si>
+  <si>
+    <t>Puede ser: si miramos solo la unidad parece más alto. Arranquemos con pocas unidades y vemos rotación esta semana.</t>
+  </si>
+  <si>
+    <t>Te entiendo. Si hoy no te cierra, no pasa nada; lo dejamos para más adelante y seguís con lo que te esté funcionando.</t>
+  </si>
+  <si>
+    <t>Sí, está caro por costos e impuestos. Igual te puedo mejorar un poco el precio si así te sirve arrancar.</t>
+  </si>
+  <si>
+    <t>I3</t>
+  </si>
+  <si>
+    <t>En una respuesta a objecion, cual pieza suele faltar cuando el preventista dice solo: 'Te entiendo'?</t>
+  </si>
+  <si>
+    <t>Sumar una pregunta breve para profundizar la causa (rotación, precio, competencia) antes de proponer algo.</t>
+  </si>
+  <si>
+    <t>Credibilidad y beneficios concretos, más una propuesta chica para bajar el riesgo y poder avanzar sin forzar.</t>
+  </si>
+  <si>
+    <t>Enmarcar con una frase corta de ayuda (“para que no pierdas ventas”) antes de avanzar con la propuesta.</t>
+  </si>
+  <si>
+    <t>Tomar nota en el sistema y cerrar; priorizar el registro por sobre la conversación.</t>
+  </si>
+  <si>
+    <t>Ir directo a reponer lo de siempre sin agregar diagnóstico ni validación de la objeción.</t>
+  </si>
+  <si>
+    <t>I4</t>
+  </si>
+  <si>
+    <t>Cual de estas frases funciona mejor como inicio de empatia?</t>
+  </si>
+  <si>
+    <t>Entiendo por qué lo ves así; a varios les está pasando.</t>
+  </si>
+  <si>
+    <t>Puede ser que parezca eso; contame un segundo qué es lo que te hace ruido.</t>
+  </si>
+  <si>
+    <t>Si hoy no armamos nada, me complica justificar la visita.</t>
+  </si>
+  <si>
+    <t>Ok, no pasa nada. Para dejar una salida concreta.</t>
+  </si>
+  <si>
+    <t>Bueno, eso lo resolvés vos; yo solo tomo el pedido.</t>
+  </si>
+  <si>
+    <t>I5</t>
+  </si>
+  <si>
+    <t>Caso: Estás en la visita y, cuando empezás a mostrar opciones, el cliente te frena con: “No tengo plata.” Pregunta: ¿Qué respuesta suele cortar la conversación y empeorar la visita (porque te saca del juego en vez de destrabar)?</t>
+  </si>
+  <si>
+    <t>“Te entiendo. Hagamos algo chico y de rotación segura, así cuidás caja y no frenás.”</t>
+  </si>
+  <si>
+    <t>“Te entiendo. A otros del barrio les pasó; arrancaron con poco y les funcionó, sin presión.”</t>
+  </si>
+  <si>
+    <t>“Listo, entonces no hacemos nada hoy. Cuando se acomode tu plata, me avisás y vuelvo.”</t>
+  </si>
+  <si>
+    <t>“Te entiendo. Veamos el costo total: a veces se pierde en viajes/quiebres; lo reencuadramos sin discutir.”</t>
+  </si>
+  <si>
+    <t>“Probemos con poco y lo revisamos en el próximo repaso; baja riesgo y deja una medición clara.”</t>
+  </si>
+  <si>
+    <t>I6</t>
+  </si>
+  <si>
+    <t>Cliente: 'Eso no se vende'. Elegi la mejor respuesta</t>
+  </si>
+  <si>
+    <t>Entiendo que lo veas así, pero te aseguro que sí sale.</t>
+  </si>
+  <si>
+    <t>Ok, entonces no te lo ofrezco más y seguimos con lo de siempre.</t>
+  </si>
+  <si>
+    <t>Te entiendo; llevá igual y después me contás.</t>
+  </si>
+  <si>
+    <t>Te entiendo. En locales similares rindió probar poco, bien visible y con una promo corta; dejamos chico</t>
+  </si>
+  <si>
+    <t>Puede ser. Entonces cambiemos a otra cosa. Para ordenar el foco y avanzar.</t>
+  </si>
+  <si>
+    <t>I7</t>
+  </si>
+  <si>
+    <t>En objeciones, por que conviene limitarte a 2-3 beneficios y no listar 7?</t>
+  </si>
+  <si>
+    <t>Porque con 2–3 beneficios ligados a su objeción respondés directo y el cliente lo puede evaluar sin perderse.</t>
+  </si>
+  <si>
+    <t>Porque así siempre repetís el mismo discurso y no te olvidás de nada en la visita.</t>
+  </si>
+  <si>
+    <t>Porque si decís 7 beneficios, el cliente siempre va a pedir descuento aunque no lo haya mencionado.</t>
+  </si>
+  <si>
+    <t>Porque es mejor evitar beneficios y pasar directo a cerrar para no alargar la conversación.</t>
+  </si>
+  <si>
+    <t>Porque cuanto más hablás, más autoridad mostrás y más fácil es que acepte sin preguntas.</t>
+  </si>
+  <si>
+    <t>I8</t>
+  </si>
+  <si>
+    <t>Cual frase es un ejemplo de 'credibilidad/comparacion'?</t>
+  </si>
+  <si>
+    <t>“Te entiendo; a varios les viene pasando algo parecido.”</t>
+  </si>
+  <si>
+    <t>“En mi ruta, a clientes que estaban igual les funcionó este ajuste y se les acomodó la rotación.”</t>
+  </si>
+  <si>
+    <t>“Si querés, lo probamos con poca cantidad esta semana y lo revisamos en la próxima visita.”</t>
+  </si>
+  <si>
+    <t>“En otros almacenes parecidos al tuyo probamos esto y les funcionó.”</t>
+  </si>
+  <si>
+    <t>“Con esto vas a notar la diferencia y se va a mover más rápido esta semana.”</t>
+  </si>
+  <si>
+    <t>I9</t>
+  </si>
+  <si>
+    <t>Objecion: 'Lo consigo mas barato en el mayorista'. Que respuesta aplica mejor el modelo sin pelear?</t>
+  </si>
+  <si>
+    <t>Puede ser que allá esté más barato. Igual, ese precio es el que hay.</t>
+  </si>
+  <si>
+    <t>Entiendo. Si querés, lo vemos la próxima y hoy seguimos con lo de siempre.</t>
+  </si>
+  <si>
+    <t>Dale, te lo igualo y arrancamos. Para no meter presión ni discutir. Para dejar una salida concreta.</t>
+  </si>
+  <si>
+    <t>Sí, a veces pasa. ¿Cada cuánto tenés que ir y qué te implica en tiempo y efectivo?</t>
+  </si>
+  <si>
+    <t>Te entiendo. A otros les pasaba; cuando sumaron viaje, tiempo y manejo de efectivo, les cerró recibir en el local. Probemos chico y comparás.</t>
+  </si>
+  <si>
+    <t>I10</t>
+  </si>
+  <si>
+    <t>El cliente repite la objecion por segunda vez. Que estrategia suele ser mas efectiva para destrabar sin presionar?</t>
+  </si>
+  <si>
+    <t>“Te entiendo. Para no dar vueltas, lo dejamos por hoy y seguimos con lo que ya venís llevando.”</t>
+  </si>
+  <si>
+    <t>“Ok, anotado. ¿Qué tendría que pasar para que te sirva considerarlo en la próxima visita?”</t>
+  </si>
+  <si>
+    <t>“Dale, no hay problema. Igual te lo dejo marcado porque esto en general termina funcionando bien.”</t>
+  </si>
+  <si>
+    <t>“Perfecto, entonces lo saco. ¿Querés que te muestre otra cosa para compensar el pedido?”</t>
+  </si>
+  <si>
+    <t>“Te entiendo. ¿Qué es lo que más te frena (rotación, margen o espacio)?” y, según eso, proponer una prueba acotada con qué mirar. Respuestas + explicacion (por que es correcta)</t>
   </si>
 </sst>
 </file>
@@ -674,7 +674,7 @@
         <v>16</v>
       </c>
       <c r="I2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
@@ -732,7 +732,7 @@
         <v>30</v>
       </c>
       <c r="I4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
@@ -761,7 +761,7 @@
         <v>37</v>
       </c>
       <c r="I5" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
@@ -790,7 +790,7 @@
         <v>44</v>
       </c>
       <c r="I6" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
@@ -848,7 +848,7 @@
         <v>58</v>
       </c>
       <c r="I8" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
@@ -877,7 +877,7 @@
         <v>65</v>
       </c>
       <c r="I9" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
@@ -906,7 +906,7 @@
         <v>72</v>
       </c>
       <c r="I10" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">

--- a/public/Quiz.xlsx
+++ b/public/Quiz.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Micael\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{70830B8B-3664-464C-82F2-DA3CD8425201}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EBC327F-0300-4A37-950C-22BBFC0C8179}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{814585D2-DACD-4865-94B7-0CB5BA22B5AF}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="80">
   <si>
     <t>module</t>
   </si>
@@ -54,136 +54,217 @@
     <t>correct</t>
   </si>
   <si>
-    <t>E1</t>
-  </si>
-  <si>
-    <t>E2</t>
-  </si>
-  <si>
-    <t>E3</t>
-  </si>
-  <si>
-    <t>E4</t>
-  </si>
-  <si>
-    <t>E5</t>
-  </si>
-  <si>
-    <t>E6</t>
-  </si>
-  <si>
-    <t>E7</t>
-  </si>
-  <si>
-    <t>E8</t>
-  </si>
-  <si>
-    <t>E9</t>
-  </si>
-  <si>
-    <t>E10</t>
-  </si>
-  <si>
-    <t>Vino $1500 / costo $1000 ¿Ganancia?</t>
-  </si>
-  <si>
-    <t>$300</t>
-  </si>
-  <si>
-    <t>$400</t>
-  </si>
-  <si>
-    <t>$500</t>
-  </si>
-  <si>
-    <t>$600</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>Hamburguesa $4000 / costo $2000 ¿Markup?</t>
-  </si>
-  <si>
-    <t>50%</t>
-  </si>
-  <si>
-    <t>75%</t>
-  </si>
-  <si>
-    <t>100%</t>
-  </si>
-  <si>
-    <t>200%</t>
-  </si>
-  <si>
-    <t>Salchichas $900 / costo $600 ¿Ganancia?</t>
-  </si>
-  <si>
-    <t>$200</t>
-  </si>
-  <si>
-    <t>B</t>
-  </si>
-  <si>
-    <t>Papel higiénico $1000 / costo $800 ¿Markup?</t>
-  </si>
-  <si>
-    <t>20%</t>
-  </si>
-  <si>
-    <t>25%</t>
-  </si>
-  <si>
-    <t>40%</t>
-  </si>
-  <si>
-    <t>Pañales $6000 / costo $4000 ¿Ganancia?</t>
-  </si>
-  <si>
-    <t>$1000</t>
-  </si>
-  <si>
-    <t>$1500</t>
-  </si>
-  <si>
-    <t>$2000</t>
-  </si>
-  <si>
-    <t>$2500</t>
-  </si>
-  <si>
-    <t>Gaseosa $1200 / costo $900 ¿Markup?</t>
-  </si>
-  <si>
-    <t>33%</t>
-  </si>
-  <si>
-    <t>Galletitas $1000 / costo $500 ¿Ganancia?</t>
-  </si>
-  <si>
-    <t>$250</t>
-  </si>
-  <si>
-    <t>Helado $1600 / costo $1200 ¿Markup?</t>
-  </si>
-  <si>
-    <t>Agua $750 / costo $600 ¿Ganancia?</t>
-  </si>
-  <si>
-    <t>$100</t>
-  </si>
-  <si>
-    <t>$150</t>
-  </si>
-  <si>
-    <t>Chocolate $1500 / costo $900 ¿Markup?</t>
-  </si>
-  <si>
-    <t>60%</t>
-  </si>
-  <si>
-    <t>66%</t>
+    <t>F1</t>
+  </si>
+  <si>
+    <t>Cual de estas preguntas es un ejemplo claro de implicacion (I) y no de situacion (S)?</t>
+  </si>
+  <si>
+    <t>¿Cuántas unidades estás vendiendo por semana de esta categoría?</t>
+  </si>
+  <si>
+    <t>¿A qué precio lo estás vendiendo hoy en góndola?</t>
+  </si>
+  <si>
+    <t>Si esto sigue igual un mes más, ¿en qué te termina pegando: caja, espacio o viajes al mayorista?</t>
+  </si>
+  <si>
+    <t>¿Desde cuándo notás que bajó la rotación de este producto?</t>
+  </si>
+  <si>
+    <t>¿Qué te gustaría mejorar primero: ventas, margen o tiempo?</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>F2</t>
+  </si>
+  <si>
+    <t>Cliente: “Esta flojo”. Queres aplicar SPIN rapido. Cual secuencia es la mas ordenada?</t>
+  </si>
+  <si>
+    <t>Proponer una promo para “levantar” -&gt; preguntar qué pasa -&gt; cerrar.</t>
+  </si>
+  <si>
+    <t>Situación -&gt; problema -&gt; implicación -&gt; necesidad/pago -&gt; recién ahí oferta.</t>
+  </si>
+  <si>
+    <t>Presentar novedades -&gt; sugerir algo “para mover” -&gt; recién después preguntar cómo viene.</t>
+  </si>
+  <si>
+    <t>Hacer 1–2 preguntas de situación -&gt; listar varias promos como respuesta.</t>
+  </si>
+  <si>
+    <t>Comparar con otros (“a otros les va bien”) -&gt; presionar para que compre -&gt; luego justificar.</t>
+  </si>
+  <si>
+    <t>F3</t>
+  </si>
+  <si>
+    <t>Tenes una promo que queres empujar, pero el cliente no dijo nada aun. Que haces para no caer en venta 'al azar'?</t>
+  </si>
+  <si>
+    <t>Abrís con la promo porque está activa y “suele funcionar”, y recién después ves si aplica a su local.</t>
+  </si>
+  <si>
+    <t>Hacés 1–2 preguntas de situación/problema (venta/margen/tiempo o rotación) y mostrás la promo solo si calza.</t>
+  </si>
+  <si>
+    <t>Esperás a que el cliente la pida solo, aunque no la haya visto ni sepa que existe hoy.</t>
+  </si>
+  <si>
+    <t>Arrancás por precio y descuento, buscando que cierre rápido, sin diagnosticar qué le pesa al negocio.</t>
+  </si>
+  <si>
+    <t>Cambiás de tema para no presionar y dejás la promo para otra visita, sin plantear un próximo paso</t>
+  </si>
+  <si>
+    <t>F4</t>
+  </si>
+  <si>
+    <t>En una visita corta, cuantas preguntas de situacion suelen ser suficientes para ubicar el terreno sin interrogar?</t>
+  </si>
+  <si>
+    <t>Entre 1 y 3, cortas y al punto. Para ordenar el foco y avanzar.</t>
+  </si>
+  <si>
+    <t>Cero preguntas: mejor no preguntar nada y ofrecer directo, aunque después aparezcan objeciones por falta de contexto.</t>
+  </si>
+  <si>
+    <t>Entre 6 y 8 preguntas. Para seguir con la visita con orden.</t>
+  </si>
+  <si>
+    <t>Depende: cuanto más preguntes mejor, aunque te comas el tiempo de reposición y de propuesta con sentido.</t>
+  </si>
+  <si>
+    <t>Diez preguntas mínimo, así se nota “profesional”, aunque el cliente se canse y te corte la charla.</t>
+  </si>
+  <si>
+    <t>F5</t>
+  </si>
+  <si>
+    <t>Cual opcion diferencia mejor 'problema' de 'necesidad' en SPIN?</t>
+  </si>
+  <si>
+    <t>Problema es lo que vos querés vender hoy; necesidad es lo que el cliente te pide en el momento.</t>
+  </si>
+  <si>
+    <t>Problema es el precio alto en góndola; necesidad es bajar precio para vender más rápido hoy.</t>
+  </si>
+  <si>
+    <t>Problema es falta de stock; necesidad es meter promos, asumiendo oferta sin mirar el diagnóstico.</t>
+  </si>
+  <si>
+    <t>Problema es lo que le duele (ej. baja rentabilidad); necesidad es lo que quiere mejorar (ej. ganar más).</t>
+  </si>
+  <si>
+    <t>Problema y necesidad son lo mismo, así que no hace falta diferenciarlos en la visita.</t>
+  </si>
+  <si>
+    <t>F6</t>
+  </si>
+  <si>
+    <t>Queres abrir diagnostico sin invadir. Cual frase es la mas adecuada?</t>
+  </si>
+  <si>
+    <t>“Para ubicarme rápido, te hago dos preguntas cortas y después avanzamos con el pedido.”</t>
+  </si>
+  <si>
+    <t>“¿Me compartís tus números y tu margen de esta semana para entender cómo venís?”</t>
+  </si>
+  <si>
+    <t>“Si querés, te muestro opciones y mientras me contás qué te está pasando en el negocio.”</t>
+  </si>
+  <si>
+    <t>“Antes de ofrecerte algo, ¿te puedo hacer una pregunta corta para orientarme y ayudarte mejor?”</t>
+  </si>
+  <si>
+    <t>“Decime si te molesta que te venda y me adapto según cómo te caiga hoy.”</t>
+  </si>
+  <si>
+    <t>F7</t>
+  </si>
+  <si>
+    <t>Cliente: “No paro nunca, no tengo tiempo”. Elegí el par más coherente (Situación y Problema) para arrancar.</t>
+  </si>
+  <si>
+    <t>Situación: ¿Cuántas horas estás al frente por día y quién te cubre cuando salís? / Problema: ¿Qué parte te come más tiempo: atender, reponer o salir a comprar?</t>
+  </si>
+  <si>
+    <t>Situación: ¿Hace cuánto tenés el local y cuántos años llevás en el rubro? / Problema: ¿Te está pegando más el cansancio o la falta de ventas?</t>
+  </si>
+  <si>
+    <t>Situación: ¿Hoy te abastecés con mayorista, con reparto o combinás las dos cosas? / Problema: ¿En qué momento se te desordena más el día: compras, reposición o entregas?</t>
+  </si>
+  <si>
+    <t>Situación: ¿Cómo venís de ventas esta semana y qué productos se movieron más? / Problema: ¿Sentís que el margen te está quedando corto últimamente?</t>
+  </si>
+  <si>
+    <t>Situación: Para ubicar el foco, ¿hoy te pesa más el tiempo, las ventas o el margen? / Problema: Cuando decís “sin tiempo”, ¿qué es lo que más se te traba en el día?</t>
+  </si>
+  <si>
+    <t>F8</t>
+  </si>
+  <si>
+    <t>Cual accion rompe la logica SPIN y suele disparar objeciones innecesarias?</t>
+  </si>
+  <si>
+    <t>Escuchar y resumir lo que el cliente dijo.</t>
+  </si>
+  <si>
+    <t>Hacer una pregunta de implicación antes de ofrecer.</t>
+  </si>
+  <si>
+    <t>Ofrecer productos o promo antes de entender el problema, y después bancarte objeciones.</t>
+  </si>
+  <si>
+    <t>Preguntar qué le gustaría mejorar. Para que quede corto y claro.</t>
+  </si>
+  <si>
+    <t>Usar lo que respondió para ajustar la oferta, cambiando cantidad o enfoque según su realidad y su meta.</t>
+  </si>
+  <si>
+    <t>F9</t>
+  </si>
+  <si>
+    <t>En una conversación ya hiciste preguntas de situación y preguntas de problema, y el cliente confirmó el problema. Saltaste directo a ofrecer. ¿Qué paso clave omitiste para que el cliente lo sienta más real?</t>
+  </si>
+  <si>
+    <t>Profundizar el impacto: qué te está costando hoy ese problema en plata, tiempo o pérdida de ventas.</t>
+  </si>
+  <si>
+    <t>Reforzar el encuadre inicial: presentarte bien y marcar el propósito antes de avanzar con propuestas.</t>
+  </si>
+  <si>
+    <t>Asegurar primero la reposición base “de lo que rota” y recién después volver al problema que mencionó.</t>
+  </si>
+  <si>
+    <t>Cerrar el registro de visita (GPS/nota) y retomar la charla cuando el sistema quede completo.</t>
+  </si>
+  <si>
+    <t>Ir directo al cierre: confirmar monto y condiciones, aunque todavía no se habló del beneficio concreto.</t>
+  </si>
+  <si>
+    <t>F10</t>
+  </si>
+  <si>
+    <t>Cual cierre de diagnóstico (necesidad) arma mejor el puente hacia la oferta?</t>
+  </si>
+  <si>
+    <t>“Perfecto, entonces te muestro algunas alternativas y elegimos; arranco por las promos activas de hoy.”</t>
+  </si>
+  <si>
+    <t>“Entiendo; mejor no te ofrezco nada ahora y lo retomamos otro día con más tiempo y tranquilidad.”</t>
+  </si>
+  <si>
+    <t>“Bueno, aflojemos un poco: ¿querés un café y charlamos? Después vemos si necesitás algo del pedido.”</t>
+  </si>
+  <si>
+    <t>“Listo, seguimos con lo de siempre: cargamos lo habitual y no cambiamos nada en esta visita.”</t>
+  </si>
+  <si>
+    <t>“Entonces, si lo principal es mejorar margen sin tocar precios, probemos este mix en cantidad cuidada.” Respuestas + explicacion (por que es correcta)</t>
   </si>
 </sst>
 </file>
@@ -569,292 +650,292 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
         <v>9</v>
       </c>
       <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" t="s">
         <v>19</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E3" t="s">
         <v>20</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F3" t="s">
         <v>21</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G3" t="s">
         <v>22</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H3" t="s">
         <v>23</v>
       </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-      <c r="I2" t="s">
+      <c r="I3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="C4" t="s">
         <v>25</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D4" t="s">
         <v>26</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E4" t="s">
         <v>27</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F4" t="s">
         <v>28</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G4" t="s">
         <v>29</v>
       </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>1</v>
-      </c>
-      <c r="B4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="H4" t="s">
         <v>30</v>
       </c>
-      <c r="D4" t="s">
+      <c r="I4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
         <v>31</v>
       </c>
-      <c r="E4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F4" t="s">
-        <v>21</v>
-      </c>
-      <c r="G4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4" t="s">
+      <c r="C5" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>1</v>
-      </c>
-      <c r="B5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>33</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>34</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>35</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>36</v>
       </c>
-      <c r="G5" t="s">
-        <v>26</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
+      <c r="H5" t="s">
+        <v>37</v>
       </c>
       <c r="I5" t="s">
-        <v>32</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>1</v>
+      <c r="A6" t="s">
+        <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="C6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E6" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G6" t="s">
-        <v>41</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
+        <v>43</v>
+      </c>
+      <c r="H6" t="s">
+        <v>44</v>
       </c>
       <c r="I6" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>1</v>
+      <c r="A7" t="s">
+        <v>16</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="C7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D7" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="E7" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="F7" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="G7" t="s">
-        <v>26</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="H7" t="s">
+        <v>51</v>
       </c>
       <c r="I7" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A8">
-        <v>1</v>
+      <c r="A8" t="s">
+        <v>16</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>52</v>
       </c>
       <c r="C8" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="D8" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="E8" t="s">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="F8" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="G8" t="s">
-        <v>23</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
+        <v>57</v>
+      </c>
+      <c r="H8" t="s">
+        <v>58</v>
       </c>
       <c r="I8" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A9">
-        <v>1</v>
+      <c r="A9" t="s">
+        <v>16</v>
       </c>
       <c r="B9" t="s">
+        <v>59</v>
+      </c>
+      <c r="C9" t="s">
+        <v>60</v>
+      </c>
+      <c r="D9" t="s">
+        <v>61</v>
+      </c>
+      <c r="E9" t="s">
+        <v>62</v>
+      </c>
+      <c r="F9" t="s">
+        <v>63</v>
+      </c>
+      <c r="G9" t="s">
+        <v>64</v>
+      </c>
+      <c r="H9" t="s">
+        <v>65</v>
+      </c>
+      <c r="I9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
         <v>16</v>
       </c>
-      <c r="C9" t="s">
-        <v>46</v>
-      </c>
-      <c r="D9" t="s">
-        <v>34</v>
-      </c>
-      <c r="E9" t="s">
-        <v>35</v>
-      </c>
-      <c r="F9" t="s">
-        <v>43</v>
-      </c>
-      <c r="G9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-      <c r="I9" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A10">
-        <v>1</v>
-      </c>
       <c r="B10" t="s">
-        <v>17</v>
+        <v>66</v>
       </c>
       <c r="C10" t="s">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="D10" t="s">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="E10" t="s">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="F10" t="s">
-        <v>31</v>
+        <v>70</v>
       </c>
       <c r="G10" t="s">
-        <v>45</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
+        <v>71</v>
+      </c>
+      <c r="H10" t="s">
+        <v>72</v>
       </c>
       <c r="I10" t="s">
-        <v>32</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A11">
-        <v>1</v>
+      <c r="A11" t="s">
+        <v>16</v>
       </c>
       <c r="B11" t="s">
-        <v>18</v>
+        <v>73</v>
       </c>
       <c r="C11" t="s">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="D11" t="s">
-        <v>26</v>
+        <v>75</v>
       </c>
       <c r="E11" t="s">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="F11" t="s">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="G11" t="s">
-        <v>27</v>
-      </c>
-      <c r="H11">
-        <v>0</v>
+        <v>78</v>
+      </c>
+      <c r="H11" t="s">
+        <v>79</v>
       </c>
       <c r="I11" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/public/Quiz.xlsx
+++ b/public/Quiz.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Micael\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EBC327F-0300-4A37-950C-22BBFC0C8179}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B368D66A-9560-4050-89A3-9FC1352F8D65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{814585D2-DACD-4865-94B7-0CB5BA22B5AF}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="80">
   <si>
     <t>module</t>
   </si>
@@ -54,217 +54,217 @@
     <t>correct</t>
   </si>
   <si>
-    <t>F1</t>
-  </si>
-  <si>
-    <t>Cual de estas preguntas es un ejemplo claro de implicacion (I) y no de situacion (S)?</t>
-  </si>
-  <si>
-    <t>¿Cuántas unidades estás vendiendo por semana de esta categoría?</t>
-  </si>
-  <si>
-    <t>¿A qué precio lo estás vendiendo hoy en góndola?</t>
-  </si>
-  <si>
-    <t>Si esto sigue igual un mes más, ¿en qué te termina pegando: caja, espacio o viajes al mayorista?</t>
-  </si>
-  <si>
-    <t>¿Desde cuándo notás que bajó la rotación de este producto?</t>
-  </si>
-  <si>
-    <t>¿Qué te gustaría mejorar primero: ventas, margen o tiempo?</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>F2</t>
-  </si>
-  <si>
-    <t>Cliente: “Esta flojo”. Queres aplicar SPIN rapido. Cual secuencia es la mas ordenada?</t>
-  </si>
-  <si>
-    <t>Proponer una promo para “levantar” -&gt; preguntar qué pasa -&gt; cerrar.</t>
-  </si>
-  <si>
-    <t>Situación -&gt; problema -&gt; implicación -&gt; necesidad/pago -&gt; recién ahí oferta.</t>
-  </si>
-  <si>
-    <t>Presentar novedades -&gt; sugerir algo “para mover” -&gt; recién después preguntar cómo viene.</t>
-  </si>
-  <si>
-    <t>Hacer 1–2 preguntas de situación -&gt; listar varias promos como respuesta.</t>
-  </si>
-  <si>
-    <t>Comparar con otros (“a otros les va bien”) -&gt; presionar para que compre -&gt; luego justificar.</t>
-  </si>
-  <si>
-    <t>F3</t>
-  </si>
-  <si>
-    <t>Tenes una promo que queres empujar, pero el cliente no dijo nada aun. Que haces para no caer en venta 'al azar'?</t>
-  </si>
-  <si>
-    <t>Abrís con la promo porque está activa y “suele funcionar”, y recién después ves si aplica a su local.</t>
-  </si>
-  <si>
-    <t>Hacés 1–2 preguntas de situación/problema (venta/margen/tiempo o rotación) y mostrás la promo solo si calza.</t>
-  </si>
-  <si>
-    <t>Esperás a que el cliente la pida solo, aunque no la haya visto ni sepa que existe hoy.</t>
-  </si>
-  <si>
-    <t>Arrancás por precio y descuento, buscando que cierre rápido, sin diagnosticar qué le pesa al negocio.</t>
-  </si>
-  <si>
-    <t>Cambiás de tema para no presionar y dejás la promo para otra visita, sin plantear un próximo paso</t>
-  </si>
-  <si>
-    <t>F4</t>
-  </si>
-  <si>
-    <t>En una visita corta, cuantas preguntas de situacion suelen ser suficientes para ubicar el terreno sin interrogar?</t>
-  </si>
-  <si>
-    <t>Entre 1 y 3, cortas y al punto. Para ordenar el foco y avanzar.</t>
-  </si>
-  <si>
-    <t>Cero preguntas: mejor no preguntar nada y ofrecer directo, aunque después aparezcan objeciones por falta de contexto.</t>
-  </si>
-  <si>
-    <t>Entre 6 y 8 preguntas. Para seguir con la visita con orden.</t>
-  </si>
-  <si>
-    <t>Depende: cuanto más preguntes mejor, aunque te comas el tiempo de reposición y de propuesta con sentido.</t>
-  </si>
-  <si>
-    <t>Diez preguntas mínimo, así se nota “profesional”, aunque el cliente se canse y te corte la charla.</t>
-  </si>
-  <si>
-    <t>F5</t>
-  </si>
-  <si>
-    <t>Cual opcion diferencia mejor 'problema' de 'necesidad' en SPIN?</t>
-  </si>
-  <si>
-    <t>Problema es lo que vos querés vender hoy; necesidad es lo que el cliente te pide en el momento.</t>
-  </si>
-  <si>
-    <t>Problema es el precio alto en góndola; necesidad es bajar precio para vender más rápido hoy.</t>
-  </si>
-  <si>
-    <t>Problema es falta de stock; necesidad es meter promos, asumiendo oferta sin mirar el diagnóstico.</t>
-  </si>
-  <si>
-    <t>Problema es lo que le duele (ej. baja rentabilidad); necesidad es lo que quiere mejorar (ej. ganar más).</t>
-  </si>
-  <si>
-    <t>Problema y necesidad son lo mismo, así que no hace falta diferenciarlos en la visita.</t>
-  </si>
-  <si>
-    <t>F6</t>
-  </si>
-  <si>
-    <t>Queres abrir diagnostico sin invadir. Cual frase es la mas adecuada?</t>
-  </si>
-  <si>
-    <t>“Para ubicarme rápido, te hago dos preguntas cortas y después avanzamos con el pedido.”</t>
-  </si>
-  <si>
-    <t>“¿Me compartís tus números y tu margen de esta semana para entender cómo venís?”</t>
-  </si>
-  <si>
-    <t>“Si querés, te muestro opciones y mientras me contás qué te está pasando en el negocio.”</t>
-  </si>
-  <si>
-    <t>“Antes de ofrecerte algo, ¿te puedo hacer una pregunta corta para orientarme y ayudarte mejor?”</t>
-  </si>
-  <si>
-    <t>“Decime si te molesta que te venda y me adapto según cómo te caiga hoy.”</t>
-  </si>
-  <si>
-    <t>F7</t>
-  </si>
-  <si>
-    <t>Cliente: “No paro nunca, no tengo tiempo”. Elegí el par más coherente (Situación y Problema) para arrancar.</t>
-  </si>
-  <si>
-    <t>Situación: ¿Cuántas horas estás al frente por día y quién te cubre cuando salís? / Problema: ¿Qué parte te come más tiempo: atender, reponer o salir a comprar?</t>
-  </si>
-  <si>
-    <t>Situación: ¿Hace cuánto tenés el local y cuántos años llevás en el rubro? / Problema: ¿Te está pegando más el cansancio o la falta de ventas?</t>
-  </si>
-  <si>
-    <t>Situación: ¿Hoy te abastecés con mayorista, con reparto o combinás las dos cosas? / Problema: ¿En qué momento se te desordena más el día: compras, reposición o entregas?</t>
-  </si>
-  <si>
-    <t>Situación: ¿Cómo venís de ventas esta semana y qué productos se movieron más? / Problema: ¿Sentís que el margen te está quedando corto últimamente?</t>
-  </si>
-  <si>
-    <t>Situación: Para ubicar el foco, ¿hoy te pesa más el tiempo, las ventas o el margen? / Problema: Cuando decís “sin tiempo”, ¿qué es lo que más se te traba en el día?</t>
-  </si>
-  <si>
-    <t>F8</t>
-  </si>
-  <si>
-    <t>Cual accion rompe la logica SPIN y suele disparar objeciones innecesarias?</t>
-  </si>
-  <si>
-    <t>Escuchar y resumir lo que el cliente dijo.</t>
-  </si>
-  <si>
-    <t>Hacer una pregunta de implicación antes de ofrecer.</t>
-  </si>
-  <si>
-    <t>Ofrecer productos o promo antes de entender el problema, y después bancarte objeciones.</t>
-  </si>
-  <si>
-    <t>Preguntar qué le gustaría mejorar. Para que quede corto y claro.</t>
-  </si>
-  <si>
-    <t>Usar lo que respondió para ajustar la oferta, cambiando cantidad o enfoque según su realidad y su meta.</t>
-  </si>
-  <si>
-    <t>F9</t>
-  </si>
-  <si>
-    <t>En una conversación ya hiciste preguntas de situación y preguntas de problema, y el cliente confirmó el problema. Saltaste directo a ofrecer. ¿Qué paso clave omitiste para que el cliente lo sienta más real?</t>
-  </si>
-  <si>
-    <t>Profundizar el impacto: qué te está costando hoy ese problema en plata, tiempo o pérdida de ventas.</t>
-  </si>
-  <si>
-    <t>Reforzar el encuadre inicial: presentarte bien y marcar el propósito antes de avanzar con propuestas.</t>
-  </si>
-  <si>
-    <t>Asegurar primero la reposición base “de lo que rota” y recién después volver al problema que mencionó.</t>
-  </si>
-  <si>
-    <t>Cerrar el registro de visita (GPS/nota) y retomar la charla cuando el sistema quede completo.</t>
-  </si>
-  <si>
-    <t>Ir directo al cierre: confirmar monto y condiciones, aunque todavía no se habló del beneficio concreto.</t>
-  </si>
-  <si>
-    <t>F10</t>
-  </si>
-  <si>
-    <t>Cual cierre de diagnóstico (necesidad) arma mejor el puente hacia la oferta?</t>
-  </si>
-  <si>
-    <t>“Perfecto, entonces te muestro algunas alternativas y elegimos; arranco por las promos activas de hoy.”</t>
-  </si>
-  <si>
-    <t>“Entiendo; mejor no te ofrezco nada ahora y lo retomamos otro día con más tiempo y tranquilidad.”</t>
-  </si>
-  <si>
-    <t>“Bueno, aflojemos un poco: ¿querés un café y charlamos? Después vemos si necesitás algo del pedido.”</t>
-  </si>
-  <si>
-    <t>“Listo, seguimos con lo de siempre: cargamos lo habitual y no cambiamos nada en esta visita.”</t>
-  </si>
-  <si>
-    <t>“Entonces, si lo principal es mejorar margen sin tocar precios, probemos este mix en cantidad cuidada.” Respuestas + explicacion (por que es correcta)</t>
+    <t>6</t>
+  </si>
+  <si>
+    <t>G1</t>
+  </si>
+  <si>
+    <t>Cliente: “Vendo, pero no me queda nada”. En que tipo de dolor cae principalmente?</t>
+  </si>
+  <si>
+    <t>Dolor de ventas: vende “algo”, pero siente que no alcanza volumen, como si el movimiento no compensara el esfuerzo del día.</t>
+  </si>
+  <si>
+    <t>Dolor de rentabilidad/margen: hay venta, pero la ganancia por operación es baja y “no queda nada” al final, aunque entre plata.</t>
+  </si>
+  <si>
+    <t>Dolor de tiempo/cansancio: vende y trabaja. Para dejar una salida concreta. Para no entrar en detalles de más.</t>
+  </si>
+  <si>
+    <t>Dolor de espacio/stock: vende, pero se le desordena el local, se acumula mercadería o no puede exhibir bien, y eso le come resultado.</t>
+  </si>
+  <si>
+    <t>Comentario general: expresa frustración, pero no permite ubicar si es margen, ventas, tiempo o stock sin una pregunta más.</t>
+  </si>
+  <si>
+    <t>G2</t>
+  </si>
+  <si>
+    <t>Cliente: “No paro nunca, siempre tengo que ir yo al mayorista”. Que pregunta convierte mejor ese comentario en necesidad explicita?</t>
+  </si>
+  <si>
+    <t>“¿Te pasa que preferís hacerlo vos o es que no tenés a quién delegarlo en el local?”</t>
+  </si>
+  <si>
+    <t>“Si pudieras ahorrarte uno o dos viajes al mayorista por mes, ¿eso te resolvería parte del día?”</t>
+  </si>
+  <si>
+    <t>“¿Cuánto te cuesta por semana entre nafta, peajes y el tiempo que perdés en esos viajes?”</t>
+  </si>
+  <si>
+    <t>“¿Qué es lo que te obliga a ir vos: precio, falta de entrega o no tener una reposición armada?”</t>
+  </si>
+  <si>
+    <t>“Entiendo; hoy sigamos con lo de siempre y la próxima lo miramos con más calma.”</t>
+  </si>
+  <si>
+    <t>G3</t>
+  </si>
+  <si>
+    <t>Elegi la mejor pregunta de implicacion para un cliente con stock clavado.</t>
+  </si>
+  <si>
+    <t>“Si ese stock sigue parado 2–3 meses más, ¿qué te termina costando: plata inmovilizada, espacio o perder otras ventas?”.</t>
+  </si>
+  <si>
+    <t>“¿Cuánto espacio de góndola/heladera tenés disponible hoy?”. Para que quede corto y claro.</t>
+  </si>
+  <si>
+    <t>“¿Te convence esta marca o preferís otra?”. Para seguir con la visita con orden.</t>
+  </si>
+  <si>
+    <t>“Cuando vas al mayorista, ¿cada cuánto terminás yendo por semana?”.</t>
+  </si>
+  <si>
+    <t>“¿Hace cuánto lo trabajás y desde cuándo notaste que se clavó?”.</t>
+  </si>
+  <si>
+    <t>G4</t>
+  </si>
+  <si>
+    <t>Cliente: “Tengo el deposito explotado”. Cual frase de empatia es mas alineada?</t>
+  </si>
+  <si>
+    <t>“Te entiendo; a veces pasa cuando se compra sin mirar rotación y después queda todo apretado.”</t>
+  </si>
+  <si>
+    <t>“Te entiendo; es bastante común en estos días, vamos viendo cómo lo acomodamos con calma.”</t>
+  </si>
+  <si>
+    <t>“Te entiendo; con el depósito así se traba todo: no entra reposición, se desordena y se pierden ventas por falta de espacio.”</t>
+  </si>
+  <si>
+    <t>“Te entiendo; no es tan grave, suele acomodarse solo con un poco de orden y tiempo.”</t>
+  </si>
+  <si>
+    <t>“Te entiendo; metamos igual y después lo acomodás, así aprovechamos la visita y no perdés la vuelta.”</t>
+  </si>
+  <si>
+    <t>G5</t>
+  </si>
+  <si>
+    <t>El cliente dice dos cosas: “No se vende” y “no tengo lugar”. Que haria mejor un preventista para definir el foco?</t>
+  </si>
+  <si>
+    <t>“Para ordenar la charla, si tuvieras que elegir una sola: ¿hoy te frena más la venta o el espacio?”</t>
+  </si>
+  <si>
+    <t>“Arranco con una promo puntual para destrabar algo rápido y después vemos lo del lugar.”</t>
+  </si>
+  <si>
+    <t>“Dale, pasame lo de siempre y lo cargo, así no perdemos tiempo en esta visita.”</t>
+  </si>
+  <si>
+    <t>“Antes de eso, contame cómo venís con costos fijos e impuestos este mes, así entiendo el contexto.”</t>
+  </si>
+  <si>
+    <t>“En otros locales se está vendiendo; contame qué estás haciendo distinto acá con la categoría.”</t>
+  </si>
+  <si>
+    <t>G6</t>
+  </si>
+  <si>
+    <t>Mientras el cliente te cuenta su problema, cual conducta va en contra de una buena profundizacion del dolor?</t>
+  </si>
+  <si>
+    <t>Dejarlo terminar y hacer una pregunta corta para ordenar lo que escuchaste.</t>
+  </si>
+  <si>
+    <t>Hacer una pregunta sobre consecuencias para dimensionar el impacto del problema en su negocio.</t>
+  </si>
+  <si>
+    <t>Usar una frase breve de empatía y seguir con una pregunta para entender mejor el punto.</t>
+  </si>
+  <si>
+    <t>Interrumpir para mostrar catálogos y precios y pasar directo a oferta “para ahorrar tiempo”.</t>
+  </si>
+  <si>
+    <t>Repetir con tus palabras lo entendido y confirmar si lo interpretaste bien.</t>
+  </si>
+  <si>
+    <t>G7</t>
+  </si>
+  <si>
+    <t>Cliente: “Vendo, pero no me queda plata. Encima los impuestos me matan”. Elegi la mejor combinacion (pregunta de implicación + frase de empatía) para seguir.</t>
+  </si>
+  <si>
+    <t>Pregunta: ¿Más o menos cuánto se te va en impuestos por mes? + Empatía: Te entiendo, es un golpe cuando el margen ya viene justo.</t>
+  </si>
+  <si>
+    <t>Pregunta: ¿Y qué estás haciendo distinto que antes? + Empatía: A muchos les pasa, hay que aguantar. Para que quede corto y claro.</t>
+  </si>
+  <si>
+    <t>Pregunta: ¿Si subís un poco los precios lo compensás? + Empatía: Tranquilo, se acomoda. Para no entrar en detalles de más.</t>
+  </si>
+  <si>
+    <t>Pregunta: Si seguís con este margen 6 meses más, ¿qué te pasa en el negocio (pagos, reinversión, compras)? + Empatía: Te entiendo, es frustrante trabajar y que no quede.</t>
+  </si>
+  <si>
+    <t>Pregunta: ¿Qué sentís que te pega más: impuestos, costos o precio de compra? + Empatía: Qué bronca, la verdad.</t>
+  </si>
+  <si>
+    <t>G8</t>
+  </si>
+  <si>
+    <t>Despues de una pregunta de implicacion, cual es el paso mas conveniente antes de ofrecer producto?</t>
+  </si>
+  <si>
+    <t>Pasar directo a “te muestro cinco opciones que suelen funcionar”, sin chequear si encaja con lo que reconoció.</t>
+  </si>
+  <si>
+    <t>Hacer un comentario neutro y cambiar de tema, dejando la consecuencia planteada sin siguiente paso.</t>
+  </si>
+  <si>
+    <t>Empezar a hablar de entregas y condiciones, aunque no responda al foco del problema que salió.</t>
+  </si>
+  <si>
+    <t>Ir a “cerrémoslo así” y pedir confirmación del pedido, sin acordar antes qué sería útil.</t>
+  </si>
+  <si>
+    <t>Resumir en una frase, chequear acuerdo y recién ahí proponer una opción alineada al foco.</t>
+  </si>
+  <si>
+    <t>G9</t>
+  </si>
+  <si>
+    <t>Cual de estas frases es un ejemplo de necesidad explicita (no solo queja)?</t>
+  </si>
+  <si>
+    <t>“Estoy cansado” y me está costando sostener el ritmo del local esta semana.</t>
+  </si>
+  <si>
+    <t>“No se vende nada” y siento que la mercadería no se está moviendo como antes.</t>
+  </si>
+  <si>
+    <t>“Necesito un proveedor que me entregue y me ahorre ir al mayorista cada semana.”</t>
+  </si>
+  <si>
+    <t>“Los precios están altos” y así se me complica vender sin perder margen del local.</t>
+  </si>
+  <si>
+    <t>“El barrio está difícil” y cada vez entra menos gente a comprar en estos días.</t>
+  </si>
+  <si>
+    <t>G10</t>
+  </si>
+  <si>
+    <t>El cliente dice rápido: “No paro nunca, tengo que ir yo al mayorista.” Tenés 1 minuto para profundizar sin invadir. ¿Qué micro-pregunta es la más efectiva?</t>
+  </si>
+  <si>
+    <t>“¿Cada cuánto estás yendo al mayorista y en qué momento del día se te complica más hacerlo?”</t>
+  </si>
+  <si>
+    <t>“¿Qué es lo que te obliga a ir vos: precio, falta de entrega o que se te corta la mercadería?”</t>
+  </si>
+  <si>
+    <t>“Cuando vas al mayorista, ¿qué terminás buscando sí o sí para no quedarte corto en la semana?”</t>
+  </si>
+  <si>
+    <t>“¿Te pasa por falta de tiempo o porque no confiás en que te entreguen como corresponde siempre?”</t>
+  </si>
+  <si>
+    <t>“Si pudieras ahorrarte uno o dos viajes al mayorista por mes, ¿eso te resolvería parte del día?” Respuestas + explicacion (por que es correcta)</t>
   </si>
 </sst>
 </file>
@@ -649,37 +649,37 @@
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>5</v>
+      <c r="A2" t="s">
+        <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
         <v>17</v>
@@ -708,7 +708,7 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
@@ -732,12 +732,12 @@
         <v>30</v>
       </c>
       <c r="I4" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
         <v>31</v>
@@ -761,12 +761,12 @@
         <v>37</v>
       </c>
       <c r="I5" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
         <v>38</v>
@@ -790,12 +790,12 @@
         <v>44</v>
       </c>
       <c r="I6" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
         <v>45</v>
@@ -824,7 +824,7 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="B8" t="s">
         <v>52</v>
@@ -848,12 +848,12 @@
         <v>58</v>
       </c>
       <c r="I8" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="B9" t="s">
         <v>59</v>
@@ -877,12 +877,12 @@
         <v>65</v>
       </c>
       <c r="I9" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="B10" t="s">
         <v>66</v>
@@ -906,12 +906,12 @@
         <v>72</v>
       </c>
       <c r="I10" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="B11" t="s">
         <v>73</v>

--- a/public/Quiz.xlsx
+++ b/public/Quiz.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Micael\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B368D66A-9560-4050-89A3-9FC1352F8D65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE839F75-0D87-457D-AB75-55CFBE05BCE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{814585D2-DACD-4865-94B7-0CB5BA22B5AF}"/>
   </bookViews>
@@ -54,217 +54,217 @@
     <t>correct</t>
   </si>
   <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>G1</t>
-  </si>
-  <si>
-    <t>Cliente: “Vendo, pero no me queda nada”. En que tipo de dolor cae principalmente?</t>
-  </si>
-  <si>
-    <t>Dolor de ventas: vende “algo”, pero siente que no alcanza volumen, como si el movimiento no compensara el esfuerzo del día.</t>
-  </si>
-  <si>
-    <t>Dolor de rentabilidad/margen: hay venta, pero la ganancia por operación es baja y “no queda nada” al final, aunque entre plata.</t>
-  </si>
-  <si>
-    <t>Dolor de tiempo/cansancio: vende y trabaja. Para dejar una salida concreta. Para no entrar en detalles de más.</t>
-  </si>
-  <si>
-    <t>Dolor de espacio/stock: vende, pero se le desordena el local, se acumula mercadería o no puede exhibir bien, y eso le come resultado.</t>
-  </si>
-  <si>
-    <t>Comentario general: expresa frustración, pero no permite ubicar si es margen, ventas, tiempo o stock sin una pregunta más.</t>
-  </si>
-  <si>
-    <t>G2</t>
-  </si>
-  <si>
-    <t>Cliente: “No paro nunca, siempre tengo que ir yo al mayorista”. Que pregunta convierte mejor ese comentario en necesidad explicita?</t>
-  </si>
-  <si>
-    <t>“¿Te pasa que preferís hacerlo vos o es que no tenés a quién delegarlo en el local?”</t>
-  </si>
-  <si>
-    <t>“Si pudieras ahorrarte uno o dos viajes al mayorista por mes, ¿eso te resolvería parte del día?”</t>
-  </si>
-  <si>
-    <t>“¿Cuánto te cuesta por semana entre nafta, peajes y el tiempo que perdés en esos viajes?”</t>
-  </si>
-  <si>
-    <t>“¿Qué es lo que te obliga a ir vos: precio, falta de entrega o no tener una reposición armada?”</t>
-  </si>
-  <si>
-    <t>“Entiendo; hoy sigamos con lo de siempre y la próxima lo miramos con más calma.”</t>
-  </si>
-  <si>
-    <t>G3</t>
-  </si>
-  <si>
-    <t>Elegi la mejor pregunta de implicacion para un cliente con stock clavado.</t>
-  </si>
-  <si>
-    <t>“Si ese stock sigue parado 2–3 meses más, ¿qué te termina costando: plata inmovilizada, espacio o perder otras ventas?”.</t>
-  </si>
-  <si>
-    <t>“¿Cuánto espacio de góndola/heladera tenés disponible hoy?”. Para que quede corto y claro.</t>
-  </si>
-  <si>
-    <t>“¿Te convence esta marca o preferís otra?”. Para seguir con la visita con orden.</t>
-  </si>
-  <si>
-    <t>“Cuando vas al mayorista, ¿cada cuánto terminás yendo por semana?”.</t>
-  </si>
-  <si>
-    <t>“¿Hace cuánto lo trabajás y desde cuándo notaste que se clavó?”.</t>
-  </si>
-  <si>
-    <t>G4</t>
-  </si>
-  <si>
-    <t>Cliente: “Tengo el deposito explotado”. Cual frase de empatia es mas alineada?</t>
-  </si>
-  <si>
-    <t>“Te entiendo; a veces pasa cuando se compra sin mirar rotación y después queda todo apretado.”</t>
-  </si>
-  <si>
-    <t>“Te entiendo; es bastante común en estos días, vamos viendo cómo lo acomodamos con calma.”</t>
-  </si>
-  <si>
-    <t>“Te entiendo; con el depósito así se traba todo: no entra reposición, se desordena y se pierden ventas por falta de espacio.”</t>
-  </si>
-  <si>
-    <t>“Te entiendo; no es tan grave, suele acomodarse solo con un poco de orden y tiempo.”</t>
-  </si>
-  <si>
-    <t>“Te entiendo; metamos igual y después lo acomodás, así aprovechamos la visita y no perdés la vuelta.”</t>
-  </si>
-  <si>
-    <t>G5</t>
-  </si>
-  <si>
-    <t>El cliente dice dos cosas: “No se vende” y “no tengo lugar”. Que haria mejor un preventista para definir el foco?</t>
-  </si>
-  <si>
-    <t>“Para ordenar la charla, si tuvieras que elegir una sola: ¿hoy te frena más la venta o el espacio?”</t>
-  </si>
-  <si>
-    <t>“Arranco con una promo puntual para destrabar algo rápido y después vemos lo del lugar.”</t>
-  </si>
-  <si>
-    <t>“Dale, pasame lo de siempre y lo cargo, así no perdemos tiempo en esta visita.”</t>
-  </si>
-  <si>
-    <t>“Antes de eso, contame cómo venís con costos fijos e impuestos este mes, así entiendo el contexto.”</t>
-  </si>
-  <si>
-    <t>“En otros locales se está vendiendo; contame qué estás haciendo distinto acá con la categoría.”</t>
-  </si>
-  <si>
-    <t>G6</t>
-  </si>
-  <si>
-    <t>Mientras el cliente te cuenta su problema, cual conducta va en contra de una buena profundizacion del dolor?</t>
-  </si>
-  <si>
-    <t>Dejarlo terminar y hacer una pregunta corta para ordenar lo que escuchaste.</t>
-  </si>
-  <si>
-    <t>Hacer una pregunta sobre consecuencias para dimensionar el impacto del problema en su negocio.</t>
-  </si>
-  <si>
-    <t>Usar una frase breve de empatía y seguir con una pregunta para entender mejor el punto.</t>
-  </si>
-  <si>
-    <t>Interrumpir para mostrar catálogos y precios y pasar directo a oferta “para ahorrar tiempo”.</t>
-  </si>
-  <si>
-    <t>Repetir con tus palabras lo entendido y confirmar si lo interpretaste bien.</t>
-  </si>
-  <si>
-    <t>G7</t>
-  </si>
-  <si>
-    <t>Cliente: “Vendo, pero no me queda plata. Encima los impuestos me matan”. Elegi la mejor combinacion (pregunta de implicación + frase de empatía) para seguir.</t>
-  </si>
-  <si>
-    <t>Pregunta: ¿Más o menos cuánto se te va en impuestos por mes? + Empatía: Te entiendo, es un golpe cuando el margen ya viene justo.</t>
-  </si>
-  <si>
-    <t>Pregunta: ¿Y qué estás haciendo distinto que antes? + Empatía: A muchos les pasa, hay que aguantar. Para que quede corto y claro.</t>
-  </si>
-  <si>
-    <t>Pregunta: ¿Si subís un poco los precios lo compensás? + Empatía: Tranquilo, se acomoda. Para no entrar en detalles de más.</t>
-  </si>
-  <si>
-    <t>Pregunta: Si seguís con este margen 6 meses más, ¿qué te pasa en el negocio (pagos, reinversión, compras)? + Empatía: Te entiendo, es frustrante trabajar y que no quede.</t>
-  </si>
-  <si>
-    <t>Pregunta: ¿Qué sentís que te pega más: impuestos, costos o precio de compra? + Empatía: Qué bronca, la verdad.</t>
-  </si>
-  <si>
-    <t>G8</t>
-  </si>
-  <si>
-    <t>Despues de una pregunta de implicacion, cual es el paso mas conveniente antes de ofrecer producto?</t>
-  </si>
-  <si>
-    <t>Pasar directo a “te muestro cinco opciones que suelen funcionar”, sin chequear si encaja con lo que reconoció.</t>
-  </si>
-  <si>
-    <t>Hacer un comentario neutro y cambiar de tema, dejando la consecuencia planteada sin siguiente paso.</t>
-  </si>
-  <si>
-    <t>Empezar a hablar de entregas y condiciones, aunque no responda al foco del problema que salió.</t>
-  </si>
-  <si>
-    <t>Ir a “cerrémoslo así” y pedir confirmación del pedido, sin acordar antes qué sería útil.</t>
-  </si>
-  <si>
-    <t>Resumir en una frase, chequear acuerdo y recién ahí proponer una opción alineada al foco.</t>
-  </si>
-  <si>
-    <t>G9</t>
-  </si>
-  <si>
-    <t>Cual de estas frases es un ejemplo de necesidad explicita (no solo queja)?</t>
-  </si>
-  <si>
-    <t>“Estoy cansado” y me está costando sostener el ritmo del local esta semana.</t>
-  </si>
-  <si>
-    <t>“No se vende nada” y siento que la mercadería no se está moviendo como antes.</t>
-  </si>
-  <si>
-    <t>“Necesito un proveedor que me entregue y me ahorre ir al mayorista cada semana.”</t>
-  </si>
-  <si>
-    <t>“Los precios están altos” y así se me complica vender sin perder margen del local.</t>
-  </si>
-  <si>
-    <t>“El barrio está difícil” y cada vez entra menos gente a comprar en estos días.</t>
-  </si>
-  <si>
-    <t>G10</t>
-  </si>
-  <si>
-    <t>El cliente dice rápido: “No paro nunca, tengo que ir yo al mayorista.” Tenés 1 minuto para profundizar sin invadir. ¿Qué micro-pregunta es la más efectiva?</t>
-  </si>
-  <si>
-    <t>“¿Cada cuánto estás yendo al mayorista y en qué momento del día se te complica más hacerlo?”</t>
-  </si>
-  <si>
-    <t>“¿Qué es lo que te obliga a ir vos: precio, falta de entrega o que se te corta la mercadería?”</t>
-  </si>
-  <si>
-    <t>“Cuando vas al mayorista, ¿qué terminás buscando sí o sí para no quedarte corto en la semana?”</t>
-  </si>
-  <si>
-    <t>“¿Te pasa por falta de tiempo o porque no confiás en que te entreguen como corresponde siempre?”</t>
-  </si>
-  <si>
-    <t>“Si pudieras ahorrarte uno o dos viajes al mayorista por mes, ¿eso te resolvería parte del día?” Respuestas + explicacion (por que es correcta)</t>
+    <t>4</t>
+  </si>
+  <si>
+    <t>E1</t>
+  </si>
+  <si>
+    <t>En góndola ves un hueco de tu producto más rotador (A) y, en su lugar, un producto de otro proveedor (C). El cliente está ocupado. ¿Cuál es tu primera acción más inteligente?</t>
+  </si>
+  <si>
+    <t>Preguntar por qué está comprando C a otro proveedor antes de resolver reposición y quiebres de tus productos.</t>
+  </si>
+  <si>
+    <t>Asegurar reposición de A para no perder ventas y, con eso cubierto, abrir la conversación sobre el frente de C.</t>
+  </si>
+  <si>
+    <t>Pedirle que saque C de la góndola y te dé ese frente, sin revisar rotación ni motivo de la elección.</t>
+  </si>
+  <si>
+    <t>Dejar el quiebre de A para después y arrancar mostrando promos generales para sumar volumen hoy.</t>
+  </si>
+  <si>
+    <t>Abrir la charla por logística/entregas antes de resolver el faltante visible en góndola y su impacto.</t>
+  </si>
+  <si>
+    <t>E2</t>
+  </si>
+  <si>
+    <t>Ves un producto tuyo bien ubicado pero sin precio visible. Cual accion se alinea mejor al rol?</t>
+  </si>
+  <si>
+    <t>No decir nada: asumir que el cliente ya sabe el precio y que eso no afecta la decisión de compra.</t>
+  </si>
+  <si>
+    <t>Sugerir poner precio visible y, si corresponde, un cartel simple para facilitar la venta y la rotación.</t>
+  </si>
+  <si>
+    <t>Cambiar vos mismo el precio con una etiqueta nueva, aunque no corresponda. Para dejar una salida concreta.</t>
+  </si>
+  <si>
+    <t>Sacar el producto del frente para que no se note, y después ver si lo reubicás en otro lado.</t>
+  </si>
+  <si>
+    <t>Usar ese detalle para presionarlo a comprar más. Para ordenar el foco y avanzar.</t>
+  </si>
+  <si>
+    <t>E3</t>
+  </si>
+  <si>
+    <t>El cliente te dice: “La entrega anterior llegó tarde”. Cual respuesta te mantiene profesional y te devuelve rapido al foco comercial?</t>
+  </si>
+  <si>
+    <t>Entiendo, gracias por avisarme. Lo registro para que se corrija. Para no perder ventas hoy: ¿cómo venís de stock y reposición?</t>
+  </si>
+  <si>
+    <t>Sí, tenés razón, no vuelve a pasar; te explico rápido qué pasó y cómo se corrige.</t>
+  </si>
+  <si>
+    <t>No fue culpa mía; si tu encargado pidió tarde o el depósito se demoró, no es tema mío.</t>
+  </si>
+  <si>
+    <t>Contame bien: qué hora, quién recibió, qué remito y qué faltó, y lo vemos ahora.</t>
+  </si>
+  <si>
+    <t>Eso no lo manejo yo, yo solo vendo. Para que quede corto y claro.</t>
+  </si>
+  <si>
+    <t>E4</t>
+  </si>
+  <si>
+    <t>El Bot muestra que normalmente compra 5 cajas por semana de un producto. En heladera quedan 2 unidades. Cual propuesta de reposicion es mas ordenada?</t>
+  </si>
+  <si>
+    <t>“Veo que venís en 5 cajas por semana y hoy te quedan 2 unidades; ¿reponemos 5 para cubrir esta semana?”</t>
+  </si>
+  <si>
+    <t>“Decime qué te gustaría llevar hoy y lo armamos sobre la marcha con lo que te parezca.”</t>
+  </si>
+  <si>
+    <t>“Aprovechemos y llevemos 15 cajas así te olvidás por un tiempo y no te preocupás después.”</t>
+  </si>
+  <si>
+    <t>“Si te quedó poco, mejor no repongas por ahora y lo revisamos más adelante en otra visita.”</t>
+  </si>
+  <si>
+    <t>“Te dejo el catálogo para que lo mires y después lo vemos con más tiempo cuando estés más tranquilo.”</t>
+  </si>
+  <si>
+    <t>E5</t>
+  </si>
+  <si>
+    <t>Detectas un producto tuyo clavado (mismo nivel de stock hace semanas). Que enfoque de reposicion es mas inteligente?</t>
+  </si>
+  <si>
+    <t>“Sumemos un poco más del mismo para darle más presencia y ver si se mueve por volumen.”</t>
+  </si>
+  <si>
+    <t>“Dejémoslo como está y sigamos con el pedido habitual, sin meternos en ese producto hoy.”</t>
+  </si>
+  <si>
+    <t>“Antes de reponer, ubiquemos qué lo frena: salida, precio o ubicación, y definimos un ajuste puntual.”</t>
+  </si>
+  <si>
+    <t>“Esto lo compraste mal; así no se trabaja. La próxima pedime solo lo que rota bien.”</t>
+  </si>
+  <si>
+    <t>“Después lo vemos; por ahora sigamos con otra cosa y cerramos el pedido como siempre hoy.”</t>
+  </si>
+  <si>
+    <t>E6</t>
+  </si>
+  <si>
+    <t>Despues de asegurar reposicion, queres entender por que el cliente compra una categoria a otro proveedor. Que pregunta cuida mejor el vinculo?</t>
+  </si>
+  <si>
+    <t>¿Por qué le comprás a otro si yo también te lo puedo vender hoy mismo acá?</t>
+  </si>
+  <si>
+    <t>¿Ese proveedor te da mejor precio? Si no, te conviene comprarme a mí esta vez hoy.</t>
+  </si>
+  <si>
+    <t>¿Qué te gusta más de ese proveedor: precio, entrega o surtido, para entender tu elección mejor?</t>
+  </si>
+  <si>
+    <t>¿Qué te viene resolviendo ese proveedor en esa categoría, para ver cómo me ajusto yo también?</t>
+  </si>
+  <si>
+    <t>Si preferís, no lo hablamos ahora; seguimos con lo de siempre y cerramos tranquilo hoy acá.</t>
+  </si>
+  <si>
+    <t>E7</t>
+  </si>
+  <si>
+    <t>Ves que el precio en gondola de tu producto esta muy por encima de lo habitual del barrio. Que accion es mas alineada al foco en venta?</t>
+  </si>
+  <si>
+    <t>“Lo dejo como está; el precio lo maneja el local y no me meto con eso hoy.”</t>
+  </si>
+  <si>
+    <t>“Lo bajo yo ahora mismo para que se venda, y después vemos el resto cuando haya tiempo.”</t>
+  </si>
+  <si>
+    <t>“Ese precio está mal; así no vas a vender” y lo marco como error sin preguntar contexto.</t>
+  </si>
+  <si>
+    <t>“Llevemos más cantidad igual para compensar” y después vemos si se mueve con volumen ahí.</t>
+  </si>
+  <si>
+    <t>“¿A cuánto lo estás vendiendo hoy?” para entender el punto de partida antes de proponer ajuste.</t>
+  </si>
+  <si>
+    <t>E8</t>
+  </si>
+  <si>
+    <t>Que tema NO deberias abrir vos durante la recorrida si el cliente no lo menciona?</t>
+  </si>
+  <si>
+    <t>Faltantes de stock o quiebres en góndola que puedan estar frenando ventas hoy.</t>
+  </si>
+  <si>
+    <t>Productos que no rotan o están clavados y ocupan espacio sin aportar margen.</t>
+  </si>
+  <si>
+    <t>Precio visible en góndola si está fuera de rango para el barrio o la rotación.</t>
+  </si>
+  <si>
+    <t>Problemas de logística o entregas como tema principal, sin señal previa del cliente.</t>
+  </si>
+  <si>
+    <t>Productos de otros proveedores en la categoría y cómo conviven con tus frentes actuales.</t>
+  </si>
+  <si>
+    <t>E9</t>
+  </si>
+  <si>
+    <t>Tenes 3 minutos para recorrer. Que chequeo te da mas informacion para armar un pedido base con sentido?</t>
+  </si>
+  <si>
+    <t>Chequear faltantes y quiebres de lo que más rota para armar la reposición base del local hoy.</t>
+  </si>
+  <si>
+    <t>Detectar qué productos están clavados y qué conviene pausar, sin mirar el resto del recorrido.</t>
+  </si>
+  <si>
+    <t>Revisar precios visibles en góndola para ver desvíos, sin mirar rotación ni faltantes del local.</t>
+  </si>
+  <si>
+    <t>Abrir por entregas y servicio para ver reclamos, antes de revisar stock en punto de venta.</t>
+  </si>
+  <si>
+    <t>Mirar el triángulo: vendido, no vendido y competencia, para armar base y una oportunidad real.</t>
+  </si>
+  <si>
+    <t>E10</t>
+  </si>
+  <si>
+    <t>Cual frase propone reposicion base sin marear al cliente?</t>
+  </si>
+  <si>
+    <t>Si querés, decime qué te falta hoy y lo armamos rápido con eso.</t>
+  </si>
+  <si>
+    <t>Te muestro algunas opciones y vos vas eligiendo de a poco lo que prefieras.</t>
+  </si>
+  <si>
+    <t>Veo que de X estás corto; para cubrir la semana te propongo reponer 5 cajas hoy.</t>
+  </si>
+  <si>
+    <t>Hoy te recomiendo sumar algunos lanzamientos que están saliendo y probarlos esta semana.</t>
+  </si>
+  <si>
+    <t>Necesito que hoy el pedido sea más grande para que me cierre bien la visita. Respuestas + explicacion (por que es correcta)</t>
   </si>
 </sst>
 </file>
@@ -761,7 +761,7 @@
         <v>37</v>
       </c>
       <c r="I5" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
@@ -790,7 +790,7 @@
         <v>44</v>
       </c>
       <c r="I6" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
@@ -848,7 +848,7 @@
         <v>58</v>
       </c>
       <c r="I8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
@@ -877,7 +877,7 @@
         <v>65</v>
       </c>
       <c r="I9" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
@@ -906,7 +906,7 @@
         <v>72</v>
       </c>
       <c r="I10" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
@@ -935,7 +935,7 @@
         <v>79</v>
       </c>
       <c r="I11" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
